--- a/plantillas/Registro_Casino.xlsx
+++ b/plantillas/Registro_Casino.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Registro!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Registro!$A$4:$H$2004</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Registro!$A$4:$I$2004</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0">
+    <comment ref="I6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t xml:space="preserve">Registro diario del Casino</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">A mano</t>
   </si>
   <si>
-    <t xml:space="preserve">Escribe Fecha (dd-mm-aaaa), Nombre, Área (lista), Hora ingreso y Hora almuerzo (hh:mm) y en "Almorzó" elige SI o NO.</t>
+    <t xml:space="preserve">Escribe Fecha (dd-mm-aaaa), Nombre, Área (lista), Hora ingreso y Hora almuerzo (hh:mm) y en "Almorzó" elige SI o NO. Si el área es Visitante, en "Área visita" elige a qué área viene.</t>
   </si>
   <si>
     <t xml:space="preserve">Fila de ejemplo</t>
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Registro diario de personas que pasan al casino</t>
   </si>
   <si>
-    <t xml:space="preserve">Mismo orden de columnas que el CSV de la app (A a G). Columna H para observaciones.</t>
+    <t xml:space="preserve">Mismo orden de columnas que el CSV de la app (A a H). Columna I para observaciones. "Área visita" solo se llena si el área es Visitante.</t>
   </si>
   <si>
     <t xml:space="preserve">ID QR</t>
@@ -219,6 +219,9 @@
     <t xml:space="preserve">Hora almuerzo</t>
   </si>
   <si>
+    <t xml:space="preserve">Área visita</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observaciones</t>
   </si>
   <si>
@@ -228,7 +231,7 @@
     <t xml:space="preserve">Juan Pérez (EJEMPLO, borrar)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mantención</t>
+    <t xml:space="preserve">Mantenimiento</t>
   </si>
   <si>
     <t xml:space="preserve">SI</t>
@@ -267,6 +270,9 @@
     <t xml:space="preserve">% que almorzó</t>
   </si>
   <si>
+    <t xml:space="preserve">Visitantes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Primer almuerzo</t>
   </si>
   <si>
@@ -283,6 +289,9 @@
   </si>
   <si>
     <t xml:space="preserve">% almorzó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitas recibidas</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -315,22 +324,25 @@
     <t xml:space="preserve">Producción</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega</t>
+    <t xml:space="preserve">Control calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Calidad</t>
+    <t xml:space="preserve">Logística</t>
   </si>
   <si>
-    <t xml:space="preserve">Administración</t>
+    <t xml:space="preserve">Seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevención de Riesgos</t>
+    <t xml:space="preserve">HSE</t>
   </si>
   <si>
-    <t xml:space="preserve">Contratista</t>
+    <t xml:space="preserve">Gestión Humana</t>
   </si>
   <si>
-    <t xml:space="preserve">Visita</t>
+    <t xml:space="preserve">Contabilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitante</t>
   </si>
 </sst>
 </file>
@@ -452,7 +464,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF9C4"/>
-        <bgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFF3F4F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -685,7 +697,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -730,6 +742,13 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE68A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -796,7 +815,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFDE68A"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFCA5A5"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1156,17 +1175,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H1005"/>
+  <dimension ref="A1:I1005"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1204,30 +1224,34 @@
       <c r="H4" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="I4" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0.327777777777778</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0.545138888888889</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1240,6 +1264,7 @@
       <c r="F6" s="18"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15"/>
@@ -1250,6 +1275,7 @@
       <c r="F7" s="18"/>
       <c r="G7" s="17"/>
       <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15"/>
@@ -1260,6 +1286,7 @@
       <c r="F8" s="18"/>
       <c r="G8" s="17"/>
       <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
@@ -1270,6 +1297,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="17"/>
       <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15"/>
@@ -1280,6 +1308,7 @@
       <c r="F10" s="18"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15"/>
@@ -1290,6 +1319,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="17"/>
       <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15"/>
@@ -1300,6 +1330,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="17"/>
       <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15"/>
@@ -1310,6 +1341,7 @@
       <c r="F13" s="18"/>
       <c r="G13" s="17"/>
       <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15"/>
@@ -1320,6 +1352,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15"/>
@@ -1330,6 +1363,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="17"/>
       <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15"/>
@@ -1340,6 +1374,7 @@
       <c r="F16" s="18"/>
       <c r="G16" s="17"/>
       <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15"/>
@@ -1350,6 +1385,7 @@
       <c r="F17" s="18"/>
       <c r="G17" s="17"/>
       <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15"/>
@@ -1360,6 +1396,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="17"/>
       <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15"/>
@@ -1370,6 +1407,7 @@
       <c r="F19" s="18"/>
       <c r="G19" s="17"/>
       <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15"/>
@@ -1380,6 +1418,7 @@
       <c r="F20" s="18"/>
       <c r="G20" s="17"/>
       <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15"/>
@@ -1390,6 +1429,7 @@
       <c r="F21" s="18"/>
       <c r="G21" s="17"/>
       <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15"/>
@@ -1400,6 +1440,7 @@
       <c r="F22" s="18"/>
       <c r="G22" s="17"/>
       <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15"/>
@@ -1410,6 +1451,7 @@
       <c r="F23" s="18"/>
       <c r="G23" s="17"/>
       <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15"/>
@@ -1420,6 +1462,7 @@
       <c r="F24" s="18"/>
       <c r="G24" s="17"/>
       <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15"/>
@@ -1430,6 +1473,7 @@
       <c r="F25" s="18"/>
       <c r="G25" s="17"/>
       <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15"/>
@@ -1440,6 +1484,7 @@
       <c r="F26" s="18"/>
       <c r="G26" s="17"/>
       <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15"/>
@@ -1450,6 +1495,7 @@
       <c r="F27" s="18"/>
       <c r="G27" s="17"/>
       <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15"/>
@@ -1460,6 +1506,7 @@
       <c r="F28" s="18"/>
       <c r="G28" s="17"/>
       <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15"/>
@@ -1470,6 +1517,7 @@
       <c r="F29" s="18"/>
       <c r="G29" s="17"/>
       <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15"/>
@@ -1480,6 +1528,7 @@
       <c r="F30" s="18"/>
       <c r="G30" s="17"/>
       <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15"/>
@@ -1490,6 +1539,7 @@
       <c r="F31" s="18"/>
       <c r="G31" s="17"/>
       <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15"/>
@@ -1500,6 +1550,7 @@
       <c r="F32" s="18"/>
       <c r="G32" s="17"/>
       <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15"/>
@@ -1510,6 +1561,7 @@
       <c r="F33" s="18"/>
       <c r="G33" s="17"/>
       <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15"/>
@@ -1520,6 +1572,7 @@
       <c r="F34" s="18"/>
       <c r="G34" s="17"/>
       <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15"/>
@@ -1530,6 +1583,7 @@
       <c r="F35" s="18"/>
       <c r="G35" s="17"/>
       <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15"/>
@@ -1540,6 +1594,7 @@
       <c r="F36" s="18"/>
       <c r="G36" s="17"/>
       <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15"/>
@@ -1550,6 +1605,7 @@
       <c r="F37" s="18"/>
       <c r="G37" s="17"/>
       <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15"/>
@@ -1560,6 +1616,7 @@
       <c r="F38" s="18"/>
       <c r="G38" s="17"/>
       <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15"/>
@@ -1570,6 +1627,7 @@
       <c r="F39" s="18"/>
       <c r="G39" s="17"/>
       <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15"/>
@@ -1580,6 +1638,7 @@
       <c r="F40" s="18"/>
       <c r="G40" s="17"/>
       <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15"/>
@@ -1590,6 +1649,7 @@
       <c r="F41" s="18"/>
       <c r="G41" s="17"/>
       <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15"/>
@@ -1600,6 +1660,7 @@
       <c r="F42" s="18"/>
       <c r="G42" s="17"/>
       <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15"/>
@@ -1610,6 +1671,7 @@
       <c r="F43" s="18"/>
       <c r="G43" s="17"/>
       <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15"/>
@@ -1620,6 +1682,7 @@
       <c r="F44" s="18"/>
       <c r="G44" s="17"/>
       <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15"/>
@@ -1630,6 +1693,7 @@
       <c r="F45" s="18"/>
       <c r="G45" s="17"/>
       <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15"/>
@@ -1640,6 +1704,7 @@
       <c r="F46" s="18"/>
       <c r="G46" s="17"/>
       <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15"/>
@@ -1650,6 +1715,7 @@
       <c r="F47" s="18"/>
       <c r="G47" s="17"/>
       <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15"/>
@@ -1660,6 +1726,7 @@
       <c r="F48" s="18"/>
       <c r="G48" s="17"/>
       <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15"/>
@@ -1670,6 +1737,7 @@
       <c r="F49" s="18"/>
       <c r="G49" s="17"/>
       <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15"/>
@@ -1680,6 +1748,7 @@
       <c r="F50" s="18"/>
       <c r="G50" s="17"/>
       <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15"/>
@@ -1690,6 +1759,7 @@
       <c r="F51" s="18"/>
       <c r="G51" s="17"/>
       <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15"/>
@@ -1700,6 +1770,7 @@
       <c r="F52" s="18"/>
       <c r="G52" s="17"/>
       <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15"/>
@@ -1710,6 +1781,7 @@
       <c r="F53" s="18"/>
       <c r="G53" s="17"/>
       <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15"/>
@@ -1720,6 +1792,7 @@
       <c r="F54" s="18"/>
       <c r="G54" s="17"/>
       <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15"/>
@@ -1730,6 +1803,7 @@
       <c r="F55" s="18"/>
       <c r="G55" s="17"/>
       <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15"/>
@@ -1740,6 +1814,7 @@
       <c r="F56" s="18"/>
       <c r="G56" s="17"/>
       <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15"/>
@@ -1750,6 +1825,7 @@
       <c r="F57" s="18"/>
       <c r="G57" s="17"/>
       <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15"/>
@@ -1760,6 +1836,7 @@
       <c r="F58" s="18"/>
       <c r="G58" s="17"/>
       <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15"/>
@@ -1770,6 +1847,7 @@
       <c r="F59" s="18"/>
       <c r="G59" s="17"/>
       <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15"/>
@@ -1780,6 +1858,7 @@
       <c r="F60" s="18"/>
       <c r="G60" s="17"/>
       <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15"/>
@@ -1790,6 +1869,7 @@
       <c r="F61" s="18"/>
       <c r="G61" s="17"/>
       <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15"/>
@@ -1800,6 +1880,7 @@
       <c r="F62" s="18"/>
       <c r="G62" s="17"/>
       <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15"/>
@@ -1810,6 +1891,7 @@
       <c r="F63" s="18"/>
       <c r="G63" s="17"/>
       <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15"/>
@@ -1820,6 +1902,7 @@
       <c r="F64" s="18"/>
       <c r="G64" s="17"/>
       <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15"/>
@@ -1830,6 +1913,7 @@
       <c r="F65" s="18"/>
       <c r="G65" s="17"/>
       <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15"/>
@@ -1840,6 +1924,7 @@
       <c r="F66" s="18"/>
       <c r="G66" s="17"/>
       <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15"/>
@@ -1850,6 +1935,7 @@
       <c r="F67" s="18"/>
       <c r="G67" s="17"/>
       <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15"/>
@@ -1860,6 +1946,7 @@
       <c r="F68" s="18"/>
       <c r="G68" s="17"/>
       <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15"/>
@@ -1870,6 +1957,7 @@
       <c r="F69" s="18"/>
       <c r="G69" s="17"/>
       <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15"/>
@@ -1880,6 +1968,7 @@
       <c r="F70" s="18"/>
       <c r="G70" s="17"/>
       <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="15"/>
@@ -1890,6 +1979,7 @@
       <c r="F71" s="18"/>
       <c r="G71" s="17"/>
       <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15"/>
@@ -1900,6 +1990,7 @@
       <c r="F72" s="18"/>
       <c r="G72" s="17"/>
       <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15"/>
@@ -1910,6 +2001,7 @@
       <c r="F73" s="18"/>
       <c r="G73" s="17"/>
       <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="15"/>
@@ -1920,6 +2012,7 @@
       <c r="F74" s="18"/>
       <c r="G74" s="17"/>
       <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15"/>
@@ -1930,6 +2023,7 @@
       <c r="F75" s="18"/>
       <c r="G75" s="17"/>
       <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="15"/>
@@ -1940,6 +2034,7 @@
       <c r="F76" s="18"/>
       <c r="G76" s="17"/>
       <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="15"/>
@@ -1950,6 +2045,7 @@
       <c r="F77" s="18"/>
       <c r="G77" s="17"/>
       <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="15"/>
@@ -1960,6 +2056,7 @@
       <c r="F78" s="18"/>
       <c r="G78" s="17"/>
       <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="15"/>
@@ -1970,6 +2067,7 @@
       <c r="F79" s="18"/>
       <c r="G79" s="17"/>
       <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15"/>
@@ -1980,6 +2078,7 @@
       <c r="F80" s="18"/>
       <c r="G80" s="17"/>
       <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="15"/>
@@ -1990,6 +2089,7 @@
       <c r="F81" s="18"/>
       <c r="G81" s="17"/>
       <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="15"/>
@@ -2000,6 +2100,7 @@
       <c r="F82" s="18"/>
       <c r="G82" s="17"/>
       <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="15"/>
@@ -2010,6 +2111,7 @@
       <c r="F83" s="18"/>
       <c r="G83" s="17"/>
       <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="15"/>
@@ -2020,6 +2122,7 @@
       <c r="F84" s="18"/>
       <c r="G84" s="17"/>
       <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="15"/>
@@ -2030,6 +2133,7 @@
       <c r="F85" s="18"/>
       <c r="G85" s="17"/>
       <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15"/>
@@ -2040,6 +2144,7 @@
       <c r="F86" s="18"/>
       <c r="G86" s="17"/>
       <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="15"/>
@@ -2050,6 +2155,7 @@
       <c r="F87" s="18"/>
       <c r="G87" s="17"/>
       <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="15"/>
@@ -2060,6 +2166,7 @@
       <c r="F88" s="18"/>
       <c r="G88" s="17"/>
       <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="15"/>
@@ -2070,6 +2177,7 @@
       <c r="F89" s="18"/>
       <c r="G89" s="17"/>
       <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15"/>
@@ -2080,6 +2188,7 @@
       <c r="F90" s="18"/>
       <c r="G90" s="17"/>
       <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="15"/>
@@ -2090,6 +2199,7 @@
       <c r="F91" s="18"/>
       <c r="G91" s="17"/>
       <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="15"/>
@@ -2100,6 +2210,7 @@
       <c r="F92" s="18"/>
       <c r="G92" s="17"/>
       <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="15"/>
@@ -2110,6 +2221,7 @@
       <c r="F93" s="18"/>
       <c r="G93" s="17"/>
       <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15"/>
@@ -2120,6 +2232,7 @@
       <c r="F94" s="18"/>
       <c r="G94" s="17"/>
       <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="15"/>
@@ -2130,6 +2243,7 @@
       <c r="F95" s="18"/>
       <c r="G95" s="17"/>
       <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="15"/>
@@ -2140,6 +2254,7 @@
       <c r="F96" s="18"/>
       <c r="G96" s="17"/>
       <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="15"/>
@@ -2150,6 +2265,7 @@
       <c r="F97" s="18"/>
       <c r="G97" s="17"/>
       <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="15"/>
@@ -2160,6 +2276,7 @@
       <c r="F98" s="18"/>
       <c r="G98" s="17"/>
       <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="15"/>
@@ -2170,6 +2287,7 @@
       <c r="F99" s="18"/>
       <c r="G99" s="17"/>
       <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="15"/>
@@ -2180,6 +2298,7 @@
       <c r="F100" s="18"/>
       <c r="G100" s="17"/>
       <c r="H100" s="15"/>
+      <c r="I100" s="15"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="15"/>
@@ -2190,6 +2309,7 @@
       <c r="F101" s="18"/>
       <c r="G101" s="17"/>
       <c r="H101" s="15"/>
+      <c r="I101" s="15"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15"/>
@@ -2200,6 +2320,7 @@
       <c r="F102" s="18"/>
       <c r="G102" s="17"/>
       <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15"/>
@@ -2210,6 +2331,7 @@
       <c r="F103" s="18"/>
       <c r="G103" s="17"/>
       <c r="H103" s="15"/>
+      <c r="I103" s="15"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="15"/>
@@ -2220,6 +2342,7 @@
       <c r="F104" s="18"/>
       <c r="G104" s="17"/>
       <c r="H104" s="15"/>
+      <c r="I104" s="15"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="15"/>
@@ -2230,6 +2353,7 @@
       <c r="F105" s="18"/>
       <c r="G105" s="17"/>
       <c r="H105" s="15"/>
+      <c r="I105" s="15"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="15"/>
@@ -2240,6 +2364,7 @@
       <c r="F106" s="18"/>
       <c r="G106" s="17"/>
       <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="15"/>
@@ -2250,6 +2375,7 @@
       <c r="F107" s="18"/>
       <c r="G107" s="17"/>
       <c r="H107" s="15"/>
+      <c r="I107" s="15"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="15"/>
@@ -2260,6 +2386,7 @@
       <c r="F108" s="18"/>
       <c r="G108" s="17"/>
       <c r="H108" s="15"/>
+      <c r="I108" s="15"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="15"/>
@@ -2270,6 +2397,7 @@
       <c r="F109" s="18"/>
       <c r="G109" s="17"/>
       <c r="H109" s="15"/>
+      <c r="I109" s="15"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="15"/>
@@ -2280,6 +2408,7 @@
       <c r="F110" s="18"/>
       <c r="G110" s="17"/>
       <c r="H110" s="15"/>
+      <c r="I110" s="15"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="15"/>
@@ -2290,6 +2419,7 @@
       <c r="F111" s="18"/>
       <c r="G111" s="17"/>
       <c r="H111" s="15"/>
+      <c r="I111" s="15"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15"/>
@@ -2300,6 +2430,7 @@
       <c r="F112" s="18"/>
       <c r="G112" s="17"/>
       <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="15"/>
@@ -2310,6 +2441,7 @@
       <c r="F113" s="18"/>
       <c r="G113" s="17"/>
       <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="15"/>
@@ -2320,6 +2452,7 @@
       <c r="F114" s="18"/>
       <c r="G114" s="17"/>
       <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="15"/>
@@ -2330,6 +2463,7 @@
       <c r="F115" s="18"/>
       <c r="G115" s="17"/>
       <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="15"/>
@@ -2340,6 +2474,7 @@
       <c r="F116" s="18"/>
       <c r="G116" s="17"/>
       <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="15"/>
@@ -2350,6 +2485,7 @@
       <c r="F117" s="18"/>
       <c r="G117" s="17"/>
       <c r="H117" s="15"/>
+      <c r="I117" s="15"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="15"/>
@@ -2360,6 +2496,7 @@
       <c r="F118" s="18"/>
       <c r="G118" s="17"/>
       <c r="H118" s="15"/>
+      <c r="I118" s="15"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="15"/>
@@ -2370,6 +2507,7 @@
       <c r="F119" s="18"/>
       <c r="G119" s="17"/>
       <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="15"/>
@@ -2380,6 +2518,7 @@
       <c r="F120" s="18"/>
       <c r="G120" s="17"/>
       <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="15"/>
@@ -2390,6 +2529,7 @@
       <c r="F121" s="18"/>
       <c r="G121" s="17"/>
       <c r="H121" s="15"/>
+      <c r="I121" s="15"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="15"/>
@@ -2400,6 +2540,7 @@
       <c r="F122" s="18"/>
       <c r="G122" s="17"/>
       <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="15"/>
@@ -2410,6 +2551,7 @@
       <c r="F123" s="18"/>
       <c r="G123" s="17"/>
       <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="15"/>
@@ -2420,6 +2562,7 @@
       <c r="F124" s="18"/>
       <c r="G124" s="17"/>
       <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="15"/>
@@ -2430,6 +2573,7 @@
       <c r="F125" s="18"/>
       <c r="G125" s="17"/>
       <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="15"/>
@@ -2440,6 +2584,7 @@
       <c r="F126" s="18"/>
       <c r="G126" s="17"/>
       <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="15"/>
@@ -2450,6 +2595,7 @@
       <c r="F127" s="18"/>
       <c r="G127" s="17"/>
       <c r="H127" s="15"/>
+      <c r="I127" s="15"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="15"/>
@@ -2460,6 +2606,7 @@
       <c r="F128" s="18"/>
       <c r="G128" s="17"/>
       <c r="H128" s="15"/>
+      <c r="I128" s="15"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="15"/>
@@ -2470,6 +2617,7 @@
       <c r="F129" s="18"/>
       <c r="G129" s="17"/>
       <c r="H129" s="15"/>
+      <c r="I129" s="15"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="15"/>
@@ -2480,6 +2628,7 @@
       <c r="F130" s="18"/>
       <c r="G130" s="17"/>
       <c r="H130" s="15"/>
+      <c r="I130" s="15"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="15"/>
@@ -2490,6 +2639,7 @@
       <c r="F131" s="18"/>
       <c r="G131" s="17"/>
       <c r="H131" s="15"/>
+      <c r="I131" s="15"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="15"/>
@@ -2500,6 +2650,7 @@
       <c r="F132" s="18"/>
       <c r="G132" s="17"/>
       <c r="H132" s="15"/>
+      <c r="I132" s="15"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="15"/>
@@ -2510,6 +2661,7 @@
       <c r="F133" s="18"/>
       <c r="G133" s="17"/>
       <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="15"/>
@@ -2520,6 +2672,7 @@
       <c r="F134" s="18"/>
       <c r="G134" s="17"/>
       <c r="H134" s="15"/>
+      <c r="I134" s="15"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="15"/>
@@ -2530,6 +2683,7 @@
       <c r="F135" s="18"/>
       <c r="G135" s="17"/>
       <c r="H135" s="15"/>
+      <c r="I135" s="15"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="15"/>
@@ -2540,6 +2694,7 @@
       <c r="F136" s="18"/>
       <c r="G136" s="17"/>
       <c r="H136" s="15"/>
+      <c r="I136" s="15"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="15"/>
@@ -2550,6 +2705,7 @@
       <c r="F137" s="18"/>
       <c r="G137" s="17"/>
       <c r="H137" s="15"/>
+      <c r="I137" s="15"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="15"/>
@@ -2560,6 +2716,7 @@
       <c r="F138" s="18"/>
       <c r="G138" s="17"/>
       <c r="H138" s="15"/>
+      <c r="I138" s="15"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="15"/>
@@ -2570,6 +2727,7 @@
       <c r="F139" s="18"/>
       <c r="G139" s="17"/>
       <c r="H139" s="15"/>
+      <c r="I139" s="15"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="15"/>
@@ -2580,6 +2738,7 @@
       <c r="F140" s="18"/>
       <c r="G140" s="17"/>
       <c r="H140" s="15"/>
+      <c r="I140" s="15"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="15"/>
@@ -2590,6 +2749,7 @@
       <c r="F141" s="18"/>
       <c r="G141" s="17"/>
       <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="15"/>
@@ -2600,6 +2760,7 @@
       <c r="F142" s="18"/>
       <c r="G142" s="17"/>
       <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="15"/>
@@ -2610,6 +2771,7 @@
       <c r="F143" s="18"/>
       <c r="G143" s="17"/>
       <c r="H143" s="15"/>
+      <c r="I143" s="15"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="15"/>
@@ -2620,6 +2782,7 @@
       <c r="F144" s="18"/>
       <c r="G144" s="17"/>
       <c r="H144" s="15"/>
+      <c r="I144" s="15"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="15"/>
@@ -2630,6 +2793,7 @@
       <c r="F145" s="18"/>
       <c r="G145" s="17"/>
       <c r="H145" s="15"/>
+      <c r="I145" s="15"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="15"/>
@@ -2640,6 +2804,7 @@
       <c r="F146" s="18"/>
       <c r="G146" s="17"/>
       <c r="H146" s="15"/>
+      <c r="I146" s="15"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="15"/>
@@ -2650,6 +2815,7 @@
       <c r="F147" s="18"/>
       <c r="G147" s="17"/>
       <c r="H147" s="15"/>
+      <c r="I147" s="15"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="15"/>
@@ -2660,6 +2826,7 @@
       <c r="F148" s="18"/>
       <c r="G148" s="17"/>
       <c r="H148" s="15"/>
+      <c r="I148" s="15"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="15"/>
@@ -2670,6 +2837,7 @@
       <c r="F149" s="18"/>
       <c r="G149" s="17"/>
       <c r="H149" s="15"/>
+      <c r="I149" s="15"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="15"/>
@@ -2680,6 +2848,7 @@
       <c r="F150" s="18"/>
       <c r="G150" s="17"/>
       <c r="H150" s="15"/>
+      <c r="I150" s="15"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="15"/>
@@ -2690,6 +2859,7 @@
       <c r="F151" s="18"/>
       <c r="G151" s="17"/>
       <c r="H151" s="15"/>
+      <c r="I151" s="15"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="15"/>
@@ -2700,6 +2870,7 @@
       <c r="F152" s="18"/>
       <c r="G152" s="17"/>
       <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="15"/>
@@ -2710,6 +2881,7 @@
       <c r="F153" s="18"/>
       <c r="G153" s="17"/>
       <c r="H153" s="15"/>
+      <c r="I153" s="15"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="15"/>
@@ -2720,6 +2892,7 @@
       <c r="F154" s="18"/>
       <c r="G154" s="17"/>
       <c r="H154" s="15"/>
+      <c r="I154" s="15"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="15"/>
@@ -2730,6 +2903,7 @@
       <c r="F155" s="18"/>
       <c r="G155" s="17"/>
       <c r="H155" s="15"/>
+      <c r="I155" s="15"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="15"/>
@@ -2740,6 +2914,7 @@
       <c r="F156" s="18"/>
       <c r="G156" s="17"/>
       <c r="H156" s="15"/>
+      <c r="I156" s="15"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="15"/>
@@ -2750,6 +2925,7 @@
       <c r="F157" s="18"/>
       <c r="G157" s="17"/>
       <c r="H157" s="15"/>
+      <c r="I157" s="15"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="15"/>
@@ -2760,6 +2936,7 @@
       <c r="F158" s="18"/>
       <c r="G158" s="17"/>
       <c r="H158" s="15"/>
+      <c r="I158" s="15"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="15"/>
@@ -2770,6 +2947,7 @@
       <c r="F159" s="18"/>
       <c r="G159" s="17"/>
       <c r="H159" s="15"/>
+      <c r="I159" s="15"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="15"/>
@@ -2780,6 +2958,7 @@
       <c r="F160" s="18"/>
       <c r="G160" s="17"/>
       <c r="H160" s="15"/>
+      <c r="I160" s="15"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="15"/>
@@ -2790,6 +2969,7 @@
       <c r="F161" s="18"/>
       <c r="G161" s="17"/>
       <c r="H161" s="15"/>
+      <c r="I161" s="15"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="15"/>
@@ -2800,6 +2980,7 @@
       <c r="F162" s="18"/>
       <c r="G162" s="17"/>
       <c r="H162" s="15"/>
+      <c r="I162" s="15"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="15"/>
@@ -2810,6 +2991,7 @@
       <c r="F163" s="18"/>
       <c r="G163" s="17"/>
       <c r="H163" s="15"/>
+      <c r="I163" s="15"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="15"/>
@@ -2820,6 +3002,7 @@
       <c r="F164" s="18"/>
       <c r="G164" s="17"/>
       <c r="H164" s="15"/>
+      <c r="I164" s="15"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="15"/>
@@ -2830,6 +3013,7 @@
       <c r="F165" s="18"/>
       <c r="G165" s="17"/>
       <c r="H165" s="15"/>
+      <c r="I165" s="15"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="15"/>
@@ -2840,6 +3024,7 @@
       <c r="F166" s="18"/>
       <c r="G166" s="17"/>
       <c r="H166" s="15"/>
+      <c r="I166" s="15"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="15"/>
@@ -2850,6 +3035,7 @@
       <c r="F167" s="18"/>
       <c r="G167" s="17"/>
       <c r="H167" s="15"/>
+      <c r="I167" s="15"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="15"/>
@@ -2860,6 +3046,7 @@
       <c r="F168" s="18"/>
       <c r="G168" s="17"/>
       <c r="H168" s="15"/>
+      <c r="I168" s="15"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="15"/>
@@ -2870,6 +3057,7 @@
       <c r="F169" s="18"/>
       <c r="G169" s="17"/>
       <c r="H169" s="15"/>
+      <c r="I169" s="15"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="15"/>
@@ -2880,6 +3068,7 @@
       <c r="F170" s="18"/>
       <c r="G170" s="17"/>
       <c r="H170" s="15"/>
+      <c r="I170" s="15"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="15"/>
@@ -2890,6 +3079,7 @@
       <c r="F171" s="18"/>
       <c r="G171" s="17"/>
       <c r="H171" s="15"/>
+      <c r="I171" s="15"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="15"/>
@@ -2900,6 +3090,7 @@
       <c r="F172" s="18"/>
       <c r="G172" s="17"/>
       <c r="H172" s="15"/>
+      <c r="I172" s="15"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="15"/>
@@ -2910,6 +3101,7 @@
       <c r="F173" s="18"/>
       <c r="G173" s="17"/>
       <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="15"/>
@@ -2920,6 +3112,7 @@
       <c r="F174" s="18"/>
       <c r="G174" s="17"/>
       <c r="H174" s="15"/>
+      <c r="I174" s="15"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="15"/>
@@ -2930,6 +3123,7 @@
       <c r="F175" s="18"/>
       <c r="G175" s="17"/>
       <c r="H175" s="15"/>
+      <c r="I175" s="15"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="15"/>
@@ -2940,6 +3134,7 @@
       <c r="F176" s="18"/>
       <c r="G176" s="17"/>
       <c r="H176" s="15"/>
+      <c r="I176" s="15"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="15"/>
@@ -2950,6 +3145,7 @@
       <c r="F177" s="18"/>
       <c r="G177" s="17"/>
       <c r="H177" s="15"/>
+      <c r="I177" s="15"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="15"/>
@@ -2960,6 +3156,7 @@
       <c r="F178" s="18"/>
       <c r="G178" s="17"/>
       <c r="H178" s="15"/>
+      <c r="I178" s="15"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="15"/>
@@ -2970,6 +3167,7 @@
       <c r="F179" s="18"/>
       <c r="G179" s="17"/>
       <c r="H179" s="15"/>
+      <c r="I179" s="15"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="15"/>
@@ -2980,6 +3178,7 @@
       <c r="F180" s="18"/>
       <c r="G180" s="17"/>
       <c r="H180" s="15"/>
+      <c r="I180" s="15"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="15"/>
@@ -2990,6 +3189,7 @@
       <c r="F181" s="18"/>
       <c r="G181" s="17"/>
       <c r="H181" s="15"/>
+      <c r="I181" s="15"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="15"/>
@@ -3000,6 +3200,7 @@
       <c r="F182" s="18"/>
       <c r="G182" s="17"/>
       <c r="H182" s="15"/>
+      <c r="I182" s="15"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="15"/>
@@ -3010,6 +3211,7 @@
       <c r="F183" s="18"/>
       <c r="G183" s="17"/>
       <c r="H183" s="15"/>
+      <c r="I183" s="15"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="15"/>
@@ -3020,6 +3222,7 @@
       <c r="F184" s="18"/>
       <c r="G184" s="17"/>
       <c r="H184" s="15"/>
+      <c r="I184" s="15"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="15"/>
@@ -3030,6 +3233,7 @@
       <c r="F185" s="18"/>
       <c r="G185" s="17"/>
       <c r="H185" s="15"/>
+      <c r="I185" s="15"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="15"/>
@@ -3040,6 +3244,7 @@
       <c r="F186" s="18"/>
       <c r="G186" s="17"/>
       <c r="H186" s="15"/>
+      <c r="I186" s="15"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="15"/>
@@ -3050,6 +3255,7 @@
       <c r="F187" s="18"/>
       <c r="G187" s="17"/>
       <c r="H187" s="15"/>
+      <c r="I187" s="15"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="15"/>
@@ -3060,6 +3266,7 @@
       <c r="F188" s="18"/>
       <c r="G188" s="17"/>
       <c r="H188" s="15"/>
+      <c r="I188" s="15"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="15"/>
@@ -3070,6 +3277,7 @@
       <c r="F189" s="18"/>
       <c r="G189" s="17"/>
       <c r="H189" s="15"/>
+      <c r="I189" s="15"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="15"/>
@@ -3080,6 +3288,7 @@
       <c r="F190" s="18"/>
       <c r="G190" s="17"/>
       <c r="H190" s="15"/>
+      <c r="I190" s="15"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="15"/>
@@ -3090,6 +3299,7 @@
       <c r="F191" s="18"/>
       <c r="G191" s="17"/>
       <c r="H191" s="15"/>
+      <c r="I191" s="15"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="15"/>
@@ -3100,6 +3310,7 @@
       <c r="F192" s="18"/>
       <c r="G192" s="17"/>
       <c r="H192" s="15"/>
+      <c r="I192" s="15"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="15"/>
@@ -3110,6 +3321,7 @@
       <c r="F193" s="18"/>
       <c r="G193" s="17"/>
       <c r="H193" s="15"/>
+      <c r="I193" s="15"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="15"/>
@@ -3120,6 +3332,7 @@
       <c r="F194" s="18"/>
       <c r="G194" s="17"/>
       <c r="H194" s="15"/>
+      <c r="I194" s="15"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="15"/>
@@ -3130,6 +3343,7 @@
       <c r="F195" s="18"/>
       <c r="G195" s="17"/>
       <c r="H195" s="15"/>
+      <c r="I195" s="15"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="15"/>
@@ -3140,6 +3354,7 @@
       <c r="F196" s="18"/>
       <c r="G196" s="17"/>
       <c r="H196" s="15"/>
+      <c r="I196" s="15"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="15"/>
@@ -3150,6 +3365,7 @@
       <c r="F197" s="18"/>
       <c r="G197" s="17"/>
       <c r="H197" s="15"/>
+      <c r="I197" s="15"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="15"/>
@@ -3160,6 +3376,7 @@
       <c r="F198" s="18"/>
       <c r="G198" s="17"/>
       <c r="H198" s="15"/>
+      <c r="I198" s="15"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="15"/>
@@ -3170,6 +3387,7 @@
       <c r="F199" s="18"/>
       <c r="G199" s="17"/>
       <c r="H199" s="15"/>
+      <c r="I199" s="15"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="15"/>
@@ -3180,6 +3398,7 @@
       <c r="F200" s="18"/>
       <c r="G200" s="17"/>
       <c r="H200" s="15"/>
+      <c r="I200" s="15"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="15"/>
@@ -3190,6 +3409,7 @@
       <c r="F201" s="18"/>
       <c r="G201" s="17"/>
       <c r="H201" s="15"/>
+      <c r="I201" s="15"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="15"/>
@@ -3200,6 +3420,7 @@
       <c r="F202" s="18"/>
       <c r="G202" s="17"/>
       <c r="H202" s="15"/>
+      <c r="I202" s="15"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="15"/>
@@ -3210,6 +3431,7 @@
       <c r="F203" s="18"/>
       <c r="G203" s="17"/>
       <c r="H203" s="15"/>
+      <c r="I203" s="15"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="15"/>
@@ -3220,6 +3442,7 @@
       <c r="F204" s="18"/>
       <c r="G204" s="17"/>
       <c r="H204" s="15"/>
+      <c r="I204" s="15"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="15"/>
@@ -3230,6 +3453,7 @@
       <c r="F205" s="18"/>
       <c r="G205" s="17"/>
       <c r="H205" s="15"/>
+      <c r="I205" s="15"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="15"/>
@@ -3240,6 +3464,7 @@
       <c r="F206" s="18"/>
       <c r="G206" s="17"/>
       <c r="H206" s="15"/>
+      <c r="I206" s="15"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="15"/>
@@ -3250,6 +3475,7 @@
       <c r="F207" s="18"/>
       <c r="G207" s="17"/>
       <c r="H207" s="15"/>
+      <c r="I207" s="15"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="15"/>
@@ -3260,6 +3486,7 @@
       <c r="F208" s="18"/>
       <c r="G208" s="17"/>
       <c r="H208" s="15"/>
+      <c r="I208" s="15"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="15"/>
@@ -3270,6 +3497,7 @@
       <c r="F209" s="18"/>
       <c r="G209" s="17"/>
       <c r="H209" s="15"/>
+      <c r="I209" s="15"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="15"/>
@@ -3280,6 +3508,7 @@
       <c r="F210" s="18"/>
       <c r="G210" s="17"/>
       <c r="H210" s="15"/>
+      <c r="I210" s="15"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="15"/>
@@ -3290,6 +3519,7 @@
       <c r="F211" s="18"/>
       <c r="G211" s="17"/>
       <c r="H211" s="15"/>
+      <c r="I211" s="15"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="15"/>
@@ -3300,6 +3530,7 @@
       <c r="F212" s="18"/>
       <c r="G212" s="17"/>
       <c r="H212" s="15"/>
+      <c r="I212" s="15"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="15"/>
@@ -3310,6 +3541,7 @@
       <c r="F213" s="18"/>
       <c r="G213" s="17"/>
       <c r="H213" s="15"/>
+      <c r="I213" s="15"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="15"/>
@@ -3320,6 +3552,7 @@
       <c r="F214" s="18"/>
       <c r="G214" s="17"/>
       <c r="H214" s="15"/>
+      <c r="I214" s="15"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="15"/>
@@ -3330,6 +3563,7 @@
       <c r="F215" s="18"/>
       <c r="G215" s="17"/>
       <c r="H215" s="15"/>
+      <c r="I215" s="15"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="15"/>
@@ -3340,6 +3574,7 @@
       <c r="F216" s="18"/>
       <c r="G216" s="17"/>
       <c r="H216" s="15"/>
+      <c r="I216" s="15"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="15"/>
@@ -3350,6 +3585,7 @@
       <c r="F217" s="18"/>
       <c r="G217" s="17"/>
       <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="15"/>
@@ -3360,6 +3596,7 @@
       <c r="F218" s="18"/>
       <c r="G218" s="17"/>
       <c r="H218" s="15"/>
+      <c r="I218" s="15"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="15"/>
@@ -3370,6 +3607,7 @@
       <c r="F219" s="18"/>
       <c r="G219" s="17"/>
       <c r="H219" s="15"/>
+      <c r="I219" s="15"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="15"/>
@@ -3380,6 +3618,7 @@
       <c r="F220" s="18"/>
       <c r="G220" s="17"/>
       <c r="H220" s="15"/>
+      <c r="I220" s="15"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="15"/>
@@ -3390,6 +3629,7 @@
       <c r="F221" s="18"/>
       <c r="G221" s="17"/>
       <c r="H221" s="15"/>
+      <c r="I221" s="15"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="15"/>
@@ -3400,6 +3640,7 @@
       <c r="F222" s="18"/>
       <c r="G222" s="17"/>
       <c r="H222" s="15"/>
+      <c r="I222" s="15"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="15"/>
@@ -3410,6 +3651,7 @@
       <c r="F223" s="18"/>
       <c r="G223" s="17"/>
       <c r="H223" s="15"/>
+      <c r="I223" s="15"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="15"/>
@@ -3420,6 +3662,7 @@
       <c r="F224" s="18"/>
       <c r="G224" s="17"/>
       <c r="H224" s="15"/>
+      <c r="I224" s="15"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="15"/>
@@ -3430,6 +3673,7 @@
       <c r="F225" s="18"/>
       <c r="G225" s="17"/>
       <c r="H225" s="15"/>
+      <c r="I225" s="15"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="15"/>
@@ -3440,6 +3684,7 @@
       <c r="F226" s="18"/>
       <c r="G226" s="17"/>
       <c r="H226" s="15"/>
+      <c r="I226" s="15"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="15"/>
@@ -3450,6 +3695,7 @@
       <c r="F227" s="18"/>
       <c r="G227" s="17"/>
       <c r="H227" s="15"/>
+      <c r="I227" s="15"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="15"/>
@@ -3460,6 +3706,7 @@
       <c r="F228" s="18"/>
       <c r="G228" s="17"/>
       <c r="H228" s="15"/>
+      <c r="I228" s="15"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="15"/>
@@ -3470,6 +3717,7 @@
       <c r="F229" s="18"/>
       <c r="G229" s="17"/>
       <c r="H229" s="15"/>
+      <c r="I229" s="15"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="15"/>
@@ -3480,6 +3728,7 @@
       <c r="F230" s="18"/>
       <c r="G230" s="17"/>
       <c r="H230" s="15"/>
+      <c r="I230" s="15"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="15"/>
@@ -3490,6 +3739,7 @@
       <c r="F231" s="18"/>
       <c r="G231" s="17"/>
       <c r="H231" s="15"/>
+      <c r="I231" s="15"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="15"/>
@@ -3500,6 +3750,7 @@
       <c r="F232" s="18"/>
       <c r="G232" s="17"/>
       <c r="H232" s="15"/>
+      <c r="I232" s="15"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="15"/>
@@ -3510,6 +3761,7 @@
       <c r="F233" s="18"/>
       <c r="G233" s="17"/>
       <c r="H233" s="15"/>
+      <c r="I233" s="15"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="15"/>
@@ -3520,6 +3772,7 @@
       <c r="F234" s="18"/>
       <c r="G234" s="17"/>
       <c r="H234" s="15"/>
+      <c r="I234" s="15"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="15"/>
@@ -3530,6 +3783,7 @@
       <c r="F235" s="18"/>
       <c r="G235" s="17"/>
       <c r="H235" s="15"/>
+      <c r="I235" s="15"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="15"/>
@@ -3540,6 +3794,7 @@
       <c r="F236" s="18"/>
       <c r="G236" s="17"/>
       <c r="H236" s="15"/>
+      <c r="I236" s="15"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="15"/>
@@ -3550,6 +3805,7 @@
       <c r="F237" s="18"/>
       <c r="G237" s="17"/>
       <c r="H237" s="15"/>
+      <c r="I237" s="15"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="15"/>
@@ -3560,6 +3816,7 @@
       <c r="F238" s="18"/>
       <c r="G238" s="17"/>
       <c r="H238" s="15"/>
+      <c r="I238" s="15"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="15"/>
@@ -3570,6 +3827,7 @@
       <c r="F239" s="18"/>
       <c r="G239" s="17"/>
       <c r="H239" s="15"/>
+      <c r="I239" s="15"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="15"/>
@@ -3580,6 +3838,7 @@
       <c r="F240" s="18"/>
       <c r="G240" s="17"/>
       <c r="H240" s="15"/>
+      <c r="I240" s="15"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="15"/>
@@ -3590,6 +3849,7 @@
       <c r="F241" s="18"/>
       <c r="G241" s="17"/>
       <c r="H241" s="15"/>
+      <c r="I241" s="15"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="15"/>
@@ -3600,6 +3860,7 @@
       <c r="F242" s="18"/>
       <c r="G242" s="17"/>
       <c r="H242" s="15"/>
+      <c r="I242" s="15"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="15"/>
@@ -3610,6 +3871,7 @@
       <c r="F243" s="18"/>
       <c r="G243" s="17"/>
       <c r="H243" s="15"/>
+      <c r="I243" s="15"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="15"/>
@@ -3620,6 +3882,7 @@
       <c r="F244" s="18"/>
       <c r="G244" s="17"/>
       <c r="H244" s="15"/>
+      <c r="I244" s="15"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="15"/>
@@ -3630,6 +3893,7 @@
       <c r="F245" s="18"/>
       <c r="G245" s="17"/>
       <c r="H245" s="15"/>
+      <c r="I245" s="15"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="15"/>
@@ -3640,6 +3904,7 @@
       <c r="F246" s="18"/>
       <c r="G246" s="17"/>
       <c r="H246" s="15"/>
+      <c r="I246" s="15"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="15"/>
@@ -3650,6 +3915,7 @@
       <c r="F247" s="18"/>
       <c r="G247" s="17"/>
       <c r="H247" s="15"/>
+      <c r="I247" s="15"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="15"/>
@@ -3660,6 +3926,7 @@
       <c r="F248" s="18"/>
       <c r="G248" s="17"/>
       <c r="H248" s="15"/>
+      <c r="I248" s="15"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="15"/>
@@ -3670,6 +3937,7 @@
       <c r="F249" s="18"/>
       <c r="G249" s="17"/>
       <c r="H249" s="15"/>
+      <c r="I249" s="15"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="15"/>
@@ -3680,6 +3948,7 @@
       <c r="F250" s="18"/>
       <c r="G250" s="17"/>
       <c r="H250" s="15"/>
+      <c r="I250" s="15"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="15"/>
@@ -3690,6 +3959,7 @@
       <c r="F251" s="18"/>
       <c r="G251" s="17"/>
       <c r="H251" s="15"/>
+      <c r="I251" s="15"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="15"/>
@@ -3700,6 +3970,7 @@
       <c r="F252" s="18"/>
       <c r="G252" s="17"/>
       <c r="H252" s="15"/>
+      <c r="I252" s="15"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="15"/>
@@ -3710,6 +3981,7 @@
       <c r="F253" s="18"/>
       <c r="G253" s="17"/>
       <c r="H253" s="15"/>
+      <c r="I253" s="15"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="15"/>
@@ -3720,6 +3992,7 @@
       <c r="F254" s="18"/>
       <c r="G254" s="17"/>
       <c r="H254" s="15"/>
+      <c r="I254" s="15"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="15"/>
@@ -3730,6 +4003,7 @@
       <c r="F255" s="18"/>
       <c r="G255" s="17"/>
       <c r="H255" s="15"/>
+      <c r="I255" s="15"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="15"/>
@@ -3740,6 +4014,7 @@
       <c r="F256" s="18"/>
       <c r="G256" s="17"/>
       <c r="H256" s="15"/>
+      <c r="I256" s="15"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="15"/>
@@ -3750,6 +4025,7 @@
       <c r="F257" s="18"/>
       <c r="G257" s="17"/>
       <c r="H257" s="15"/>
+      <c r="I257" s="15"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="15"/>
@@ -3760,6 +4036,7 @@
       <c r="F258" s="18"/>
       <c r="G258" s="17"/>
       <c r="H258" s="15"/>
+      <c r="I258" s="15"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="15"/>
@@ -3770,6 +4047,7 @@
       <c r="F259" s="18"/>
       <c r="G259" s="17"/>
       <c r="H259" s="15"/>
+      <c r="I259" s="15"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="15"/>
@@ -3780,6 +4058,7 @@
       <c r="F260" s="18"/>
       <c r="G260" s="17"/>
       <c r="H260" s="15"/>
+      <c r="I260" s="15"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="15"/>
@@ -3790,6 +4069,7 @@
       <c r="F261" s="18"/>
       <c r="G261" s="17"/>
       <c r="H261" s="15"/>
+      <c r="I261" s="15"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="15"/>
@@ -3800,6 +4080,7 @@
       <c r="F262" s="18"/>
       <c r="G262" s="17"/>
       <c r="H262" s="15"/>
+      <c r="I262" s="15"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="15"/>
@@ -3810,6 +4091,7 @@
       <c r="F263" s="18"/>
       <c r="G263" s="17"/>
       <c r="H263" s="15"/>
+      <c r="I263" s="15"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="15"/>
@@ -3820,6 +4102,7 @@
       <c r="F264" s="18"/>
       <c r="G264" s="17"/>
       <c r="H264" s="15"/>
+      <c r="I264" s="15"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="15"/>
@@ -3830,6 +4113,7 @@
       <c r="F265" s="18"/>
       <c r="G265" s="17"/>
       <c r="H265" s="15"/>
+      <c r="I265" s="15"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="15"/>
@@ -3840,6 +4124,7 @@
       <c r="F266" s="18"/>
       <c r="G266" s="17"/>
       <c r="H266" s="15"/>
+      <c r="I266" s="15"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="15"/>
@@ -3850,6 +4135,7 @@
       <c r="F267" s="18"/>
       <c r="G267" s="17"/>
       <c r="H267" s="15"/>
+      <c r="I267" s="15"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="15"/>
@@ -3860,6 +4146,7 @@
       <c r="F268" s="18"/>
       <c r="G268" s="17"/>
       <c r="H268" s="15"/>
+      <c r="I268" s="15"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="15"/>
@@ -3870,6 +4157,7 @@
       <c r="F269" s="18"/>
       <c r="G269" s="17"/>
       <c r="H269" s="15"/>
+      <c r="I269" s="15"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="15"/>
@@ -3880,6 +4168,7 @@
       <c r="F270" s="18"/>
       <c r="G270" s="17"/>
       <c r="H270" s="15"/>
+      <c r="I270" s="15"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="15"/>
@@ -3890,6 +4179,7 @@
       <c r="F271" s="18"/>
       <c r="G271" s="17"/>
       <c r="H271" s="15"/>
+      <c r="I271" s="15"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="15"/>
@@ -3900,6 +4190,7 @@
       <c r="F272" s="18"/>
       <c r="G272" s="17"/>
       <c r="H272" s="15"/>
+      <c r="I272" s="15"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="15"/>
@@ -3910,6 +4201,7 @@
       <c r="F273" s="18"/>
       <c r="G273" s="17"/>
       <c r="H273" s="15"/>
+      <c r="I273" s="15"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="15"/>
@@ -3920,6 +4212,7 @@
       <c r="F274" s="18"/>
       <c r="G274" s="17"/>
       <c r="H274" s="15"/>
+      <c r="I274" s="15"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="15"/>
@@ -3930,6 +4223,7 @@
       <c r="F275" s="18"/>
       <c r="G275" s="17"/>
       <c r="H275" s="15"/>
+      <c r="I275" s="15"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="15"/>
@@ -3940,6 +4234,7 @@
       <c r="F276" s="18"/>
       <c r="G276" s="17"/>
       <c r="H276" s="15"/>
+      <c r="I276" s="15"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="15"/>
@@ -3950,6 +4245,7 @@
       <c r="F277" s="18"/>
       <c r="G277" s="17"/>
       <c r="H277" s="15"/>
+      <c r="I277" s="15"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="15"/>
@@ -3960,6 +4256,7 @@
       <c r="F278" s="18"/>
       <c r="G278" s="17"/>
       <c r="H278" s="15"/>
+      <c r="I278" s="15"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="15"/>
@@ -3970,6 +4267,7 @@
       <c r="F279" s="18"/>
       <c r="G279" s="17"/>
       <c r="H279" s="15"/>
+      <c r="I279" s="15"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="15"/>
@@ -3980,6 +4278,7 @@
       <c r="F280" s="18"/>
       <c r="G280" s="17"/>
       <c r="H280" s="15"/>
+      <c r="I280" s="15"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="15"/>
@@ -3990,6 +4289,7 @@
       <c r="F281" s="18"/>
       <c r="G281" s="17"/>
       <c r="H281" s="15"/>
+      <c r="I281" s="15"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="15"/>
@@ -4000,6 +4300,7 @@
       <c r="F282" s="18"/>
       <c r="G282" s="17"/>
       <c r="H282" s="15"/>
+      <c r="I282" s="15"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="15"/>
@@ -4010,6 +4311,7 @@
       <c r="F283" s="18"/>
       <c r="G283" s="17"/>
       <c r="H283" s="15"/>
+      <c r="I283" s="15"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="15"/>
@@ -4020,6 +4322,7 @@
       <c r="F284" s="18"/>
       <c r="G284" s="17"/>
       <c r="H284" s="15"/>
+      <c r="I284" s="15"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="15"/>
@@ -4030,6 +4333,7 @@
       <c r="F285" s="18"/>
       <c r="G285" s="17"/>
       <c r="H285" s="15"/>
+      <c r="I285" s="15"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="15"/>
@@ -4040,6 +4344,7 @@
       <c r="F286" s="18"/>
       <c r="G286" s="17"/>
       <c r="H286" s="15"/>
+      <c r="I286" s="15"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="15"/>
@@ -4050,6 +4355,7 @@
       <c r="F287" s="18"/>
       <c r="G287" s="17"/>
       <c r="H287" s="15"/>
+      <c r="I287" s="15"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="15"/>
@@ -4060,6 +4366,7 @@
       <c r="F288" s="18"/>
       <c r="G288" s="17"/>
       <c r="H288" s="15"/>
+      <c r="I288" s="15"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="15"/>
@@ -4070,6 +4377,7 @@
       <c r="F289" s="18"/>
       <c r="G289" s="17"/>
       <c r="H289" s="15"/>
+      <c r="I289" s="15"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="15"/>
@@ -4080,6 +4388,7 @@
       <c r="F290" s="18"/>
       <c r="G290" s="17"/>
       <c r="H290" s="15"/>
+      <c r="I290" s="15"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="15"/>
@@ -4090,6 +4399,7 @@
       <c r="F291" s="18"/>
       <c r="G291" s="17"/>
       <c r="H291" s="15"/>
+      <c r="I291" s="15"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="15"/>
@@ -4100,6 +4410,7 @@
       <c r="F292" s="18"/>
       <c r="G292" s="17"/>
       <c r="H292" s="15"/>
+      <c r="I292" s="15"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="15"/>
@@ -4110,6 +4421,7 @@
       <c r="F293" s="18"/>
       <c r="G293" s="17"/>
       <c r="H293" s="15"/>
+      <c r="I293" s="15"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="15"/>
@@ -4120,6 +4432,7 @@
       <c r="F294" s="18"/>
       <c r="G294" s="17"/>
       <c r="H294" s="15"/>
+      <c r="I294" s="15"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="15"/>
@@ -4130,6 +4443,7 @@
       <c r="F295" s="18"/>
       <c r="G295" s="17"/>
       <c r="H295" s="15"/>
+      <c r="I295" s="15"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="15"/>
@@ -4140,6 +4454,7 @@
       <c r="F296" s="18"/>
       <c r="G296" s="17"/>
       <c r="H296" s="15"/>
+      <c r="I296" s="15"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="15"/>
@@ -4150,6 +4465,7 @@
       <c r="F297" s="18"/>
       <c r="G297" s="17"/>
       <c r="H297" s="15"/>
+      <c r="I297" s="15"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="15"/>
@@ -4160,6 +4476,7 @@
       <c r="F298" s="18"/>
       <c r="G298" s="17"/>
       <c r="H298" s="15"/>
+      <c r="I298" s="15"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="15"/>
@@ -4170,6 +4487,7 @@
       <c r="F299" s="18"/>
       <c r="G299" s="17"/>
       <c r="H299" s="15"/>
+      <c r="I299" s="15"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="15"/>
@@ -4180,6 +4498,7 @@
       <c r="F300" s="18"/>
       <c r="G300" s="17"/>
       <c r="H300" s="15"/>
+      <c r="I300" s="15"/>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="15"/>
@@ -4190,6 +4509,7 @@
       <c r="F301" s="18"/>
       <c r="G301" s="17"/>
       <c r="H301" s="15"/>
+      <c r="I301" s="15"/>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="15"/>
@@ -4200,6 +4520,7 @@
       <c r="F302" s="18"/>
       <c r="G302" s="17"/>
       <c r="H302" s="15"/>
+      <c r="I302" s="15"/>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="15"/>
@@ -4210,6 +4531,7 @@
       <c r="F303" s="18"/>
       <c r="G303" s="17"/>
       <c r="H303" s="15"/>
+      <c r="I303" s="15"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="15"/>
@@ -4220,6 +4542,7 @@
       <c r="F304" s="18"/>
       <c r="G304" s="17"/>
       <c r="H304" s="15"/>
+      <c r="I304" s="15"/>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="15"/>
@@ -4230,6 +4553,7 @@
       <c r="F305" s="18"/>
       <c r="G305" s="17"/>
       <c r="H305" s="15"/>
+      <c r="I305" s="15"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="15"/>
@@ -4240,6 +4564,7 @@
       <c r="F306" s="18"/>
       <c r="G306" s="17"/>
       <c r="H306" s="15"/>
+      <c r="I306" s="15"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="15"/>
@@ -4250,6 +4575,7 @@
       <c r="F307" s="18"/>
       <c r="G307" s="17"/>
       <c r="H307" s="15"/>
+      <c r="I307" s="15"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="15"/>
@@ -4260,6 +4586,7 @@
       <c r="F308" s="18"/>
       <c r="G308" s="17"/>
       <c r="H308" s="15"/>
+      <c r="I308" s="15"/>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="15"/>
@@ -4270,6 +4597,7 @@
       <c r="F309" s="18"/>
       <c r="G309" s="17"/>
       <c r="H309" s="15"/>
+      <c r="I309" s="15"/>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="15"/>
@@ -4280,6 +4608,7 @@
       <c r="F310" s="18"/>
       <c r="G310" s="17"/>
       <c r="H310" s="15"/>
+      <c r="I310" s="15"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="15"/>
@@ -4290,6 +4619,7 @@
       <c r="F311" s="18"/>
       <c r="G311" s="17"/>
       <c r="H311" s="15"/>
+      <c r="I311" s="15"/>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="15"/>
@@ -4300,6 +4630,7 @@
       <c r="F312" s="18"/>
       <c r="G312" s="17"/>
       <c r="H312" s="15"/>
+      <c r="I312" s="15"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="15"/>
@@ -4310,6 +4641,7 @@
       <c r="F313" s="18"/>
       <c r="G313" s="17"/>
       <c r="H313" s="15"/>
+      <c r="I313" s="15"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="15"/>
@@ -4320,6 +4652,7 @@
       <c r="F314" s="18"/>
       <c r="G314" s="17"/>
       <c r="H314" s="15"/>
+      <c r="I314" s="15"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="15"/>
@@ -4330,6 +4663,7 @@
       <c r="F315" s="18"/>
       <c r="G315" s="17"/>
       <c r="H315" s="15"/>
+      <c r="I315" s="15"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="15"/>
@@ -4340,6 +4674,7 @@
       <c r="F316" s="18"/>
       <c r="G316" s="17"/>
       <c r="H316" s="15"/>
+      <c r="I316" s="15"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="15"/>
@@ -4350,6 +4685,7 @@
       <c r="F317" s="18"/>
       <c r="G317" s="17"/>
       <c r="H317" s="15"/>
+      <c r="I317" s="15"/>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="15"/>
@@ -4360,6 +4696,7 @@
       <c r="F318" s="18"/>
       <c r="G318" s="17"/>
       <c r="H318" s="15"/>
+      <c r="I318" s="15"/>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="15"/>
@@ -4370,6 +4707,7 @@
       <c r="F319" s="18"/>
       <c r="G319" s="17"/>
       <c r="H319" s="15"/>
+      <c r="I319" s="15"/>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="15"/>
@@ -4380,6 +4718,7 @@
       <c r="F320" s="18"/>
       <c r="G320" s="17"/>
       <c r="H320" s="15"/>
+      <c r="I320" s="15"/>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="15"/>
@@ -4390,6 +4729,7 @@
       <c r="F321" s="18"/>
       <c r="G321" s="17"/>
       <c r="H321" s="15"/>
+      <c r="I321" s="15"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="15"/>
@@ -4400,6 +4740,7 @@
       <c r="F322" s="18"/>
       <c r="G322" s="17"/>
       <c r="H322" s="15"/>
+      <c r="I322" s="15"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="15"/>
@@ -4410,6 +4751,7 @@
       <c r="F323" s="18"/>
       <c r="G323" s="17"/>
       <c r="H323" s="15"/>
+      <c r="I323" s="15"/>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="15"/>
@@ -4420,6 +4762,7 @@
       <c r="F324" s="18"/>
       <c r="G324" s="17"/>
       <c r="H324" s="15"/>
+      <c r="I324" s="15"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="15"/>
@@ -4430,6 +4773,7 @@
       <c r="F325" s="18"/>
       <c r="G325" s="17"/>
       <c r="H325" s="15"/>
+      <c r="I325" s="15"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="15"/>
@@ -4440,6 +4784,7 @@
       <c r="F326" s="18"/>
       <c r="G326" s="17"/>
       <c r="H326" s="15"/>
+      <c r="I326" s="15"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="15"/>
@@ -4450,6 +4795,7 @@
       <c r="F327" s="18"/>
       <c r="G327" s="17"/>
       <c r="H327" s="15"/>
+      <c r="I327" s="15"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="15"/>
@@ -4460,6 +4806,7 @@
       <c r="F328" s="18"/>
       <c r="G328" s="17"/>
       <c r="H328" s="15"/>
+      <c r="I328" s="15"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="15"/>
@@ -4470,6 +4817,7 @@
       <c r="F329" s="18"/>
       <c r="G329" s="17"/>
       <c r="H329" s="15"/>
+      <c r="I329" s="15"/>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="15"/>
@@ -4480,6 +4828,7 @@
       <c r="F330" s="18"/>
       <c r="G330" s="17"/>
       <c r="H330" s="15"/>
+      <c r="I330" s="15"/>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="15"/>
@@ -4490,6 +4839,7 @@
       <c r="F331" s="18"/>
       <c r="G331" s="17"/>
       <c r="H331" s="15"/>
+      <c r="I331" s="15"/>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="15"/>
@@ -4500,6 +4850,7 @@
       <c r="F332" s="18"/>
       <c r="G332" s="17"/>
       <c r="H332" s="15"/>
+      <c r="I332" s="15"/>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="15"/>
@@ -4510,6 +4861,7 @@
       <c r="F333" s="18"/>
       <c r="G333" s="17"/>
       <c r="H333" s="15"/>
+      <c r="I333" s="15"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="15"/>
@@ -4520,6 +4872,7 @@
       <c r="F334" s="18"/>
       <c r="G334" s="17"/>
       <c r="H334" s="15"/>
+      <c r="I334" s="15"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="15"/>
@@ -4530,6 +4883,7 @@
       <c r="F335" s="18"/>
       <c r="G335" s="17"/>
       <c r="H335" s="15"/>
+      <c r="I335" s="15"/>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="15"/>
@@ -4540,6 +4894,7 @@
       <c r="F336" s="18"/>
       <c r="G336" s="17"/>
       <c r="H336" s="15"/>
+      <c r="I336" s="15"/>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="15"/>
@@ -4550,6 +4905,7 @@
       <c r="F337" s="18"/>
       <c r="G337" s="17"/>
       <c r="H337" s="15"/>
+      <c r="I337" s="15"/>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="15"/>
@@ -4560,6 +4916,7 @@
       <c r="F338" s="18"/>
       <c r="G338" s="17"/>
       <c r="H338" s="15"/>
+      <c r="I338" s="15"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="15"/>
@@ -4570,6 +4927,7 @@
       <c r="F339" s="18"/>
       <c r="G339" s="17"/>
       <c r="H339" s="15"/>
+      <c r="I339" s="15"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="15"/>
@@ -4580,6 +4938,7 @@
       <c r="F340" s="18"/>
       <c r="G340" s="17"/>
       <c r="H340" s="15"/>
+      <c r="I340" s="15"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="15"/>
@@ -4590,6 +4949,7 @@
       <c r="F341" s="18"/>
       <c r="G341" s="17"/>
       <c r="H341" s="15"/>
+      <c r="I341" s="15"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="15"/>
@@ -4600,6 +4960,7 @@
       <c r="F342" s="18"/>
       <c r="G342" s="17"/>
       <c r="H342" s="15"/>
+      <c r="I342" s="15"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="15"/>
@@ -4610,6 +4971,7 @@
       <c r="F343" s="18"/>
       <c r="G343" s="17"/>
       <c r="H343" s="15"/>
+      <c r="I343" s="15"/>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="15"/>
@@ -4620,6 +4982,7 @@
       <c r="F344" s="18"/>
       <c r="G344" s="17"/>
       <c r="H344" s="15"/>
+      <c r="I344" s="15"/>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="15"/>
@@ -4630,6 +4993,7 @@
       <c r="F345" s="18"/>
       <c r="G345" s="17"/>
       <c r="H345" s="15"/>
+      <c r="I345" s="15"/>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="15"/>
@@ -4640,6 +5004,7 @@
       <c r="F346" s="18"/>
       <c r="G346" s="17"/>
       <c r="H346" s="15"/>
+      <c r="I346" s="15"/>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="15"/>
@@ -4650,6 +5015,7 @@
       <c r="F347" s="18"/>
       <c r="G347" s="17"/>
       <c r="H347" s="15"/>
+      <c r="I347" s="15"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="15"/>
@@ -4660,6 +5026,7 @@
       <c r="F348" s="18"/>
       <c r="G348" s="17"/>
       <c r="H348" s="15"/>
+      <c r="I348" s="15"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="15"/>
@@ -4670,6 +5037,7 @@
       <c r="F349" s="18"/>
       <c r="G349" s="17"/>
       <c r="H349" s="15"/>
+      <c r="I349" s="15"/>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="15"/>
@@ -4680,6 +5048,7 @@
       <c r="F350" s="18"/>
       <c r="G350" s="17"/>
       <c r="H350" s="15"/>
+      <c r="I350" s="15"/>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="15"/>
@@ -4690,6 +5059,7 @@
       <c r="F351" s="18"/>
       <c r="G351" s="17"/>
       <c r="H351" s="15"/>
+      <c r="I351" s="15"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="15"/>
@@ -4700,6 +5070,7 @@
       <c r="F352" s="18"/>
       <c r="G352" s="17"/>
       <c r="H352" s="15"/>
+      <c r="I352" s="15"/>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="15"/>
@@ -4710,6 +5081,7 @@
       <c r="F353" s="18"/>
       <c r="G353" s="17"/>
       <c r="H353" s="15"/>
+      <c r="I353" s="15"/>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="15"/>
@@ -4720,6 +5092,7 @@
       <c r="F354" s="18"/>
       <c r="G354" s="17"/>
       <c r="H354" s="15"/>
+      <c r="I354" s="15"/>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="15"/>
@@ -4730,6 +5103,7 @@
       <c r="F355" s="18"/>
       <c r="G355" s="17"/>
       <c r="H355" s="15"/>
+      <c r="I355" s="15"/>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="15"/>
@@ -4740,6 +5114,7 @@
       <c r="F356" s="18"/>
       <c r="G356" s="17"/>
       <c r="H356" s="15"/>
+      <c r="I356" s="15"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="15"/>
@@ -4750,6 +5125,7 @@
       <c r="F357" s="18"/>
       <c r="G357" s="17"/>
       <c r="H357" s="15"/>
+      <c r="I357" s="15"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="15"/>
@@ -4760,6 +5136,7 @@
       <c r="F358" s="18"/>
       <c r="G358" s="17"/>
       <c r="H358" s="15"/>
+      <c r="I358" s="15"/>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="15"/>
@@ -4770,6 +5147,7 @@
       <c r="F359" s="18"/>
       <c r="G359" s="17"/>
       <c r="H359" s="15"/>
+      <c r="I359" s="15"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="15"/>
@@ -4780,6 +5158,7 @@
       <c r="F360" s="18"/>
       <c r="G360" s="17"/>
       <c r="H360" s="15"/>
+      <c r="I360" s="15"/>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="15"/>
@@ -4790,6 +5169,7 @@
       <c r="F361" s="18"/>
       <c r="G361" s="17"/>
       <c r="H361" s="15"/>
+      <c r="I361" s="15"/>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="15"/>
@@ -4800,6 +5180,7 @@
       <c r="F362" s="18"/>
       <c r="G362" s="17"/>
       <c r="H362" s="15"/>
+      <c r="I362" s="15"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="15"/>
@@ -4810,6 +5191,7 @@
       <c r="F363" s="18"/>
       <c r="G363" s="17"/>
       <c r="H363" s="15"/>
+      <c r="I363" s="15"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="15"/>
@@ -4820,6 +5202,7 @@
       <c r="F364" s="18"/>
       <c r="G364" s="17"/>
       <c r="H364" s="15"/>
+      <c r="I364" s="15"/>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="15"/>
@@ -4830,6 +5213,7 @@
       <c r="F365" s="18"/>
       <c r="G365" s="17"/>
       <c r="H365" s="15"/>
+      <c r="I365" s="15"/>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="15"/>
@@ -4840,6 +5224,7 @@
       <c r="F366" s="18"/>
       <c r="G366" s="17"/>
       <c r="H366" s="15"/>
+      <c r="I366" s="15"/>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="15"/>
@@ -4850,6 +5235,7 @@
       <c r="F367" s="18"/>
       <c r="G367" s="17"/>
       <c r="H367" s="15"/>
+      <c r="I367" s="15"/>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="15"/>
@@ -4860,6 +5246,7 @@
       <c r="F368" s="18"/>
       <c r="G368" s="17"/>
       <c r="H368" s="15"/>
+      <c r="I368" s="15"/>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="15"/>
@@ -4870,6 +5257,7 @@
       <c r="F369" s="18"/>
       <c r="G369" s="17"/>
       <c r="H369" s="15"/>
+      <c r="I369" s="15"/>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="15"/>
@@ -4880,6 +5268,7 @@
       <c r="F370" s="18"/>
       <c r="G370" s="17"/>
       <c r="H370" s="15"/>
+      <c r="I370" s="15"/>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="15"/>
@@ -4890,6 +5279,7 @@
       <c r="F371" s="18"/>
       <c r="G371" s="17"/>
       <c r="H371" s="15"/>
+      <c r="I371" s="15"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="15"/>
@@ -4900,6 +5290,7 @@
       <c r="F372" s="18"/>
       <c r="G372" s="17"/>
       <c r="H372" s="15"/>
+      <c r="I372" s="15"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="15"/>
@@ -4910,6 +5301,7 @@
       <c r="F373" s="18"/>
       <c r="G373" s="17"/>
       <c r="H373" s="15"/>
+      <c r="I373" s="15"/>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="15"/>
@@ -4920,6 +5312,7 @@
       <c r="F374" s="18"/>
       <c r="G374" s="17"/>
       <c r="H374" s="15"/>
+      <c r="I374" s="15"/>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="15"/>
@@ -4930,6 +5323,7 @@
       <c r="F375" s="18"/>
       <c r="G375" s="17"/>
       <c r="H375" s="15"/>
+      <c r="I375" s="15"/>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="15"/>
@@ -4940,6 +5334,7 @@
       <c r="F376" s="18"/>
       <c r="G376" s="17"/>
       <c r="H376" s="15"/>
+      <c r="I376" s="15"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="15"/>
@@ -4950,6 +5345,7 @@
       <c r="F377" s="18"/>
       <c r="G377" s="17"/>
       <c r="H377" s="15"/>
+      <c r="I377" s="15"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="15"/>
@@ -4960,6 +5356,7 @@
       <c r="F378" s="18"/>
       <c r="G378" s="17"/>
       <c r="H378" s="15"/>
+      <c r="I378" s="15"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="15"/>
@@ -4970,6 +5367,7 @@
       <c r="F379" s="18"/>
       <c r="G379" s="17"/>
       <c r="H379" s="15"/>
+      <c r="I379" s="15"/>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="15"/>
@@ -4980,6 +5378,7 @@
       <c r="F380" s="18"/>
       <c r="G380" s="17"/>
       <c r="H380" s="15"/>
+      <c r="I380" s="15"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="15"/>
@@ -4990,6 +5389,7 @@
       <c r="F381" s="18"/>
       <c r="G381" s="17"/>
       <c r="H381" s="15"/>
+      <c r="I381" s="15"/>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="15"/>
@@ -5000,6 +5400,7 @@
       <c r="F382" s="18"/>
       <c r="G382" s="17"/>
       <c r="H382" s="15"/>
+      <c r="I382" s="15"/>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="15"/>
@@ -5010,6 +5411,7 @@
       <c r="F383" s="18"/>
       <c r="G383" s="17"/>
       <c r="H383" s="15"/>
+      <c r="I383" s="15"/>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="15"/>
@@ -5020,6 +5422,7 @@
       <c r="F384" s="18"/>
       <c r="G384" s="17"/>
       <c r="H384" s="15"/>
+      <c r="I384" s="15"/>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="15"/>
@@ -5030,6 +5433,7 @@
       <c r="F385" s="18"/>
       <c r="G385" s="17"/>
       <c r="H385" s="15"/>
+      <c r="I385" s="15"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="15"/>
@@ -5040,6 +5444,7 @@
       <c r="F386" s="18"/>
       <c r="G386" s="17"/>
       <c r="H386" s="15"/>
+      <c r="I386" s="15"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="15"/>
@@ -5050,6 +5455,7 @@
       <c r="F387" s="18"/>
       <c r="G387" s="17"/>
       <c r="H387" s="15"/>
+      <c r="I387" s="15"/>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="15"/>
@@ -5060,6 +5466,7 @@
       <c r="F388" s="18"/>
       <c r="G388" s="17"/>
       <c r="H388" s="15"/>
+      <c r="I388" s="15"/>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="15"/>
@@ -5070,6 +5477,7 @@
       <c r="F389" s="18"/>
       <c r="G389" s="17"/>
       <c r="H389" s="15"/>
+      <c r="I389" s="15"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="15"/>
@@ -5080,6 +5488,7 @@
       <c r="F390" s="18"/>
       <c r="G390" s="17"/>
       <c r="H390" s="15"/>
+      <c r="I390" s="15"/>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="15"/>
@@ -5090,6 +5499,7 @@
       <c r="F391" s="18"/>
       <c r="G391" s="17"/>
       <c r="H391" s="15"/>
+      <c r="I391" s="15"/>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="15"/>
@@ -5100,6 +5510,7 @@
       <c r="F392" s="18"/>
       <c r="G392" s="17"/>
       <c r="H392" s="15"/>
+      <c r="I392" s="15"/>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="15"/>
@@ -5110,6 +5521,7 @@
       <c r="F393" s="18"/>
       <c r="G393" s="17"/>
       <c r="H393" s="15"/>
+      <c r="I393" s="15"/>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="15"/>
@@ -5120,6 +5532,7 @@
       <c r="F394" s="18"/>
       <c r="G394" s="17"/>
       <c r="H394" s="15"/>
+      <c r="I394" s="15"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="15"/>
@@ -5130,6 +5543,7 @@
       <c r="F395" s="18"/>
       <c r="G395" s="17"/>
       <c r="H395" s="15"/>
+      <c r="I395" s="15"/>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="15"/>
@@ -5140,6 +5554,7 @@
       <c r="F396" s="18"/>
       <c r="G396" s="17"/>
       <c r="H396" s="15"/>
+      <c r="I396" s="15"/>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="15"/>
@@ -5150,6 +5565,7 @@
       <c r="F397" s="18"/>
       <c r="G397" s="17"/>
       <c r="H397" s="15"/>
+      <c r="I397" s="15"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="15"/>
@@ -5160,6 +5576,7 @@
       <c r="F398" s="18"/>
       <c r="G398" s="17"/>
       <c r="H398" s="15"/>
+      <c r="I398" s="15"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="15"/>
@@ -5170,6 +5587,7 @@
       <c r="F399" s="18"/>
       <c r="G399" s="17"/>
       <c r="H399" s="15"/>
+      <c r="I399" s="15"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="15"/>
@@ -5180,6 +5598,7 @@
       <c r="F400" s="18"/>
       <c r="G400" s="17"/>
       <c r="H400" s="15"/>
+      <c r="I400" s="15"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="15"/>
@@ -5190,6 +5609,7 @@
       <c r="F401" s="18"/>
       <c r="G401" s="17"/>
       <c r="H401" s="15"/>
+      <c r="I401" s="15"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="15"/>
@@ -5200,6 +5620,7 @@
       <c r="F402" s="18"/>
       <c r="G402" s="17"/>
       <c r="H402" s="15"/>
+      <c r="I402" s="15"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="15"/>
@@ -5210,6 +5631,7 @@
       <c r="F403" s="18"/>
       <c r="G403" s="17"/>
       <c r="H403" s="15"/>
+      <c r="I403" s="15"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="15"/>
@@ -5220,6 +5642,7 @@
       <c r="F404" s="18"/>
       <c r="G404" s="17"/>
       <c r="H404" s="15"/>
+      <c r="I404" s="15"/>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="15"/>
@@ -5230,6 +5653,7 @@
       <c r="F405" s="18"/>
       <c r="G405" s="17"/>
       <c r="H405" s="15"/>
+      <c r="I405" s="15"/>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="15"/>
@@ -5240,6 +5664,7 @@
       <c r="F406" s="18"/>
       <c r="G406" s="17"/>
       <c r="H406" s="15"/>
+      <c r="I406" s="15"/>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="15"/>
@@ -5250,6 +5675,7 @@
       <c r="F407" s="18"/>
       <c r="G407" s="17"/>
       <c r="H407" s="15"/>
+      <c r="I407" s="15"/>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="15"/>
@@ -5260,6 +5686,7 @@
       <c r="F408" s="18"/>
       <c r="G408" s="17"/>
       <c r="H408" s="15"/>
+      <c r="I408" s="15"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="15"/>
@@ -5270,6 +5697,7 @@
       <c r="F409" s="18"/>
       <c r="G409" s="17"/>
       <c r="H409" s="15"/>
+      <c r="I409" s="15"/>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="15"/>
@@ -5280,6 +5708,7 @@
       <c r="F410" s="18"/>
       <c r="G410" s="17"/>
       <c r="H410" s="15"/>
+      <c r="I410" s="15"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="15"/>
@@ -5290,6 +5719,7 @@
       <c r="F411" s="18"/>
       <c r="G411" s="17"/>
       <c r="H411" s="15"/>
+      <c r="I411" s="15"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="15"/>
@@ -5300,6 +5730,7 @@
       <c r="F412" s="18"/>
       <c r="G412" s="17"/>
       <c r="H412" s="15"/>
+      <c r="I412" s="15"/>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="15"/>
@@ -5310,6 +5741,7 @@
       <c r="F413" s="18"/>
       <c r="G413" s="17"/>
       <c r="H413" s="15"/>
+      <c r="I413" s="15"/>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="15"/>
@@ -5320,6 +5752,7 @@
       <c r="F414" s="18"/>
       <c r="G414" s="17"/>
       <c r="H414" s="15"/>
+      <c r="I414" s="15"/>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="15"/>
@@ -5330,6 +5763,7 @@
       <c r="F415" s="18"/>
       <c r="G415" s="17"/>
       <c r="H415" s="15"/>
+      <c r="I415" s="15"/>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="15"/>
@@ -5340,6 +5774,7 @@
       <c r="F416" s="18"/>
       <c r="G416" s="17"/>
       <c r="H416" s="15"/>
+      <c r="I416" s="15"/>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="15"/>
@@ -5350,6 +5785,7 @@
       <c r="F417" s="18"/>
       <c r="G417" s="17"/>
       <c r="H417" s="15"/>
+      <c r="I417" s="15"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="15"/>
@@ -5360,6 +5796,7 @@
       <c r="F418" s="18"/>
       <c r="G418" s="17"/>
       <c r="H418" s="15"/>
+      <c r="I418" s="15"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="15"/>
@@ -5370,6 +5807,7 @@
       <c r="F419" s="18"/>
       <c r="G419" s="17"/>
       <c r="H419" s="15"/>
+      <c r="I419" s="15"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="15"/>
@@ -5380,6 +5818,7 @@
       <c r="F420" s="18"/>
       <c r="G420" s="17"/>
       <c r="H420" s="15"/>
+      <c r="I420" s="15"/>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="15"/>
@@ -5390,6 +5829,7 @@
       <c r="F421" s="18"/>
       <c r="G421" s="17"/>
       <c r="H421" s="15"/>
+      <c r="I421" s="15"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="15"/>
@@ -5400,6 +5840,7 @@
       <c r="F422" s="18"/>
       <c r="G422" s="17"/>
       <c r="H422" s="15"/>
+      <c r="I422" s="15"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="15"/>
@@ -5410,6 +5851,7 @@
       <c r="F423" s="18"/>
       <c r="G423" s="17"/>
       <c r="H423" s="15"/>
+      <c r="I423" s="15"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="15"/>
@@ -5420,6 +5862,7 @@
       <c r="F424" s="18"/>
       <c r="G424" s="17"/>
       <c r="H424" s="15"/>
+      <c r="I424" s="15"/>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="15"/>
@@ -5430,6 +5873,7 @@
       <c r="F425" s="18"/>
       <c r="G425" s="17"/>
       <c r="H425" s="15"/>
+      <c r="I425" s="15"/>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="15"/>
@@ -5440,6 +5884,7 @@
       <c r="F426" s="18"/>
       <c r="G426" s="17"/>
       <c r="H426" s="15"/>
+      <c r="I426" s="15"/>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="15"/>
@@ -5450,6 +5895,7 @@
       <c r="F427" s="18"/>
       <c r="G427" s="17"/>
       <c r="H427" s="15"/>
+      <c r="I427" s="15"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="15"/>
@@ -5460,6 +5906,7 @@
       <c r="F428" s="18"/>
       <c r="G428" s="17"/>
       <c r="H428" s="15"/>
+      <c r="I428" s="15"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="15"/>
@@ -5470,6 +5917,7 @@
       <c r="F429" s="18"/>
       <c r="G429" s="17"/>
       <c r="H429" s="15"/>
+      <c r="I429" s="15"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="15"/>
@@ -5480,6 +5928,7 @@
       <c r="F430" s="18"/>
       <c r="G430" s="17"/>
       <c r="H430" s="15"/>
+      <c r="I430" s="15"/>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="15"/>
@@ -5490,6 +5939,7 @@
       <c r="F431" s="18"/>
       <c r="G431" s="17"/>
       <c r="H431" s="15"/>
+      <c r="I431" s="15"/>
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="15"/>
@@ -5500,6 +5950,7 @@
       <c r="F432" s="18"/>
       <c r="G432" s="17"/>
       <c r="H432" s="15"/>
+      <c r="I432" s="15"/>
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="15"/>
@@ -5510,6 +5961,7 @@
       <c r="F433" s="18"/>
       <c r="G433" s="17"/>
       <c r="H433" s="15"/>
+      <c r="I433" s="15"/>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="15"/>
@@ -5520,6 +5972,7 @@
       <c r="F434" s="18"/>
       <c r="G434" s="17"/>
       <c r="H434" s="15"/>
+      <c r="I434" s="15"/>
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="15"/>
@@ -5530,6 +5983,7 @@
       <c r="F435" s="18"/>
       <c r="G435" s="17"/>
       <c r="H435" s="15"/>
+      <c r="I435" s="15"/>
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="15"/>
@@ -5540,6 +5994,7 @@
       <c r="F436" s="18"/>
       <c r="G436" s="17"/>
       <c r="H436" s="15"/>
+      <c r="I436" s="15"/>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="15"/>
@@ -5550,6 +6005,7 @@
       <c r="F437" s="18"/>
       <c r="G437" s="17"/>
       <c r="H437" s="15"/>
+      <c r="I437" s="15"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="15"/>
@@ -5560,6 +6016,7 @@
       <c r="F438" s="18"/>
       <c r="G438" s="17"/>
       <c r="H438" s="15"/>
+      <c r="I438" s="15"/>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="15"/>
@@ -5570,6 +6027,7 @@
       <c r="F439" s="18"/>
       <c r="G439" s="17"/>
       <c r="H439" s="15"/>
+      <c r="I439" s="15"/>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="15"/>
@@ -5580,6 +6038,7 @@
       <c r="F440" s="18"/>
       <c r="G440" s="17"/>
       <c r="H440" s="15"/>
+      <c r="I440" s="15"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="15"/>
@@ -5590,6 +6049,7 @@
       <c r="F441" s="18"/>
       <c r="G441" s="17"/>
       <c r="H441" s="15"/>
+      <c r="I441" s="15"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="15"/>
@@ -5600,6 +6060,7 @@
       <c r="F442" s="18"/>
       <c r="G442" s="17"/>
       <c r="H442" s="15"/>
+      <c r="I442" s="15"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="15"/>
@@ -5610,6 +6071,7 @@
       <c r="F443" s="18"/>
       <c r="G443" s="17"/>
       <c r="H443" s="15"/>
+      <c r="I443" s="15"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="15"/>
@@ -5620,6 +6082,7 @@
       <c r="F444" s="18"/>
       <c r="G444" s="17"/>
       <c r="H444" s="15"/>
+      <c r="I444" s="15"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="15"/>
@@ -5630,6 +6093,7 @@
       <c r="F445" s="18"/>
       <c r="G445" s="17"/>
       <c r="H445" s="15"/>
+      <c r="I445" s="15"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="15"/>
@@ -5640,6 +6104,7 @@
       <c r="F446" s="18"/>
       <c r="G446" s="17"/>
       <c r="H446" s="15"/>
+      <c r="I446" s="15"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="15"/>
@@ -5650,6 +6115,7 @@
       <c r="F447" s="18"/>
       <c r="G447" s="17"/>
       <c r="H447" s="15"/>
+      <c r="I447" s="15"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="15"/>
@@ -5660,6 +6126,7 @@
       <c r="F448" s="18"/>
       <c r="G448" s="17"/>
       <c r="H448" s="15"/>
+      <c r="I448" s="15"/>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="15"/>
@@ -5670,6 +6137,7 @@
       <c r="F449" s="18"/>
       <c r="G449" s="17"/>
       <c r="H449" s="15"/>
+      <c r="I449" s="15"/>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="15"/>
@@ -5680,6 +6148,7 @@
       <c r="F450" s="18"/>
       <c r="G450" s="17"/>
       <c r="H450" s="15"/>
+      <c r="I450" s="15"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="15"/>
@@ -5690,6 +6159,7 @@
       <c r="F451" s="18"/>
       <c r="G451" s="17"/>
       <c r="H451" s="15"/>
+      <c r="I451" s="15"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="15"/>
@@ -5700,6 +6170,7 @@
       <c r="F452" s="18"/>
       <c r="G452" s="17"/>
       <c r="H452" s="15"/>
+      <c r="I452" s="15"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="15"/>
@@ -5710,6 +6181,7 @@
       <c r="F453" s="18"/>
       <c r="G453" s="17"/>
       <c r="H453" s="15"/>
+      <c r="I453" s="15"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="15"/>
@@ -5720,6 +6192,7 @@
       <c r="F454" s="18"/>
       <c r="G454" s="17"/>
       <c r="H454" s="15"/>
+      <c r="I454" s="15"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="15"/>
@@ -5730,6 +6203,7 @@
       <c r="F455" s="18"/>
       <c r="G455" s="17"/>
       <c r="H455" s="15"/>
+      <c r="I455" s="15"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="15"/>
@@ -5740,6 +6214,7 @@
       <c r="F456" s="18"/>
       <c r="G456" s="17"/>
       <c r="H456" s="15"/>
+      <c r="I456" s="15"/>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="15"/>
@@ -5750,6 +6225,7 @@
       <c r="F457" s="18"/>
       <c r="G457" s="17"/>
       <c r="H457" s="15"/>
+      <c r="I457" s="15"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="15"/>
@@ -5760,6 +6236,7 @@
       <c r="F458" s="18"/>
       <c r="G458" s="17"/>
       <c r="H458" s="15"/>
+      <c r="I458" s="15"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="15"/>
@@ -5770,6 +6247,7 @@
       <c r="F459" s="18"/>
       <c r="G459" s="17"/>
       <c r="H459" s="15"/>
+      <c r="I459" s="15"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="15"/>
@@ -5780,6 +6258,7 @@
       <c r="F460" s="18"/>
       <c r="G460" s="17"/>
       <c r="H460" s="15"/>
+      <c r="I460" s="15"/>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="15"/>
@@ -5790,6 +6269,7 @@
       <c r="F461" s="18"/>
       <c r="G461" s="17"/>
       <c r="H461" s="15"/>
+      <c r="I461" s="15"/>
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="15"/>
@@ -5800,6 +6280,7 @@
       <c r="F462" s="18"/>
       <c r="G462" s="17"/>
       <c r="H462" s="15"/>
+      <c r="I462" s="15"/>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="15"/>
@@ -5810,6 +6291,7 @@
       <c r="F463" s="18"/>
       <c r="G463" s="17"/>
       <c r="H463" s="15"/>
+      <c r="I463" s="15"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="15"/>
@@ -5820,6 +6302,7 @@
       <c r="F464" s="18"/>
       <c r="G464" s="17"/>
       <c r="H464" s="15"/>
+      <c r="I464" s="15"/>
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="15"/>
@@ -5830,6 +6313,7 @@
       <c r="F465" s="18"/>
       <c r="G465" s="17"/>
       <c r="H465" s="15"/>
+      <c r="I465" s="15"/>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="15"/>
@@ -5840,6 +6324,7 @@
       <c r="F466" s="18"/>
       <c r="G466" s="17"/>
       <c r="H466" s="15"/>
+      <c r="I466" s="15"/>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="15"/>
@@ -5850,6 +6335,7 @@
       <c r="F467" s="18"/>
       <c r="G467" s="17"/>
       <c r="H467" s="15"/>
+      <c r="I467" s="15"/>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="15"/>
@@ -5860,6 +6346,7 @@
       <c r="F468" s="18"/>
       <c r="G468" s="17"/>
       <c r="H468" s="15"/>
+      <c r="I468" s="15"/>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="15"/>
@@ -5870,6 +6357,7 @@
       <c r="F469" s="18"/>
       <c r="G469" s="17"/>
       <c r="H469" s="15"/>
+      <c r="I469" s="15"/>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="15"/>
@@ -5880,6 +6368,7 @@
       <c r="F470" s="18"/>
       <c r="G470" s="17"/>
       <c r="H470" s="15"/>
+      <c r="I470" s="15"/>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="15"/>
@@ -5890,6 +6379,7 @@
       <c r="F471" s="18"/>
       <c r="G471" s="17"/>
       <c r="H471" s="15"/>
+      <c r="I471" s="15"/>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="15"/>
@@ -5900,6 +6390,7 @@
       <c r="F472" s="18"/>
       <c r="G472" s="17"/>
       <c r="H472" s="15"/>
+      <c r="I472" s="15"/>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="15"/>
@@ -5910,6 +6401,7 @@
       <c r="F473" s="18"/>
       <c r="G473" s="17"/>
       <c r="H473" s="15"/>
+      <c r="I473" s="15"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="15"/>
@@ -5920,6 +6412,7 @@
       <c r="F474" s="18"/>
       <c r="G474" s="17"/>
       <c r="H474" s="15"/>
+      <c r="I474" s="15"/>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="15"/>
@@ -5930,6 +6423,7 @@
       <c r="F475" s="18"/>
       <c r="G475" s="17"/>
       <c r="H475" s="15"/>
+      <c r="I475" s="15"/>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="15"/>
@@ -5940,6 +6434,7 @@
       <c r="F476" s="18"/>
       <c r="G476" s="17"/>
       <c r="H476" s="15"/>
+      <c r="I476" s="15"/>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="15"/>
@@ -5950,6 +6445,7 @@
       <c r="F477" s="18"/>
       <c r="G477" s="17"/>
       <c r="H477" s="15"/>
+      <c r="I477" s="15"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="15"/>
@@ -5960,6 +6456,7 @@
       <c r="F478" s="18"/>
       <c r="G478" s="17"/>
       <c r="H478" s="15"/>
+      <c r="I478" s="15"/>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="15"/>
@@ -5970,6 +6467,7 @@
       <c r="F479" s="18"/>
       <c r="G479" s="17"/>
       <c r="H479" s="15"/>
+      <c r="I479" s="15"/>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="15"/>
@@ -5980,6 +6478,7 @@
       <c r="F480" s="18"/>
       <c r="G480" s="17"/>
       <c r="H480" s="15"/>
+      <c r="I480" s="15"/>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="15"/>
@@ -5990,6 +6489,7 @@
       <c r="F481" s="18"/>
       <c r="G481" s="17"/>
       <c r="H481" s="15"/>
+      <c r="I481" s="15"/>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="15"/>
@@ -6000,6 +6500,7 @@
       <c r="F482" s="18"/>
       <c r="G482" s="17"/>
       <c r="H482" s="15"/>
+      <c r="I482" s="15"/>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="15"/>
@@ -6010,6 +6511,7 @@
       <c r="F483" s="18"/>
       <c r="G483" s="17"/>
       <c r="H483" s="15"/>
+      <c r="I483" s="15"/>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="15"/>
@@ -6020,6 +6522,7 @@
       <c r="F484" s="18"/>
       <c r="G484" s="17"/>
       <c r="H484" s="15"/>
+      <c r="I484" s="15"/>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="15"/>
@@ -6030,6 +6533,7 @@
       <c r="F485" s="18"/>
       <c r="G485" s="17"/>
       <c r="H485" s="15"/>
+      <c r="I485" s="15"/>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="15"/>
@@ -6040,6 +6544,7 @@
       <c r="F486" s="18"/>
       <c r="G486" s="17"/>
       <c r="H486" s="15"/>
+      <c r="I486" s="15"/>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="15"/>
@@ -6050,6 +6555,7 @@
       <c r="F487" s="18"/>
       <c r="G487" s="17"/>
       <c r="H487" s="15"/>
+      <c r="I487" s="15"/>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="15"/>
@@ -6060,6 +6566,7 @@
       <c r="F488" s="18"/>
       <c r="G488" s="17"/>
       <c r="H488" s="15"/>
+      <c r="I488" s="15"/>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="15"/>
@@ -6070,6 +6577,7 @@
       <c r="F489" s="18"/>
       <c r="G489" s="17"/>
       <c r="H489" s="15"/>
+      <c r="I489" s="15"/>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="15"/>
@@ -6080,6 +6588,7 @@
       <c r="F490" s="18"/>
       <c r="G490" s="17"/>
       <c r="H490" s="15"/>
+      <c r="I490" s="15"/>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="15"/>
@@ -6090,6 +6599,7 @@
       <c r="F491" s="18"/>
       <c r="G491" s="17"/>
       <c r="H491" s="15"/>
+      <c r="I491" s="15"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="15"/>
@@ -6100,6 +6610,7 @@
       <c r="F492" s="18"/>
       <c r="G492" s="17"/>
       <c r="H492" s="15"/>
+      <c r="I492" s="15"/>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="15"/>
@@ -6110,6 +6621,7 @@
       <c r="F493" s="18"/>
       <c r="G493" s="17"/>
       <c r="H493" s="15"/>
+      <c r="I493" s="15"/>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="15"/>
@@ -6120,6 +6632,7 @@
       <c r="F494" s="18"/>
       <c r="G494" s="17"/>
       <c r="H494" s="15"/>
+      <c r="I494" s="15"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="15"/>
@@ -6130,6 +6643,7 @@
       <c r="F495" s="18"/>
       <c r="G495" s="17"/>
       <c r="H495" s="15"/>
+      <c r="I495" s="15"/>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="15"/>
@@ -6140,6 +6654,7 @@
       <c r="F496" s="18"/>
       <c r="G496" s="17"/>
       <c r="H496" s="15"/>
+      <c r="I496" s="15"/>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="15"/>
@@ -6150,6 +6665,7 @@
       <c r="F497" s="18"/>
       <c r="G497" s="17"/>
       <c r="H497" s="15"/>
+      <c r="I497" s="15"/>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="15"/>
@@ -6160,6 +6676,7 @@
       <c r="F498" s="18"/>
       <c r="G498" s="17"/>
       <c r="H498" s="15"/>
+      <c r="I498" s="15"/>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="15"/>
@@ -6170,6 +6687,7 @@
       <c r="F499" s="18"/>
       <c r="G499" s="17"/>
       <c r="H499" s="15"/>
+      <c r="I499" s="15"/>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="15"/>
@@ -6180,6 +6698,7 @@
       <c r="F500" s="18"/>
       <c r="G500" s="17"/>
       <c r="H500" s="15"/>
+      <c r="I500" s="15"/>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="15"/>
@@ -6190,6 +6709,7 @@
       <c r="F501" s="18"/>
       <c r="G501" s="17"/>
       <c r="H501" s="15"/>
+      <c r="I501" s="15"/>
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="15"/>
@@ -6200,6 +6720,7 @@
       <c r="F502" s="18"/>
       <c r="G502" s="17"/>
       <c r="H502" s="15"/>
+      <c r="I502" s="15"/>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="15"/>
@@ -6210,6 +6731,7 @@
       <c r="F503" s="18"/>
       <c r="G503" s="17"/>
       <c r="H503" s="15"/>
+      <c r="I503" s="15"/>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="15"/>
@@ -6220,6 +6742,7 @@
       <c r="F504" s="18"/>
       <c r="G504" s="17"/>
       <c r="H504" s="15"/>
+      <c r="I504" s="15"/>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="15"/>
@@ -6230,6 +6753,7 @@
       <c r="F505" s="18"/>
       <c r="G505" s="17"/>
       <c r="H505" s="15"/>
+      <c r="I505" s="15"/>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="15"/>
@@ -6240,6 +6764,7 @@
       <c r="F506" s="18"/>
       <c r="G506" s="17"/>
       <c r="H506" s="15"/>
+      <c r="I506" s="15"/>
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="15"/>
@@ -6250,6 +6775,7 @@
       <c r="F507" s="18"/>
       <c r="G507" s="17"/>
       <c r="H507" s="15"/>
+      <c r="I507" s="15"/>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="15"/>
@@ -6260,6 +6786,7 @@
       <c r="F508" s="18"/>
       <c r="G508" s="17"/>
       <c r="H508" s="15"/>
+      <c r="I508" s="15"/>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="15"/>
@@ -6270,6 +6797,7 @@
       <c r="F509" s="18"/>
       <c r="G509" s="17"/>
       <c r="H509" s="15"/>
+      <c r="I509" s="15"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="15"/>
@@ -6280,6 +6808,7 @@
       <c r="F510" s="18"/>
       <c r="G510" s="17"/>
       <c r="H510" s="15"/>
+      <c r="I510" s="15"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="15"/>
@@ -6290,6 +6819,7 @@
       <c r="F511" s="18"/>
       <c r="G511" s="17"/>
       <c r="H511" s="15"/>
+      <c r="I511" s="15"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="15"/>
@@ -6300,6 +6830,7 @@
       <c r="F512" s="18"/>
       <c r="G512" s="17"/>
       <c r="H512" s="15"/>
+      <c r="I512" s="15"/>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="15"/>
@@ -6310,6 +6841,7 @@
       <c r="F513" s="18"/>
       <c r="G513" s="17"/>
       <c r="H513" s="15"/>
+      <c r="I513" s="15"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="15"/>
@@ -6320,6 +6852,7 @@
       <c r="F514" s="18"/>
       <c r="G514" s="17"/>
       <c r="H514" s="15"/>
+      <c r="I514" s="15"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="15"/>
@@ -6330,6 +6863,7 @@
       <c r="F515" s="18"/>
       <c r="G515" s="17"/>
       <c r="H515" s="15"/>
+      <c r="I515" s="15"/>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="15"/>
@@ -6340,6 +6874,7 @@
       <c r="F516" s="18"/>
       <c r="G516" s="17"/>
       <c r="H516" s="15"/>
+      <c r="I516" s="15"/>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="15"/>
@@ -6350,6 +6885,7 @@
       <c r="F517" s="18"/>
       <c r="G517" s="17"/>
       <c r="H517" s="15"/>
+      <c r="I517" s="15"/>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="15"/>
@@ -6360,6 +6896,7 @@
       <c r="F518" s="18"/>
       <c r="G518" s="17"/>
       <c r="H518" s="15"/>
+      <c r="I518" s="15"/>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="15"/>
@@ -6370,6 +6907,7 @@
       <c r="F519" s="18"/>
       <c r="G519" s="17"/>
       <c r="H519" s="15"/>
+      <c r="I519" s="15"/>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="15"/>
@@ -6380,6 +6918,7 @@
       <c r="F520" s="18"/>
       <c r="G520" s="17"/>
       <c r="H520" s="15"/>
+      <c r="I520" s="15"/>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="15"/>
@@ -6390,6 +6929,7 @@
       <c r="F521" s="18"/>
       <c r="G521" s="17"/>
       <c r="H521" s="15"/>
+      <c r="I521" s="15"/>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="15"/>
@@ -6400,6 +6940,7 @@
       <c r="F522" s="18"/>
       <c r="G522" s="17"/>
       <c r="H522" s="15"/>
+      <c r="I522" s="15"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="15"/>
@@ -6410,6 +6951,7 @@
       <c r="F523" s="18"/>
       <c r="G523" s="17"/>
       <c r="H523" s="15"/>
+      <c r="I523" s="15"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="15"/>
@@ -6420,6 +6962,7 @@
       <c r="F524" s="18"/>
       <c r="G524" s="17"/>
       <c r="H524" s="15"/>
+      <c r="I524" s="15"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="15"/>
@@ -6430,6 +6973,7 @@
       <c r="F525" s="18"/>
       <c r="G525" s="17"/>
       <c r="H525" s="15"/>
+      <c r="I525" s="15"/>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="15"/>
@@ -6440,6 +6984,7 @@
       <c r="F526" s="18"/>
       <c r="G526" s="17"/>
       <c r="H526" s="15"/>
+      <c r="I526" s="15"/>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="15"/>
@@ -6450,6 +6995,7 @@
       <c r="F527" s="18"/>
       <c r="G527" s="17"/>
       <c r="H527" s="15"/>
+      <c r="I527" s="15"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="15"/>
@@ -6460,6 +7006,7 @@
       <c r="F528" s="18"/>
       <c r="G528" s="17"/>
       <c r="H528" s="15"/>
+      <c r="I528" s="15"/>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="15"/>
@@ -6470,6 +7017,7 @@
       <c r="F529" s="18"/>
       <c r="G529" s="17"/>
       <c r="H529" s="15"/>
+      <c r="I529" s="15"/>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="15"/>
@@ -6480,6 +7028,7 @@
       <c r="F530" s="18"/>
       <c r="G530" s="17"/>
       <c r="H530" s="15"/>
+      <c r="I530" s="15"/>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="15"/>
@@ -6490,6 +7039,7 @@
       <c r="F531" s="18"/>
       <c r="G531" s="17"/>
       <c r="H531" s="15"/>
+      <c r="I531" s="15"/>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="15"/>
@@ -6500,6 +7050,7 @@
       <c r="F532" s="18"/>
       <c r="G532" s="17"/>
       <c r="H532" s="15"/>
+      <c r="I532" s="15"/>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="15"/>
@@ -6510,6 +7061,7 @@
       <c r="F533" s="18"/>
       <c r="G533" s="17"/>
       <c r="H533" s="15"/>
+      <c r="I533" s="15"/>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="15"/>
@@ -6520,6 +7072,7 @@
       <c r="F534" s="18"/>
       <c r="G534" s="17"/>
       <c r="H534" s="15"/>
+      <c r="I534" s="15"/>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="15"/>
@@ -6530,6 +7083,7 @@
       <c r="F535" s="18"/>
       <c r="G535" s="17"/>
       <c r="H535" s="15"/>
+      <c r="I535" s="15"/>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="15"/>
@@ -6540,6 +7094,7 @@
       <c r="F536" s="18"/>
       <c r="G536" s="17"/>
       <c r="H536" s="15"/>
+      <c r="I536" s="15"/>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="15"/>
@@ -6550,6 +7105,7 @@
       <c r="F537" s="18"/>
       <c r="G537" s="17"/>
       <c r="H537" s="15"/>
+      <c r="I537" s="15"/>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="15"/>
@@ -6560,6 +7116,7 @@
       <c r="F538" s="18"/>
       <c r="G538" s="17"/>
       <c r="H538" s="15"/>
+      <c r="I538" s="15"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="15"/>
@@ -6570,6 +7127,7 @@
       <c r="F539" s="18"/>
       <c r="G539" s="17"/>
       <c r="H539" s="15"/>
+      <c r="I539" s="15"/>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="15"/>
@@ -6580,6 +7138,7 @@
       <c r="F540" s="18"/>
       <c r="G540" s="17"/>
       <c r="H540" s="15"/>
+      <c r="I540" s="15"/>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="15"/>
@@ -6590,6 +7149,7 @@
       <c r="F541" s="18"/>
       <c r="G541" s="17"/>
       <c r="H541" s="15"/>
+      <c r="I541" s="15"/>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="15"/>
@@ -6600,6 +7160,7 @@
       <c r="F542" s="18"/>
       <c r="G542" s="17"/>
       <c r="H542" s="15"/>
+      <c r="I542" s="15"/>
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="15"/>
@@ -6610,6 +7171,7 @@
       <c r="F543" s="18"/>
       <c r="G543" s="17"/>
       <c r="H543" s="15"/>
+      <c r="I543" s="15"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="15"/>
@@ -6620,6 +7182,7 @@
       <c r="F544" s="18"/>
       <c r="G544" s="17"/>
       <c r="H544" s="15"/>
+      <c r="I544" s="15"/>
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="15"/>
@@ -6630,6 +7193,7 @@
       <c r="F545" s="18"/>
       <c r="G545" s="17"/>
       <c r="H545" s="15"/>
+      <c r="I545" s="15"/>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="15"/>
@@ -6640,6 +7204,7 @@
       <c r="F546" s="18"/>
       <c r="G546" s="17"/>
       <c r="H546" s="15"/>
+      <c r="I546" s="15"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="15"/>
@@ -6650,6 +7215,7 @@
       <c r="F547" s="18"/>
       <c r="G547" s="17"/>
       <c r="H547" s="15"/>
+      <c r="I547" s="15"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="15"/>
@@ -6660,6 +7226,7 @@
       <c r="F548" s="18"/>
       <c r="G548" s="17"/>
       <c r="H548" s="15"/>
+      <c r="I548" s="15"/>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="15"/>
@@ -6670,6 +7237,7 @@
       <c r="F549" s="18"/>
       <c r="G549" s="17"/>
       <c r="H549" s="15"/>
+      <c r="I549" s="15"/>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="15"/>
@@ -6680,6 +7248,7 @@
       <c r="F550" s="18"/>
       <c r="G550" s="17"/>
       <c r="H550" s="15"/>
+      <c r="I550" s="15"/>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="15"/>
@@ -6690,6 +7259,7 @@
       <c r="F551" s="18"/>
       <c r="G551" s="17"/>
       <c r="H551" s="15"/>
+      <c r="I551" s="15"/>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="15"/>
@@ -6700,6 +7270,7 @@
       <c r="F552" s="18"/>
       <c r="G552" s="17"/>
       <c r="H552" s="15"/>
+      <c r="I552" s="15"/>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="15"/>
@@ -6710,6 +7281,7 @@
       <c r="F553" s="18"/>
       <c r="G553" s="17"/>
       <c r="H553" s="15"/>
+      <c r="I553" s="15"/>
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="15"/>
@@ -6720,6 +7292,7 @@
       <c r="F554" s="18"/>
       <c r="G554" s="17"/>
       <c r="H554" s="15"/>
+      <c r="I554" s="15"/>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="15"/>
@@ -6730,6 +7303,7 @@
       <c r="F555" s="18"/>
       <c r="G555" s="17"/>
       <c r="H555" s="15"/>
+      <c r="I555" s="15"/>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="15"/>
@@ -6740,6 +7314,7 @@
       <c r="F556" s="18"/>
       <c r="G556" s="17"/>
       <c r="H556" s="15"/>
+      <c r="I556" s="15"/>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="15"/>
@@ -6750,6 +7325,7 @@
       <c r="F557" s="18"/>
       <c r="G557" s="17"/>
       <c r="H557" s="15"/>
+      <c r="I557" s="15"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="15"/>
@@ -6760,6 +7336,7 @@
       <c r="F558" s="18"/>
       <c r="G558" s="17"/>
       <c r="H558" s="15"/>
+      <c r="I558" s="15"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="15"/>
@@ -6770,6 +7347,7 @@
       <c r="F559" s="18"/>
       <c r="G559" s="17"/>
       <c r="H559" s="15"/>
+      <c r="I559" s="15"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="15"/>
@@ -6780,6 +7358,7 @@
       <c r="F560" s="18"/>
       <c r="G560" s="17"/>
       <c r="H560" s="15"/>
+      <c r="I560" s="15"/>
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="15"/>
@@ -6790,6 +7369,7 @@
       <c r="F561" s="18"/>
       <c r="G561" s="17"/>
       <c r="H561" s="15"/>
+      <c r="I561" s="15"/>
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="15"/>
@@ -6800,6 +7380,7 @@
       <c r="F562" s="18"/>
       <c r="G562" s="17"/>
       <c r="H562" s="15"/>
+      <c r="I562" s="15"/>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="15"/>
@@ -6810,6 +7391,7 @@
       <c r="F563" s="18"/>
       <c r="G563" s="17"/>
       <c r="H563" s="15"/>
+      <c r="I563" s="15"/>
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="15"/>
@@ -6820,6 +7402,7 @@
       <c r="F564" s="18"/>
       <c r="G564" s="17"/>
       <c r="H564" s="15"/>
+      <c r="I564" s="15"/>
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="15"/>
@@ -6830,6 +7413,7 @@
       <c r="F565" s="18"/>
       <c r="G565" s="17"/>
       <c r="H565" s="15"/>
+      <c r="I565" s="15"/>
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="15"/>
@@ -6840,6 +7424,7 @@
       <c r="F566" s="18"/>
       <c r="G566" s="17"/>
       <c r="H566" s="15"/>
+      <c r="I566" s="15"/>
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="15"/>
@@ -6850,6 +7435,7 @@
       <c r="F567" s="18"/>
       <c r="G567" s="17"/>
       <c r="H567" s="15"/>
+      <c r="I567" s="15"/>
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="15"/>
@@ -6860,6 +7446,7 @@
       <c r="F568" s="18"/>
       <c r="G568" s="17"/>
       <c r="H568" s="15"/>
+      <c r="I568" s="15"/>
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="15"/>
@@ -6870,6 +7457,7 @@
       <c r="F569" s="18"/>
       <c r="G569" s="17"/>
       <c r="H569" s="15"/>
+      <c r="I569" s="15"/>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="15"/>
@@ -6880,6 +7468,7 @@
       <c r="F570" s="18"/>
       <c r="G570" s="17"/>
       <c r="H570" s="15"/>
+      <c r="I570" s="15"/>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="15"/>
@@ -6890,6 +7479,7 @@
       <c r="F571" s="18"/>
       <c r="G571" s="17"/>
       <c r="H571" s="15"/>
+      <c r="I571" s="15"/>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="15"/>
@@ -6900,6 +7490,7 @@
       <c r="F572" s="18"/>
       <c r="G572" s="17"/>
       <c r="H572" s="15"/>
+      <c r="I572" s="15"/>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="15"/>
@@ -6910,6 +7501,7 @@
       <c r="F573" s="18"/>
       <c r="G573" s="17"/>
       <c r="H573" s="15"/>
+      <c r="I573" s="15"/>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="15"/>
@@ -6920,6 +7512,7 @@
       <c r="F574" s="18"/>
       <c r="G574" s="17"/>
       <c r="H574" s="15"/>
+      <c r="I574" s="15"/>
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="15"/>
@@ -6930,6 +7523,7 @@
       <c r="F575" s="18"/>
       <c r="G575" s="17"/>
       <c r="H575" s="15"/>
+      <c r="I575" s="15"/>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="15"/>
@@ -6940,6 +7534,7 @@
       <c r="F576" s="18"/>
       <c r="G576" s="17"/>
       <c r="H576" s="15"/>
+      <c r="I576" s="15"/>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="15"/>
@@ -6950,6 +7545,7 @@
       <c r="F577" s="18"/>
       <c r="G577" s="17"/>
       <c r="H577" s="15"/>
+      <c r="I577" s="15"/>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="15"/>
@@ -6960,6 +7556,7 @@
       <c r="F578" s="18"/>
       <c r="G578" s="17"/>
       <c r="H578" s="15"/>
+      <c r="I578" s="15"/>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="15"/>
@@ -6970,6 +7567,7 @@
       <c r="F579" s="18"/>
       <c r="G579" s="17"/>
       <c r="H579" s="15"/>
+      <c r="I579" s="15"/>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="15"/>
@@ -6980,6 +7578,7 @@
       <c r="F580" s="18"/>
       <c r="G580" s="17"/>
       <c r="H580" s="15"/>
+      <c r="I580" s="15"/>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="15"/>
@@ -6990,6 +7589,7 @@
       <c r="F581" s="18"/>
       <c r="G581" s="17"/>
       <c r="H581" s="15"/>
+      <c r="I581" s="15"/>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="15"/>
@@ -7000,6 +7600,7 @@
       <c r="F582" s="18"/>
       <c r="G582" s="17"/>
       <c r="H582" s="15"/>
+      <c r="I582" s="15"/>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="15"/>
@@ -7010,6 +7611,7 @@
       <c r="F583" s="18"/>
       <c r="G583" s="17"/>
       <c r="H583" s="15"/>
+      <c r="I583" s="15"/>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="15"/>
@@ -7020,6 +7622,7 @@
       <c r="F584" s="18"/>
       <c r="G584" s="17"/>
       <c r="H584" s="15"/>
+      <c r="I584" s="15"/>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="15"/>
@@ -7030,6 +7633,7 @@
       <c r="F585" s="18"/>
       <c r="G585" s="17"/>
       <c r="H585" s="15"/>
+      <c r="I585" s="15"/>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="15"/>
@@ -7040,6 +7644,7 @@
       <c r="F586" s="18"/>
       <c r="G586" s="17"/>
       <c r="H586" s="15"/>
+      <c r="I586" s="15"/>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="15"/>
@@ -7050,6 +7655,7 @@
       <c r="F587" s="18"/>
       <c r="G587" s="17"/>
       <c r="H587" s="15"/>
+      <c r="I587" s="15"/>
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="15"/>
@@ -7060,6 +7666,7 @@
       <c r="F588" s="18"/>
       <c r="G588" s="17"/>
       <c r="H588" s="15"/>
+      <c r="I588" s="15"/>
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="15"/>
@@ -7070,6 +7677,7 @@
       <c r="F589" s="18"/>
       <c r="G589" s="17"/>
       <c r="H589" s="15"/>
+      <c r="I589" s="15"/>
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="15"/>
@@ -7080,6 +7688,7 @@
       <c r="F590" s="18"/>
       <c r="G590" s="17"/>
       <c r="H590" s="15"/>
+      <c r="I590" s="15"/>
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="15"/>
@@ -7090,6 +7699,7 @@
       <c r="F591" s="18"/>
       <c r="G591" s="17"/>
       <c r="H591" s="15"/>
+      <c r="I591" s="15"/>
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="15"/>
@@ -7100,6 +7710,7 @@
       <c r="F592" s="18"/>
       <c r="G592" s="17"/>
       <c r="H592" s="15"/>
+      <c r="I592" s="15"/>
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="15"/>
@@ -7110,6 +7721,7 @@
       <c r="F593" s="18"/>
       <c r="G593" s="17"/>
       <c r="H593" s="15"/>
+      <c r="I593" s="15"/>
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="15"/>
@@ -7120,6 +7732,7 @@
       <c r="F594" s="18"/>
       <c r="G594" s="17"/>
       <c r="H594" s="15"/>
+      <c r="I594" s="15"/>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="15"/>
@@ -7130,6 +7743,7 @@
       <c r="F595" s="18"/>
       <c r="G595" s="17"/>
       <c r="H595" s="15"/>
+      <c r="I595" s="15"/>
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="15"/>
@@ -7140,6 +7754,7 @@
       <c r="F596" s="18"/>
       <c r="G596" s="17"/>
       <c r="H596" s="15"/>
+      <c r="I596" s="15"/>
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="15"/>
@@ -7150,6 +7765,7 @@
       <c r="F597" s="18"/>
       <c r="G597" s="17"/>
       <c r="H597" s="15"/>
+      <c r="I597" s="15"/>
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="15"/>
@@ -7160,6 +7776,7 @@
       <c r="F598" s="18"/>
       <c r="G598" s="17"/>
       <c r="H598" s="15"/>
+      <c r="I598" s="15"/>
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="15"/>
@@ -7170,6 +7787,7 @@
       <c r="F599" s="18"/>
       <c r="G599" s="17"/>
       <c r="H599" s="15"/>
+      <c r="I599" s="15"/>
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="15"/>
@@ -7180,6 +7798,7 @@
       <c r="F600" s="18"/>
       <c r="G600" s="17"/>
       <c r="H600" s="15"/>
+      <c r="I600" s="15"/>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="15"/>
@@ -7190,6 +7809,7 @@
       <c r="F601" s="18"/>
       <c r="G601" s="17"/>
       <c r="H601" s="15"/>
+      <c r="I601" s="15"/>
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="15"/>
@@ -7200,6 +7820,7 @@
       <c r="F602" s="18"/>
       <c r="G602" s="17"/>
       <c r="H602" s="15"/>
+      <c r="I602" s="15"/>
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="15"/>
@@ -7210,6 +7831,7 @@
       <c r="F603" s="18"/>
       <c r="G603" s="17"/>
       <c r="H603" s="15"/>
+      <c r="I603" s="15"/>
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="15"/>
@@ -7220,6 +7842,7 @@
       <c r="F604" s="18"/>
       <c r="G604" s="17"/>
       <c r="H604" s="15"/>
+      <c r="I604" s="15"/>
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="15"/>
@@ -7230,6 +7853,7 @@
       <c r="F605" s="18"/>
       <c r="G605" s="17"/>
       <c r="H605" s="15"/>
+      <c r="I605" s="15"/>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="15"/>
@@ -7240,6 +7864,7 @@
       <c r="F606" s="18"/>
       <c r="G606" s="17"/>
       <c r="H606" s="15"/>
+      <c r="I606" s="15"/>
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="15"/>
@@ -7250,6 +7875,7 @@
       <c r="F607" s="18"/>
       <c r="G607" s="17"/>
       <c r="H607" s="15"/>
+      <c r="I607" s="15"/>
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="15"/>
@@ -7260,6 +7886,7 @@
       <c r="F608" s="18"/>
       <c r="G608" s="17"/>
       <c r="H608" s="15"/>
+      <c r="I608" s="15"/>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="15"/>
@@ -7270,6 +7897,7 @@
       <c r="F609" s="18"/>
       <c r="G609" s="17"/>
       <c r="H609" s="15"/>
+      <c r="I609" s="15"/>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="15"/>
@@ -7280,6 +7908,7 @@
       <c r="F610" s="18"/>
       <c r="G610" s="17"/>
       <c r="H610" s="15"/>
+      <c r="I610" s="15"/>
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="15"/>
@@ -7290,6 +7919,7 @@
       <c r="F611" s="18"/>
       <c r="G611" s="17"/>
       <c r="H611" s="15"/>
+      <c r="I611" s="15"/>
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="15"/>
@@ -7300,6 +7930,7 @@
       <c r="F612" s="18"/>
       <c r="G612" s="17"/>
       <c r="H612" s="15"/>
+      <c r="I612" s="15"/>
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="15"/>
@@ -7310,6 +7941,7 @@
       <c r="F613" s="18"/>
       <c r="G613" s="17"/>
       <c r="H613" s="15"/>
+      <c r="I613" s="15"/>
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="15"/>
@@ -7320,6 +7952,7 @@
       <c r="F614" s="18"/>
       <c r="G614" s="17"/>
       <c r="H614" s="15"/>
+      <c r="I614" s="15"/>
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="15"/>
@@ -7330,6 +7963,7 @@
       <c r="F615" s="18"/>
       <c r="G615" s="17"/>
       <c r="H615" s="15"/>
+      <c r="I615" s="15"/>
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="15"/>
@@ -7340,6 +7974,7 @@
       <c r="F616" s="18"/>
       <c r="G616" s="17"/>
       <c r="H616" s="15"/>
+      <c r="I616" s="15"/>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="15"/>
@@ -7350,6 +7985,7 @@
       <c r="F617" s="18"/>
       <c r="G617" s="17"/>
       <c r="H617" s="15"/>
+      <c r="I617" s="15"/>
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="15"/>
@@ -7360,6 +7996,7 @@
       <c r="F618" s="18"/>
       <c r="G618" s="17"/>
       <c r="H618" s="15"/>
+      <c r="I618" s="15"/>
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="15"/>
@@ -7370,6 +8007,7 @@
       <c r="F619" s="18"/>
       <c r="G619" s="17"/>
       <c r="H619" s="15"/>
+      <c r="I619" s="15"/>
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="15"/>
@@ -7380,6 +8018,7 @@
       <c r="F620" s="18"/>
       <c r="G620" s="17"/>
       <c r="H620" s="15"/>
+      <c r="I620" s="15"/>
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="15"/>
@@ -7390,6 +8029,7 @@
       <c r="F621" s="18"/>
       <c r="G621" s="17"/>
       <c r="H621" s="15"/>
+      <c r="I621" s="15"/>
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="15"/>
@@ -7400,6 +8040,7 @@
       <c r="F622" s="18"/>
       <c r="G622" s="17"/>
       <c r="H622" s="15"/>
+      <c r="I622" s="15"/>
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="15"/>
@@ -7410,6 +8051,7 @@
       <c r="F623" s="18"/>
       <c r="G623" s="17"/>
       <c r="H623" s="15"/>
+      <c r="I623" s="15"/>
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="15"/>
@@ -7420,6 +8062,7 @@
       <c r="F624" s="18"/>
       <c r="G624" s="17"/>
       <c r="H624" s="15"/>
+      <c r="I624" s="15"/>
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="15"/>
@@ -7430,6 +8073,7 @@
       <c r="F625" s="18"/>
       <c r="G625" s="17"/>
       <c r="H625" s="15"/>
+      <c r="I625" s="15"/>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="15"/>
@@ -7440,6 +8084,7 @@
       <c r="F626" s="18"/>
       <c r="G626" s="17"/>
       <c r="H626" s="15"/>
+      <c r="I626" s="15"/>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="15"/>
@@ -7450,6 +8095,7 @@
       <c r="F627" s="18"/>
       <c r="G627" s="17"/>
       <c r="H627" s="15"/>
+      <c r="I627" s="15"/>
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="15"/>
@@ -7460,6 +8106,7 @@
       <c r="F628" s="18"/>
       <c r="G628" s="17"/>
       <c r="H628" s="15"/>
+      <c r="I628" s="15"/>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="15"/>
@@ -7470,6 +8117,7 @@
       <c r="F629" s="18"/>
       <c r="G629" s="17"/>
       <c r="H629" s="15"/>
+      <c r="I629" s="15"/>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="15"/>
@@ -7480,6 +8128,7 @@
       <c r="F630" s="18"/>
       <c r="G630" s="17"/>
       <c r="H630" s="15"/>
+      <c r="I630" s="15"/>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="15"/>
@@ -7490,6 +8139,7 @@
       <c r="F631" s="18"/>
       <c r="G631" s="17"/>
       <c r="H631" s="15"/>
+      <c r="I631" s="15"/>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="15"/>
@@ -7500,6 +8150,7 @@
       <c r="F632" s="18"/>
       <c r="G632" s="17"/>
       <c r="H632" s="15"/>
+      <c r="I632" s="15"/>
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="15"/>
@@ -7510,6 +8161,7 @@
       <c r="F633" s="18"/>
       <c r="G633" s="17"/>
       <c r="H633" s="15"/>
+      <c r="I633" s="15"/>
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="15"/>
@@ -7520,6 +8172,7 @@
       <c r="F634" s="18"/>
       <c r="G634" s="17"/>
       <c r="H634" s="15"/>
+      <c r="I634" s="15"/>
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="15"/>
@@ -7530,6 +8183,7 @@
       <c r="F635" s="18"/>
       <c r="G635" s="17"/>
       <c r="H635" s="15"/>
+      <c r="I635" s="15"/>
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="15"/>
@@ -7540,6 +8194,7 @@
       <c r="F636" s="18"/>
       <c r="G636" s="17"/>
       <c r="H636" s="15"/>
+      <c r="I636" s="15"/>
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="15"/>
@@ -7550,6 +8205,7 @@
       <c r="F637" s="18"/>
       <c r="G637" s="17"/>
       <c r="H637" s="15"/>
+      <c r="I637" s="15"/>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="15"/>
@@ -7560,6 +8216,7 @@
       <c r="F638" s="18"/>
       <c r="G638" s="17"/>
       <c r="H638" s="15"/>
+      <c r="I638" s="15"/>
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="15"/>
@@ -7570,6 +8227,7 @@
       <c r="F639" s="18"/>
       <c r="G639" s="17"/>
       <c r="H639" s="15"/>
+      <c r="I639" s="15"/>
     </row>
     <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="15"/>
@@ -7580,6 +8238,7 @@
       <c r="F640" s="18"/>
       <c r="G640" s="17"/>
       <c r="H640" s="15"/>
+      <c r="I640" s="15"/>
     </row>
     <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="15"/>
@@ -7590,6 +8249,7 @@
       <c r="F641" s="18"/>
       <c r="G641" s="17"/>
       <c r="H641" s="15"/>
+      <c r="I641" s="15"/>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="15"/>
@@ -7600,6 +8260,7 @@
       <c r="F642" s="18"/>
       <c r="G642" s="17"/>
       <c r="H642" s="15"/>
+      <c r="I642" s="15"/>
     </row>
     <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="15"/>
@@ -7610,6 +8271,7 @@
       <c r="F643" s="18"/>
       <c r="G643" s="17"/>
       <c r="H643" s="15"/>
+      <c r="I643" s="15"/>
     </row>
     <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="15"/>
@@ -7620,6 +8282,7 @@
       <c r="F644" s="18"/>
       <c r="G644" s="17"/>
       <c r="H644" s="15"/>
+      <c r="I644" s="15"/>
     </row>
     <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="15"/>
@@ -7630,6 +8293,7 @@
       <c r="F645" s="18"/>
       <c r="G645" s="17"/>
       <c r="H645" s="15"/>
+      <c r="I645" s="15"/>
     </row>
     <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="15"/>
@@ -7640,6 +8304,7 @@
       <c r="F646" s="18"/>
       <c r="G646" s="17"/>
       <c r="H646" s="15"/>
+      <c r="I646" s="15"/>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="15"/>
@@ -7650,6 +8315,7 @@
       <c r="F647" s="18"/>
       <c r="G647" s="17"/>
       <c r="H647" s="15"/>
+      <c r="I647" s="15"/>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="15"/>
@@ -7660,6 +8326,7 @@
       <c r="F648" s="18"/>
       <c r="G648" s="17"/>
       <c r="H648" s="15"/>
+      <c r="I648" s="15"/>
     </row>
     <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="15"/>
@@ -7670,6 +8337,7 @@
       <c r="F649" s="18"/>
       <c r="G649" s="17"/>
       <c r="H649" s="15"/>
+      <c r="I649" s="15"/>
     </row>
     <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A650" s="15"/>
@@ -7680,6 +8348,7 @@
       <c r="F650" s="18"/>
       <c r="G650" s="17"/>
       <c r="H650" s="15"/>
+      <c r="I650" s="15"/>
     </row>
     <row r="651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="15"/>
@@ -7690,6 +8359,7 @@
       <c r="F651" s="18"/>
       <c r="G651" s="17"/>
       <c r="H651" s="15"/>
+      <c r="I651" s="15"/>
     </row>
     <row r="652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="15"/>
@@ -7700,6 +8370,7 @@
       <c r="F652" s="18"/>
       <c r="G652" s="17"/>
       <c r="H652" s="15"/>
+      <c r="I652" s="15"/>
     </row>
     <row r="653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="15"/>
@@ -7710,6 +8381,7 @@
       <c r="F653" s="18"/>
       <c r="G653" s="17"/>
       <c r="H653" s="15"/>
+      <c r="I653" s="15"/>
     </row>
     <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="15"/>
@@ -7720,6 +8392,7 @@
       <c r="F654" s="18"/>
       <c r="G654" s="17"/>
       <c r="H654" s="15"/>
+      <c r="I654" s="15"/>
     </row>
     <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="15"/>
@@ -7730,6 +8403,7 @@
       <c r="F655" s="18"/>
       <c r="G655" s="17"/>
       <c r="H655" s="15"/>
+      <c r="I655" s="15"/>
     </row>
     <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="15"/>
@@ -7740,6 +8414,7 @@
       <c r="F656" s="18"/>
       <c r="G656" s="17"/>
       <c r="H656" s="15"/>
+      <c r="I656" s="15"/>
     </row>
     <row r="657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A657" s="15"/>
@@ -7750,6 +8425,7 @@
       <c r="F657" s="18"/>
       <c r="G657" s="17"/>
       <c r="H657" s="15"/>
+      <c r="I657" s="15"/>
     </row>
     <row r="658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A658" s="15"/>
@@ -7760,6 +8436,7 @@
       <c r="F658" s="18"/>
       <c r="G658" s="17"/>
       <c r="H658" s="15"/>
+      <c r="I658" s="15"/>
     </row>
     <row r="659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A659" s="15"/>
@@ -7770,6 +8447,7 @@
       <c r="F659" s="18"/>
       <c r="G659" s="17"/>
       <c r="H659" s="15"/>
+      <c r="I659" s="15"/>
     </row>
     <row r="660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A660" s="15"/>
@@ -7780,6 +8458,7 @@
       <c r="F660" s="18"/>
       <c r="G660" s="17"/>
       <c r="H660" s="15"/>
+      <c r="I660" s="15"/>
     </row>
     <row r="661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="15"/>
@@ -7790,6 +8469,7 @@
       <c r="F661" s="18"/>
       <c r="G661" s="17"/>
       <c r="H661" s="15"/>
+      <c r="I661" s="15"/>
     </row>
     <row r="662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A662" s="15"/>
@@ -7800,6 +8480,7 @@
       <c r="F662" s="18"/>
       <c r="G662" s="17"/>
       <c r="H662" s="15"/>
+      <c r="I662" s="15"/>
     </row>
     <row r="663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A663" s="15"/>
@@ -7810,6 +8491,7 @@
       <c r="F663" s="18"/>
       <c r="G663" s="17"/>
       <c r="H663" s="15"/>
+      <c r="I663" s="15"/>
     </row>
     <row r="664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="15"/>
@@ -7820,6 +8502,7 @@
       <c r="F664" s="18"/>
       <c r="G664" s="17"/>
       <c r="H664" s="15"/>
+      <c r="I664" s="15"/>
     </row>
     <row r="665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A665" s="15"/>
@@ -7830,6 +8513,7 @@
       <c r="F665" s="18"/>
       <c r="G665" s="17"/>
       <c r="H665" s="15"/>
+      <c r="I665" s="15"/>
     </row>
     <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A666" s="15"/>
@@ -7840,6 +8524,7 @@
       <c r="F666" s="18"/>
       <c r="G666" s="17"/>
       <c r="H666" s="15"/>
+      <c r="I666" s="15"/>
     </row>
     <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A667" s="15"/>
@@ -7850,6 +8535,7 @@
       <c r="F667" s="18"/>
       <c r="G667" s="17"/>
       <c r="H667" s="15"/>
+      <c r="I667" s="15"/>
     </row>
     <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="15"/>
@@ -7860,6 +8546,7 @@
       <c r="F668" s="18"/>
       <c r="G668" s="17"/>
       <c r="H668" s="15"/>
+      <c r="I668" s="15"/>
     </row>
     <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A669" s="15"/>
@@ -7870,6 +8557,7 @@
       <c r="F669" s="18"/>
       <c r="G669" s="17"/>
       <c r="H669" s="15"/>
+      <c r="I669" s="15"/>
     </row>
     <row r="670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A670" s="15"/>
@@ -7880,6 +8568,7 @@
       <c r="F670" s="18"/>
       <c r="G670" s="17"/>
       <c r="H670" s="15"/>
+      <c r="I670" s="15"/>
     </row>
     <row r="671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A671" s="15"/>
@@ -7890,6 +8579,7 @@
       <c r="F671" s="18"/>
       <c r="G671" s="17"/>
       <c r="H671" s="15"/>
+      <c r="I671" s="15"/>
     </row>
     <row r="672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A672" s="15"/>
@@ -7900,6 +8590,7 @@
       <c r="F672" s="18"/>
       <c r="G672" s="17"/>
       <c r="H672" s="15"/>
+      <c r="I672" s="15"/>
     </row>
     <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A673" s="15"/>
@@ -7910,6 +8601,7 @@
       <c r="F673" s="18"/>
       <c r="G673" s="17"/>
       <c r="H673" s="15"/>
+      <c r="I673" s="15"/>
     </row>
     <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A674" s="15"/>
@@ -7920,6 +8612,7 @@
       <c r="F674" s="18"/>
       <c r="G674" s="17"/>
       <c r="H674" s="15"/>
+      <c r="I674" s="15"/>
     </row>
     <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A675" s="15"/>
@@ -7930,6 +8623,7 @@
       <c r="F675" s="18"/>
       <c r="G675" s="17"/>
       <c r="H675" s="15"/>
+      <c r="I675" s="15"/>
     </row>
     <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A676" s="15"/>
@@ -7940,6 +8634,7 @@
       <c r="F676" s="18"/>
       <c r="G676" s="17"/>
       <c r="H676" s="15"/>
+      <c r="I676" s="15"/>
     </row>
     <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A677" s="15"/>
@@ -7950,6 +8645,7 @@
       <c r="F677" s="18"/>
       <c r="G677" s="17"/>
       <c r="H677" s="15"/>
+      <c r="I677" s="15"/>
     </row>
     <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="15"/>
@@ -7960,6 +8656,7 @@
       <c r="F678" s="18"/>
       <c r="G678" s="17"/>
       <c r="H678" s="15"/>
+      <c r="I678" s="15"/>
     </row>
     <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A679" s="15"/>
@@ -7970,6 +8667,7 @@
       <c r="F679" s="18"/>
       <c r="G679" s="17"/>
       <c r="H679" s="15"/>
+      <c r="I679" s="15"/>
     </row>
     <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A680" s="15"/>
@@ -7980,6 +8678,7 @@
       <c r="F680" s="18"/>
       <c r="G680" s="17"/>
       <c r="H680" s="15"/>
+      <c r="I680" s="15"/>
     </row>
     <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="15"/>
@@ -7990,6 +8689,7 @@
       <c r="F681" s="18"/>
       <c r="G681" s="17"/>
       <c r="H681" s="15"/>
+      <c r="I681" s="15"/>
     </row>
     <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A682" s="15"/>
@@ -8000,6 +8700,7 @@
       <c r="F682" s="18"/>
       <c r="G682" s="17"/>
       <c r="H682" s="15"/>
+      <c r="I682" s="15"/>
     </row>
     <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A683" s="15"/>
@@ -8010,6 +8711,7 @@
       <c r="F683" s="18"/>
       <c r="G683" s="17"/>
       <c r="H683" s="15"/>
+      <c r="I683" s="15"/>
     </row>
     <row r="684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A684" s="15"/>
@@ -8020,6 +8722,7 @@
       <c r="F684" s="18"/>
       <c r="G684" s="17"/>
       <c r="H684" s="15"/>
+      <c r="I684" s="15"/>
     </row>
     <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A685" s="15"/>
@@ -8030,6 +8733,7 @@
       <c r="F685" s="18"/>
       <c r="G685" s="17"/>
       <c r="H685" s="15"/>
+      <c r="I685" s="15"/>
     </row>
     <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A686" s="15"/>
@@ -8040,6 +8744,7 @@
       <c r="F686" s="18"/>
       <c r="G686" s="17"/>
       <c r="H686" s="15"/>
+      <c r="I686" s="15"/>
     </row>
     <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A687" s="15"/>
@@ -8050,6 +8755,7 @@
       <c r="F687" s="18"/>
       <c r="G687" s="17"/>
       <c r="H687" s="15"/>
+      <c r="I687" s="15"/>
     </row>
     <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A688" s="15"/>
@@ -8060,6 +8766,7 @@
       <c r="F688" s="18"/>
       <c r="G688" s="17"/>
       <c r="H688" s="15"/>
+      <c r="I688" s="15"/>
     </row>
     <row r="689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A689" s="15"/>
@@ -8070,6 +8777,7 @@
       <c r="F689" s="18"/>
       <c r="G689" s="17"/>
       <c r="H689" s="15"/>
+      <c r="I689" s="15"/>
     </row>
     <row r="690" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A690" s="15"/>
@@ -8080,6 +8788,7 @@
       <c r="F690" s="18"/>
       <c r="G690" s="17"/>
       <c r="H690" s="15"/>
+      <c r="I690" s="15"/>
     </row>
     <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A691" s="15"/>
@@ -8090,6 +8799,7 @@
       <c r="F691" s="18"/>
       <c r="G691" s="17"/>
       <c r="H691" s="15"/>
+      <c r="I691" s="15"/>
     </row>
     <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A692" s="15"/>
@@ -8100,6 +8810,7 @@
       <c r="F692" s="18"/>
       <c r="G692" s="17"/>
       <c r="H692" s="15"/>
+      <c r="I692" s="15"/>
     </row>
     <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="15"/>
@@ -8110,6 +8821,7 @@
       <c r="F693" s="18"/>
       <c r="G693" s="17"/>
       <c r="H693" s="15"/>
+      <c r="I693" s="15"/>
     </row>
     <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A694" s="15"/>
@@ -8120,6 +8832,7 @@
       <c r="F694" s="18"/>
       <c r="G694" s="17"/>
       <c r="H694" s="15"/>
+      <c r="I694" s="15"/>
     </row>
     <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A695" s="15"/>
@@ -8130,6 +8843,7 @@
       <c r="F695" s="18"/>
       <c r="G695" s="17"/>
       <c r="H695" s="15"/>
+      <c r="I695" s="15"/>
     </row>
     <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A696" s="15"/>
@@ -8140,6 +8854,7 @@
       <c r="F696" s="18"/>
       <c r="G696" s="17"/>
       <c r="H696" s="15"/>
+      <c r="I696" s="15"/>
     </row>
     <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A697" s="15"/>
@@ -8150,6 +8865,7 @@
       <c r="F697" s="18"/>
       <c r="G697" s="17"/>
       <c r="H697" s="15"/>
+      <c r="I697" s="15"/>
     </row>
     <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A698" s="15"/>
@@ -8160,6 +8876,7 @@
       <c r="F698" s="18"/>
       <c r="G698" s="17"/>
       <c r="H698" s="15"/>
+      <c r="I698" s="15"/>
     </row>
     <row r="699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A699" s="15"/>
@@ -8170,6 +8887,7 @@
       <c r="F699" s="18"/>
       <c r="G699" s="17"/>
       <c r="H699" s="15"/>
+      <c r="I699" s="15"/>
     </row>
     <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="15"/>
@@ -8180,6 +8898,7 @@
       <c r="F700" s="18"/>
       <c r="G700" s="17"/>
       <c r="H700" s="15"/>
+      <c r="I700" s="15"/>
     </row>
     <row r="701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A701" s="15"/>
@@ -8190,6 +8909,7 @@
       <c r="F701" s="18"/>
       <c r="G701" s="17"/>
       <c r="H701" s="15"/>
+      <c r="I701" s="15"/>
     </row>
     <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A702" s="15"/>
@@ -8200,6 +8920,7 @@
       <c r="F702" s="18"/>
       <c r="G702" s="17"/>
       <c r="H702" s="15"/>
+      <c r="I702" s="15"/>
     </row>
     <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A703" s="15"/>
@@ -8210,6 +8931,7 @@
       <c r="F703" s="18"/>
       <c r="G703" s="17"/>
       <c r="H703" s="15"/>
+      <c r="I703" s="15"/>
     </row>
     <row r="704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A704" s="15"/>
@@ -8220,6 +8942,7 @@
       <c r="F704" s="18"/>
       <c r="G704" s="17"/>
       <c r="H704" s="15"/>
+      <c r="I704" s="15"/>
     </row>
     <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A705" s="15"/>
@@ -8230,6 +8953,7 @@
       <c r="F705" s="18"/>
       <c r="G705" s="17"/>
       <c r="H705" s="15"/>
+      <c r="I705" s="15"/>
     </row>
     <row r="706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A706" s="15"/>
@@ -8240,6 +8964,7 @@
       <c r="F706" s="18"/>
       <c r="G706" s="17"/>
       <c r="H706" s="15"/>
+      <c r="I706" s="15"/>
     </row>
     <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A707" s="15"/>
@@ -8250,6 +8975,7 @@
       <c r="F707" s="18"/>
       <c r="G707" s="17"/>
       <c r="H707" s="15"/>
+      <c r="I707" s="15"/>
     </row>
     <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A708" s="15"/>
@@ -8260,6 +8986,7 @@
       <c r="F708" s="18"/>
       <c r="G708" s="17"/>
       <c r="H708" s="15"/>
+      <c r="I708" s="15"/>
     </row>
     <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A709" s="15"/>
@@ -8270,6 +8997,7 @@
       <c r="F709" s="18"/>
       <c r="G709" s="17"/>
       <c r="H709" s="15"/>
+      <c r="I709" s="15"/>
     </row>
     <row r="710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A710" s="15"/>
@@ -8280,6 +9008,7 @@
       <c r="F710" s="18"/>
       <c r="G710" s="17"/>
       <c r="H710" s="15"/>
+      <c r="I710" s="15"/>
     </row>
     <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A711" s="15"/>
@@ -8290,6 +9019,7 @@
       <c r="F711" s="18"/>
       <c r="G711" s="17"/>
       <c r="H711" s="15"/>
+      <c r="I711" s="15"/>
     </row>
     <row r="712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A712" s="15"/>
@@ -8300,6 +9030,7 @@
       <c r="F712" s="18"/>
       <c r="G712" s="17"/>
       <c r="H712" s="15"/>
+      <c r="I712" s="15"/>
     </row>
     <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A713" s="15"/>
@@ -8310,6 +9041,7 @@
       <c r="F713" s="18"/>
       <c r="G713" s="17"/>
       <c r="H713" s="15"/>
+      <c r="I713" s="15"/>
     </row>
     <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A714" s="15"/>
@@ -8320,6 +9052,7 @@
       <c r="F714" s="18"/>
       <c r="G714" s="17"/>
       <c r="H714" s="15"/>
+      <c r="I714" s="15"/>
     </row>
     <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A715" s="15"/>
@@ -8330,6 +9063,7 @@
       <c r="F715" s="18"/>
       <c r="G715" s="17"/>
       <c r="H715" s="15"/>
+      <c r="I715" s="15"/>
     </row>
     <row r="716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A716" s="15"/>
@@ -8340,6 +9074,7 @@
       <c r="F716" s="18"/>
       <c r="G716" s="17"/>
       <c r="H716" s="15"/>
+      <c r="I716" s="15"/>
     </row>
     <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A717" s="15"/>
@@ -8350,6 +9085,7 @@
       <c r="F717" s="18"/>
       <c r="G717" s="17"/>
       <c r="H717" s="15"/>
+      <c r="I717" s="15"/>
     </row>
     <row r="718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A718" s="15"/>
@@ -8360,6 +9096,7 @@
       <c r="F718" s="18"/>
       <c r="G718" s="17"/>
       <c r="H718" s="15"/>
+      <c r="I718" s="15"/>
     </row>
     <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A719" s="15"/>
@@ -8370,6 +9107,7 @@
       <c r="F719" s="18"/>
       <c r="G719" s="17"/>
       <c r="H719" s="15"/>
+      <c r="I719" s="15"/>
     </row>
     <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A720" s="15"/>
@@ -8380,6 +9118,7 @@
       <c r="F720" s="18"/>
       <c r="G720" s="17"/>
       <c r="H720" s="15"/>
+      <c r="I720" s="15"/>
     </row>
     <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A721" s="15"/>
@@ -8390,6 +9129,7 @@
       <c r="F721" s="18"/>
       <c r="G721" s="17"/>
       <c r="H721" s="15"/>
+      <c r="I721" s="15"/>
     </row>
     <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A722" s="15"/>
@@ -8400,6 +9140,7 @@
       <c r="F722" s="18"/>
       <c r="G722" s="17"/>
       <c r="H722" s="15"/>
+      <c r="I722" s="15"/>
     </row>
     <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A723" s="15"/>
@@ -8410,6 +9151,7 @@
       <c r="F723" s="18"/>
       <c r="G723" s="17"/>
       <c r="H723" s="15"/>
+      <c r="I723" s="15"/>
     </row>
     <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A724" s="15"/>
@@ -8420,6 +9162,7 @@
       <c r="F724" s="18"/>
       <c r="G724" s="17"/>
       <c r="H724" s="15"/>
+      <c r="I724" s="15"/>
     </row>
     <row r="725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A725" s="15"/>
@@ -8430,6 +9173,7 @@
       <c r="F725" s="18"/>
       <c r="G725" s="17"/>
       <c r="H725" s="15"/>
+      <c r="I725" s="15"/>
     </row>
     <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A726" s="15"/>
@@ -8440,6 +9184,7 @@
       <c r="F726" s="18"/>
       <c r="G726" s="17"/>
       <c r="H726" s="15"/>
+      <c r="I726" s="15"/>
     </row>
     <row r="727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A727" s="15"/>
@@ -8450,6 +9195,7 @@
       <c r="F727" s="18"/>
       <c r="G727" s="17"/>
       <c r="H727" s="15"/>
+      <c r="I727" s="15"/>
     </row>
     <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A728" s="15"/>
@@ -8460,6 +9206,7 @@
       <c r="F728" s="18"/>
       <c r="G728" s="17"/>
       <c r="H728" s="15"/>
+      <c r="I728" s="15"/>
     </row>
     <row r="729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A729" s="15"/>
@@ -8470,6 +9217,7 @@
       <c r="F729" s="18"/>
       <c r="G729" s="17"/>
       <c r="H729" s="15"/>
+      <c r="I729" s="15"/>
     </row>
     <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A730" s="15"/>
@@ -8480,6 +9228,7 @@
       <c r="F730" s="18"/>
       <c r="G730" s="17"/>
       <c r="H730" s="15"/>
+      <c r="I730" s="15"/>
     </row>
     <row r="731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A731" s="15"/>
@@ -8490,6 +9239,7 @@
       <c r="F731" s="18"/>
       <c r="G731" s="17"/>
       <c r="H731" s="15"/>
+      <c r="I731" s="15"/>
     </row>
     <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A732" s="15"/>
@@ -8500,6 +9250,7 @@
       <c r="F732" s="18"/>
       <c r="G732" s="17"/>
       <c r="H732" s="15"/>
+      <c r="I732" s="15"/>
     </row>
     <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A733" s="15"/>
@@ -8510,6 +9261,7 @@
       <c r="F733" s="18"/>
       <c r="G733" s="17"/>
       <c r="H733" s="15"/>
+      <c r="I733" s="15"/>
     </row>
     <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A734" s="15"/>
@@ -8520,6 +9272,7 @@
       <c r="F734" s="18"/>
       <c r="G734" s="17"/>
       <c r="H734" s="15"/>
+      <c r="I734" s="15"/>
     </row>
     <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A735" s="15"/>
@@ -8530,6 +9283,7 @@
       <c r="F735" s="18"/>
       <c r="G735" s="17"/>
       <c r="H735" s="15"/>
+      <c r="I735" s="15"/>
     </row>
     <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A736" s="15"/>
@@ -8540,6 +9294,7 @@
       <c r="F736" s="18"/>
       <c r="G736" s="17"/>
       <c r="H736" s="15"/>
+      <c r="I736" s="15"/>
     </row>
     <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A737" s="15"/>
@@ -8550,6 +9305,7 @@
       <c r="F737" s="18"/>
       <c r="G737" s="17"/>
       <c r="H737" s="15"/>
+      <c r="I737" s="15"/>
     </row>
     <row r="738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A738" s="15"/>
@@ -8560,6 +9316,7 @@
       <c r="F738" s="18"/>
       <c r="G738" s="17"/>
       <c r="H738" s="15"/>
+      <c r="I738" s="15"/>
     </row>
     <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A739" s="15"/>
@@ -8570,6 +9327,7 @@
       <c r="F739" s="18"/>
       <c r="G739" s="17"/>
       <c r="H739" s="15"/>
+      <c r="I739" s="15"/>
     </row>
     <row r="740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A740" s="15"/>
@@ -8580,6 +9338,7 @@
       <c r="F740" s="18"/>
       <c r="G740" s="17"/>
       <c r="H740" s="15"/>
+      <c r="I740" s="15"/>
     </row>
     <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A741" s="15"/>
@@ -8590,6 +9349,7 @@
       <c r="F741" s="18"/>
       <c r="G741" s="17"/>
       <c r="H741" s="15"/>
+      <c r="I741" s="15"/>
     </row>
     <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A742" s="15"/>
@@ -8600,6 +9360,7 @@
       <c r="F742" s="18"/>
       <c r="G742" s="17"/>
       <c r="H742" s="15"/>
+      <c r="I742" s="15"/>
     </row>
     <row r="743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A743" s="15"/>
@@ -8610,6 +9371,7 @@
       <c r="F743" s="18"/>
       <c r="G743" s="17"/>
       <c r="H743" s="15"/>
+      <c r="I743" s="15"/>
     </row>
     <row r="744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A744" s="15"/>
@@ -8620,6 +9382,7 @@
       <c r="F744" s="18"/>
       <c r="G744" s="17"/>
       <c r="H744" s="15"/>
+      <c r="I744" s="15"/>
     </row>
     <row r="745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A745" s="15"/>
@@ -8630,6 +9393,7 @@
       <c r="F745" s="18"/>
       <c r="G745" s="17"/>
       <c r="H745" s="15"/>
+      <c r="I745" s="15"/>
     </row>
     <row r="746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A746" s="15"/>
@@ -8640,6 +9404,7 @@
       <c r="F746" s="18"/>
       <c r="G746" s="17"/>
       <c r="H746" s="15"/>
+      <c r="I746" s="15"/>
     </row>
     <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A747" s="15"/>
@@ -8650,6 +9415,7 @@
       <c r="F747" s="18"/>
       <c r="G747" s="17"/>
       <c r="H747" s="15"/>
+      <c r="I747" s="15"/>
     </row>
     <row r="748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A748" s="15"/>
@@ -8660,6 +9426,7 @@
       <c r="F748" s="18"/>
       <c r="G748" s="17"/>
       <c r="H748" s="15"/>
+      <c r="I748" s="15"/>
     </row>
     <row r="749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A749" s="15"/>
@@ -8670,6 +9437,7 @@
       <c r="F749" s="18"/>
       <c r="G749" s="17"/>
       <c r="H749" s="15"/>
+      <c r="I749" s="15"/>
     </row>
     <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A750" s="15"/>
@@ -8680,6 +9448,7 @@
       <c r="F750" s="18"/>
       <c r="G750" s="17"/>
       <c r="H750" s="15"/>
+      <c r="I750" s="15"/>
     </row>
     <row r="751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A751" s="15"/>
@@ -8690,6 +9459,7 @@
       <c r="F751" s="18"/>
       <c r="G751" s="17"/>
       <c r="H751" s="15"/>
+      <c r="I751" s="15"/>
     </row>
     <row r="752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A752" s="15"/>
@@ -8700,6 +9470,7 @@
       <c r="F752" s="18"/>
       <c r="G752" s="17"/>
       <c r="H752" s="15"/>
+      <c r="I752" s="15"/>
     </row>
     <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A753" s="15"/>
@@ -8710,6 +9481,7 @@
       <c r="F753" s="18"/>
       <c r="G753" s="17"/>
       <c r="H753" s="15"/>
+      <c r="I753" s="15"/>
     </row>
     <row r="754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A754" s="15"/>
@@ -8720,6 +9492,7 @@
       <c r="F754" s="18"/>
       <c r="G754" s="17"/>
       <c r="H754" s="15"/>
+      <c r="I754" s="15"/>
     </row>
     <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A755" s="15"/>
@@ -8730,6 +9503,7 @@
       <c r="F755" s="18"/>
       <c r="G755" s="17"/>
       <c r="H755" s="15"/>
+      <c r="I755" s="15"/>
     </row>
     <row r="756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="15"/>
@@ -8740,6 +9514,7 @@
       <c r="F756" s="18"/>
       <c r="G756" s="17"/>
       <c r="H756" s="15"/>
+      <c r="I756" s="15"/>
     </row>
     <row r="757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A757" s="15"/>
@@ -8750,6 +9525,7 @@
       <c r="F757" s="18"/>
       <c r="G757" s="17"/>
       <c r="H757" s="15"/>
+      <c r="I757" s="15"/>
     </row>
     <row r="758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A758" s="15"/>
@@ -8760,6 +9536,7 @@
       <c r="F758" s="18"/>
       <c r="G758" s="17"/>
       <c r="H758" s="15"/>
+      <c r="I758" s="15"/>
     </row>
     <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A759" s="15"/>
@@ -8770,6 +9547,7 @@
       <c r="F759" s="18"/>
       <c r="G759" s="17"/>
       <c r="H759" s="15"/>
+      <c r="I759" s="15"/>
     </row>
     <row r="760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A760" s="15"/>
@@ -8780,6 +9558,7 @@
       <c r="F760" s="18"/>
       <c r="G760" s="17"/>
       <c r="H760" s="15"/>
+      <c r="I760" s="15"/>
     </row>
     <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A761" s="15"/>
@@ -8790,6 +9569,7 @@
       <c r="F761" s="18"/>
       <c r="G761" s="17"/>
       <c r="H761" s="15"/>
+      <c r="I761" s="15"/>
     </row>
     <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A762" s="15"/>
@@ -8800,6 +9580,7 @@
       <c r="F762" s="18"/>
       <c r="G762" s="17"/>
       <c r="H762" s="15"/>
+      <c r="I762" s="15"/>
     </row>
     <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A763" s="15"/>
@@ -8810,6 +9591,7 @@
       <c r="F763" s="18"/>
       <c r="G763" s="17"/>
       <c r="H763" s="15"/>
+      <c r="I763" s="15"/>
     </row>
     <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A764" s="15"/>
@@ -8820,6 +9602,7 @@
       <c r="F764" s="18"/>
       <c r="G764" s="17"/>
       <c r="H764" s="15"/>
+      <c r="I764" s="15"/>
     </row>
     <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A765" s="15"/>
@@ -8830,6 +9613,7 @@
       <c r="F765" s="18"/>
       <c r="G765" s="17"/>
       <c r="H765" s="15"/>
+      <c r="I765" s="15"/>
     </row>
     <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A766" s="15"/>
@@ -8840,6 +9624,7 @@
       <c r="F766" s="18"/>
       <c r="G766" s="17"/>
       <c r="H766" s="15"/>
+      <c r="I766" s="15"/>
     </row>
     <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A767" s="15"/>
@@ -8850,6 +9635,7 @@
       <c r="F767" s="18"/>
       <c r="G767" s="17"/>
       <c r="H767" s="15"/>
+      <c r="I767" s="15"/>
     </row>
     <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A768" s="15"/>
@@ -8860,6 +9646,7 @@
       <c r="F768" s="18"/>
       <c r="G768" s="17"/>
       <c r="H768" s="15"/>
+      <c r="I768" s="15"/>
     </row>
     <row r="769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A769" s="15"/>
@@ -8870,6 +9657,7 @@
       <c r="F769" s="18"/>
       <c r="G769" s="17"/>
       <c r="H769" s="15"/>
+      <c r="I769" s="15"/>
     </row>
     <row r="770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A770" s="15"/>
@@ -8880,6 +9668,7 @@
       <c r="F770" s="18"/>
       <c r="G770" s="17"/>
       <c r="H770" s="15"/>
+      <c r="I770" s="15"/>
     </row>
     <row r="771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A771" s="15"/>
@@ -8890,6 +9679,7 @@
       <c r="F771" s="18"/>
       <c r="G771" s="17"/>
       <c r="H771" s="15"/>
+      <c r="I771" s="15"/>
     </row>
     <row r="772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A772" s="15"/>
@@ -8900,6 +9690,7 @@
       <c r="F772" s="18"/>
       <c r="G772" s="17"/>
       <c r="H772" s="15"/>
+      <c r="I772" s="15"/>
     </row>
     <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A773" s="15"/>
@@ -8910,6 +9701,7 @@
       <c r="F773" s="18"/>
       <c r="G773" s="17"/>
       <c r="H773" s="15"/>
+      <c r="I773" s="15"/>
     </row>
     <row r="774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A774" s="15"/>
@@ -8920,6 +9712,7 @@
       <c r="F774" s="18"/>
       <c r="G774" s="17"/>
       <c r="H774" s="15"/>
+      <c r="I774" s="15"/>
     </row>
     <row r="775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A775" s="15"/>
@@ -8930,6 +9723,7 @@
       <c r="F775" s="18"/>
       <c r="G775" s="17"/>
       <c r="H775" s="15"/>
+      <c r="I775" s="15"/>
     </row>
     <row r="776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A776" s="15"/>
@@ -8940,6 +9734,7 @@
       <c r="F776" s="18"/>
       <c r="G776" s="17"/>
       <c r="H776" s="15"/>
+      <c r="I776" s="15"/>
     </row>
     <row r="777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A777" s="15"/>
@@ -8950,6 +9745,7 @@
       <c r="F777" s="18"/>
       <c r="G777" s="17"/>
       <c r="H777" s="15"/>
+      <c r="I777" s="15"/>
     </row>
     <row r="778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A778" s="15"/>
@@ -8960,6 +9756,7 @@
       <c r="F778" s="18"/>
       <c r="G778" s="17"/>
       <c r="H778" s="15"/>
+      <c r="I778" s="15"/>
     </row>
     <row r="779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A779" s="15"/>
@@ -8970,6 +9767,7 @@
       <c r="F779" s="18"/>
       <c r="G779" s="17"/>
       <c r="H779" s="15"/>
+      <c r="I779" s="15"/>
     </row>
     <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A780" s="15"/>
@@ -8980,6 +9778,7 @@
       <c r="F780" s="18"/>
       <c r="G780" s="17"/>
       <c r="H780" s="15"/>
+      <c r="I780" s="15"/>
     </row>
     <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A781" s="15"/>
@@ -8990,6 +9789,7 @@
       <c r="F781" s="18"/>
       <c r="G781" s="17"/>
       <c r="H781" s="15"/>
+      <c r="I781" s="15"/>
     </row>
     <row r="782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A782" s="15"/>
@@ -9000,6 +9800,7 @@
       <c r="F782" s="18"/>
       <c r="G782" s="17"/>
       <c r="H782" s="15"/>
+      <c r="I782" s="15"/>
     </row>
     <row r="783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A783" s="15"/>
@@ -9010,6 +9811,7 @@
       <c r="F783" s="18"/>
       <c r="G783" s="17"/>
       <c r="H783" s="15"/>
+      <c r="I783" s="15"/>
     </row>
     <row r="784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A784" s="15"/>
@@ -9020,6 +9822,7 @@
       <c r="F784" s="18"/>
       <c r="G784" s="17"/>
       <c r="H784" s="15"/>
+      <c r="I784" s="15"/>
     </row>
     <row r="785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A785" s="15"/>
@@ -9030,6 +9833,7 @@
       <c r="F785" s="18"/>
       <c r="G785" s="17"/>
       <c r="H785" s="15"/>
+      <c r="I785" s="15"/>
     </row>
     <row r="786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A786" s="15"/>
@@ -9040,6 +9844,7 @@
       <c r="F786" s="18"/>
       <c r="G786" s="17"/>
       <c r="H786" s="15"/>
+      <c r="I786" s="15"/>
     </row>
     <row r="787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A787" s="15"/>
@@ -9050,6 +9855,7 @@
       <c r="F787" s="18"/>
       <c r="G787" s="17"/>
       <c r="H787" s="15"/>
+      <c r="I787" s="15"/>
     </row>
     <row r="788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A788" s="15"/>
@@ -9060,6 +9866,7 @@
       <c r="F788" s="18"/>
       <c r="G788" s="17"/>
       <c r="H788" s="15"/>
+      <c r="I788" s="15"/>
     </row>
     <row r="789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A789" s="15"/>
@@ -9070,6 +9877,7 @@
       <c r="F789" s="18"/>
       <c r="G789" s="17"/>
       <c r="H789" s="15"/>
+      <c r="I789" s="15"/>
     </row>
     <row r="790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A790" s="15"/>
@@ -9080,6 +9888,7 @@
       <c r="F790" s="18"/>
       <c r="G790" s="17"/>
       <c r="H790" s="15"/>
+      <c r="I790" s="15"/>
     </row>
     <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A791" s="15"/>
@@ -9090,6 +9899,7 @@
       <c r="F791" s="18"/>
       <c r="G791" s="17"/>
       <c r="H791" s="15"/>
+      <c r="I791" s="15"/>
     </row>
     <row r="792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A792" s="15"/>
@@ -9100,6 +9910,7 @@
       <c r="F792" s="18"/>
       <c r="G792" s="17"/>
       <c r="H792" s="15"/>
+      <c r="I792" s="15"/>
     </row>
     <row r="793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A793" s="15"/>
@@ -9110,6 +9921,7 @@
       <c r="F793" s="18"/>
       <c r="G793" s="17"/>
       <c r="H793" s="15"/>
+      <c r="I793" s="15"/>
     </row>
     <row r="794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A794" s="15"/>
@@ -9120,6 +9932,7 @@
       <c r="F794" s="18"/>
       <c r="G794" s="17"/>
       <c r="H794" s="15"/>
+      <c r="I794" s="15"/>
     </row>
     <row r="795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A795" s="15"/>
@@ -9130,6 +9943,7 @@
       <c r="F795" s="18"/>
       <c r="G795" s="17"/>
       <c r="H795" s="15"/>
+      <c r="I795" s="15"/>
     </row>
     <row r="796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A796" s="15"/>
@@ -9140,6 +9954,7 @@
       <c r="F796" s="18"/>
       <c r="G796" s="17"/>
       <c r="H796" s="15"/>
+      <c r="I796" s="15"/>
     </row>
     <row r="797" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A797" s="15"/>
@@ -9150,6 +9965,7 @@
       <c r="F797" s="18"/>
       <c r="G797" s="17"/>
       <c r="H797" s="15"/>
+      <c r="I797" s="15"/>
     </row>
     <row r="798" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A798" s="15"/>
@@ -9160,6 +9976,7 @@
       <c r="F798" s="18"/>
       <c r="G798" s="17"/>
       <c r="H798" s="15"/>
+      <c r="I798" s="15"/>
     </row>
     <row r="799" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A799" s="15"/>
@@ -9170,6 +9987,7 @@
       <c r="F799" s="18"/>
       <c r="G799" s="17"/>
       <c r="H799" s="15"/>
+      <c r="I799" s="15"/>
     </row>
     <row r="800" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A800" s="15"/>
@@ -9180,6 +9998,7 @@
       <c r="F800" s="18"/>
       <c r="G800" s="17"/>
       <c r="H800" s="15"/>
+      <c r="I800" s="15"/>
     </row>
     <row r="801" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A801" s="15"/>
@@ -9190,6 +10009,7 @@
       <c r="F801" s="18"/>
       <c r="G801" s="17"/>
       <c r="H801" s="15"/>
+      <c r="I801" s="15"/>
     </row>
     <row r="802" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A802" s="15"/>
@@ -9200,6 +10020,7 @@
       <c r="F802" s="18"/>
       <c r="G802" s="17"/>
       <c r="H802" s="15"/>
+      <c r="I802" s="15"/>
     </row>
     <row r="803" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A803" s="15"/>
@@ -9210,6 +10031,7 @@
       <c r="F803" s="18"/>
       <c r="G803" s="17"/>
       <c r="H803" s="15"/>
+      <c r="I803" s="15"/>
     </row>
     <row r="804" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A804" s="15"/>
@@ -9220,6 +10042,7 @@
       <c r="F804" s="18"/>
       <c r="G804" s="17"/>
       <c r="H804" s="15"/>
+      <c r="I804" s="15"/>
     </row>
     <row r="805" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A805" s="15"/>
@@ -9230,6 +10053,7 @@
       <c r="F805" s="18"/>
       <c r="G805" s="17"/>
       <c r="H805" s="15"/>
+      <c r="I805" s="15"/>
     </row>
     <row r="806" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A806" s="15"/>
@@ -9240,6 +10064,7 @@
       <c r="F806" s="18"/>
       <c r="G806" s="17"/>
       <c r="H806" s="15"/>
+      <c r="I806" s="15"/>
     </row>
     <row r="807" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A807" s="15"/>
@@ -9250,6 +10075,7 @@
       <c r="F807" s="18"/>
       <c r="G807" s="17"/>
       <c r="H807" s="15"/>
+      <c r="I807" s="15"/>
     </row>
     <row r="808" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A808" s="15"/>
@@ -9260,6 +10086,7 @@
       <c r="F808" s="18"/>
       <c r="G808" s="17"/>
       <c r="H808" s="15"/>
+      <c r="I808" s="15"/>
     </row>
     <row r="809" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A809" s="15"/>
@@ -9270,6 +10097,7 @@
       <c r="F809" s="18"/>
       <c r="G809" s="17"/>
       <c r="H809" s="15"/>
+      <c r="I809" s="15"/>
     </row>
     <row r="810" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A810" s="15"/>
@@ -9280,6 +10108,7 @@
       <c r="F810" s="18"/>
       <c r="G810" s="17"/>
       <c r="H810" s="15"/>
+      <c r="I810" s="15"/>
     </row>
     <row r="811" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A811" s="15"/>
@@ -9290,6 +10119,7 @@
       <c r="F811" s="18"/>
       <c r="G811" s="17"/>
       <c r="H811" s="15"/>
+      <c r="I811" s="15"/>
     </row>
     <row r="812" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A812" s="15"/>
@@ -9300,6 +10130,7 @@
       <c r="F812" s="18"/>
       <c r="G812" s="17"/>
       <c r="H812" s="15"/>
+      <c r="I812" s="15"/>
     </row>
     <row r="813" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A813" s="15"/>
@@ -9310,6 +10141,7 @@
       <c r="F813" s="18"/>
       <c r="G813" s="17"/>
       <c r="H813" s="15"/>
+      <c r="I813" s="15"/>
     </row>
     <row r="814" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A814" s="15"/>
@@ -9320,6 +10152,7 @@
       <c r="F814" s="18"/>
       <c r="G814" s="17"/>
       <c r="H814" s="15"/>
+      <c r="I814" s="15"/>
     </row>
     <row r="815" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A815" s="15"/>
@@ -9330,6 +10163,7 @@
       <c r="F815" s="18"/>
       <c r="G815" s="17"/>
       <c r="H815" s="15"/>
+      <c r="I815" s="15"/>
     </row>
     <row r="816" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A816" s="15"/>
@@ -9340,6 +10174,7 @@
       <c r="F816" s="18"/>
       <c r="G816" s="17"/>
       <c r="H816" s="15"/>
+      <c r="I816" s="15"/>
     </row>
     <row r="817" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A817" s="15"/>
@@ -9350,6 +10185,7 @@
       <c r="F817" s="18"/>
       <c r="G817" s="17"/>
       <c r="H817" s="15"/>
+      <c r="I817" s="15"/>
     </row>
     <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A818" s="15"/>
@@ -9360,6 +10196,7 @@
       <c r="F818" s="18"/>
       <c r="G818" s="17"/>
       <c r="H818" s="15"/>
+      <c r="I818" s="15"/>
     </row>
     <row r="819" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A819" s="15"/>
@@ -9370,6 +10207,7 @@
       <c r="F819" s="18"/>
       <c r="G819" s="17"/>
       <c r="H819" s="15"/>
+      <c r="I819" s="15"/>
     </row>
     <row r="820" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A820" s="15"/>
@@ -9380,6 +10218,7 @@
       <c r="F820" s="18"/>
       <c r="G820" s="17"/>
       <c r="H820" s="15"/>
+      <c r="I820" s="15"/>
     </row>
     <row r="821" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A821" s="15"/>
@@ -9390,6 +10229,7 @@
       <c r="F821" s="18"/>
       <c r="G821" s="17"/>
       <c r="H821" s="15"/>
+      <c r="I821" s="15"/>
     </row>
     <row r="822" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A822" s="15"/>
@@ -9400,6 +10240,7 @@
       <c r="F822" s="18"/>
       <c r="G822" s="17"/>
       <c r="H822" s="15"/>
+      <c r="I822" s="15"/>
     </row>
     <row r="823" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A823" s="15"/>
@@ -9410,6 +10251,7 @@
       <c r="F823" s="18"/>
       <c r="G823" s="17"/>
       <c r="H823" s="15"/>
+      <c r="I823" s="15"/>
     </row>
     <row r="824" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A824" s="15"/>
@@ -9420,6 +10262,7 @@
       <c r="F824" s="18"/>
       <c r="G824" s="17"/>
       <c r="H824" s="15"/>
+      <c r="I824" s="15"/>
     </row>
     <row r="825" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A825" s="15"/>
@@ -9430,6 +10273,7 @@
       <c r="F825" s="18"/>
       <c r="G825" s="17"/>
       <c r="H825" s="15"/>
+      <c r="I825" s="15"/>
     </row>
     <row r="826" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A826" s="15"/>
@@ -9440,6 +10284,7 @@
       <c r="F826" s="18"/>
       <c r="G826" s="17"/>
       <c r="H826" s="15"/>
+      <c r="I826" s="15"/>
     </row>
     <row r="827" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A827" s="15"/>
@@ -9450,6 +10295,7 @@
       <c r="F827" s="18"/>
       <c r="G827" s="17"/>
       <c r="H827" s="15"/>
+      <c r="I827" s="15"/>
     </row>
     <row r="828" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A828" s="15"/>
@@ -9460,6 +10306,7 @@
       <c r="F828" s="18"/>
       <c r="G828" s="17"/>
       <c r="H828" s="15"/>
+      <c r="I828" s="15"/>
     </row>
     <row r="829" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A829" s="15"/>
@@ -9470,6 +10317,7 @@
       <c r="F829" s="18"/>
       <c r="G829" s="17"/>
       <c r="H829" s="15"/>
+      <c r="I829" s="15"/>
     </row>
     <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A830" s="15"/>
@@ -9480,6 +10328,7 @@
       <c r="F830" s="18"/>
       <c r="G830" s="17"/>
       <c r="H830" s="15"/>
+      <c r="I830" s="15"/>
     </row>
     <row r="831" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A831" s="15"/>
@@ -9490,6 +10339,7 @@
       <c r="F831" s="18"/>
       <c r="G831" s="17"/>
       <c r="H831" s="15"/>
+      <c r="I831" s="15"/>
     </row>
     <row r="832" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A832" s="15"/>
@@ -9500,6 +10350,7 @@
       <c r="F832" s="18"/>
       <c r="G832" s="17"/>
       <c r="H832" s="15"/>
+      <c r="I832" s="15"/>
     </row>
     <row r="833" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A833" s="15"/>
@@ -9510,6 +10361,7 @@
       <c r="F833" s="18"/>
       <c r="G833" s="17"/>
       <c r="H833" s="15"/>
+      <c r="I833" s="15"/>
     </row>
     <row r="834" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A834" s="15"/>
@@ -9520,6 +10372,7 @@
       <c r="F834" s="18"/>
       <c r="G834" s="17"/>
       <c r="H834" s="15"/>
+      <c r="I834" s="15"/>
     </row>
     <row r="835" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A835" s="15"/>
@@ -9530,6 +10383,7 @@
       <c r="F835" s="18"/>
       <c r="G835" s="17"/>
       <c r="H835" s="15"/>
+      <c r="I835" s="15"/>
     </row>
     <row r="836" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A836" s="15"/>
@@ -9540,6 +10394,7 @@
       <c r="F836" s="18"/>
       <c r="G836" s="17"/>
       <c r="H836" s="15"/>
+      <c r="I836" s="15"/>
     </row>
     <row r="837" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A837" s="15"/>
@@ -9550,6 +10405,7 @@
       <c r="F837" s="18"/>
       <c r="G837" s="17"/>
       <c r="H837" s="15"/>
+      <c r="I837" s="15"/>
     </row>
     <row r="838" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A838" s="15"/>
@@ -9560,6 +10416,7 @@
       <c r="F838" s="18"/>
       <c r="G838" s="17"/>
       <c r="H838" s="15"/>
+      <c r="I838" s="15"/>
     </row>
     <row r="839" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A839" s="15"/>
@@ -9570,6 +10427,7 @@
       <c r="F839" s="18"/>
       <c r="G839" s="17"/>
       <c r="H839" s="15"/>
+      <c r="I839" s="15"/>
     </row>
     <row r="840" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A840" s="15"/>
@@ -9580,6 +10438,7 @@
       <c r="F840" s="18"/>
       <c r="G840" s="17"/>
       <c r="H840" s="15"/>
+      <c r="I840" s="15"/>
     </row>
     <row r="841" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A841" s="15"/>
@@ -9590,6 +10449,7 @@
       <c r="F841" s="18"/>
       <c r="G841" s="17"/>
       <c r="H841" s="15"/>
+      <c r="I841" s="15"/>
     </row>
     <row r="842" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A842" s="15"/>
@@ -9600,6 +10460,7 @@
       <c r="F842" s="18"/>
       <c r="G842" s="17"/>
       <c r="H842" s="15"/>
+      <c r="I842" s="15"/>
     </row>
     <row r="843" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A843" s="15"/>
@@ -9610,6 +10471,7 @@
       <c r="F843" s="18"/>
       <c r="G843" s="17"/>
       <c r="H843" s="15"/>
+      <c r="I843" s="15"/>
     </row>
     <row r="844" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A844" s="15"/>
@@ -9620,6 +10482,7 @@
       <c r="F844" s="18"/>
       <c r="G844" s="17"/>
       <c r="H844" s="15"/>
+      <c r="I844" s="15"/>
     </row>
     <row r="845" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A845" s="15"/>
@@ -9630,6 +10493,7 @@
       <c r="F845" s="18"/>
       <c r="G845" s="17"/>
       <c r="H845" s="15"/>
+      <c r="I845" s="15"/>
     </row>
     <row r="846" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A846" s="15"/>
@@ -9640,6 +10504,7 @@
       <c r="F846" s="18"/>
       <c r="G846" s="17"/>
       <c r="H846" s="15"/>
+      <c r="I846" s="15"/>
     </row>
     <row r="847" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A847" s="15"/>
@@ -9650,6 +10515,7 @@
       <c r="F847" s="18"/>
       <c r="G847" s="17"/>
       <c r="H847" s="15"/>
+      <c r="I847" s="15"/>
     </row>
     <row r="848" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A848" s="15"/>
@@ -9660,6 +10526,7 @@
       <c r="F848" s="18"/>
       <c r="G848" s="17"/>
       <c r="H848" s="15"/>
+      <c r="I848" s="15"/>
     </row>
     <row r="849" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A849" s="15"/>
@@ -9670,6 +10537,7 @@
       <c r="F849" s="18"/>
       <c r="G849" s="17"/>
       <c r="H849" s="15"/>
+      <c r="I849" s="15"/>
     </row>
     <row r="850" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A850" s="15"/>
@@ -9680,6 +10548,7 @@
       <c r="F850" s="18"/>
       <c r="G850" s="17"/>
       <c r="H850" s="15"/>
+      <c r="I850" s="15"/>
     </row>
     <row r="851" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A851" s="15"/>
@@ -9690,6 +10559,7 @@
       <c r="F851" s="18"/>
       <c r="G851" s="17"/>
       <c r="H851" s="15"/>
+      <c r="I851" s="15"/>
     </row>
     <row r="852" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A852" s="15"/>
@@ -9700,6 +10570,7 @@
       <c r="F852" s="18"/>
       <c r="G852" s="17"/>
       <c r="H852" s="15"/>
+      <c r="I852" s="15"/>
     </row>
     <row r="853" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A853" s="15"/>
@@ -9710,6 +10581,7 @@
       <c r="F853" s="18"/>
       <c r="G853" s="17"/>
       <c r="H853" s="15"/>
+      <c r="I853" s="15"/>
     </row>
     <row r="854" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A854" s="15"/>
@@ -9720,6 +10592,7 @@
       <c r="F854" s="18"/>
       <c r="G854" s="17"/>
       <c r="H854" s="15"/>
+      <c r="I854" s="15"/>
     </row>
     <row r="855" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A855" s="15"/>
@@ -9730,6 +10603,7 @@
       <c r="F855" s="18"/>
       <c r="G855" s="17"/>
       <c r="H855" s="15"/>
+      <c r="I855" s="15"/>
     </row>
     <row r="856" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A856" s="15"/>
@@ -9740,6 +10614,7 @@
       <c r="F856" s="18"/>
       <c r="G856" s="17"/>
       <c r="H856" s="15"/>
+      <c r="I856" s="15"/>
     </row>
     <row r="857" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A857" s="15"/>
@@ -9750,6 +10625,7 @@
       <c r="F857" s="18"/>
       <c r="G857" s="17"/>
       <c r="H857" s="15"/>
+      <c r="I857" s="15"/>
     </row>
     <row r="858" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A858" s="15"/>
@@ -9760,6 +10636,7 @@
       <c r="F858" s="18"/>
       <c r="G858" s="17"/>
       <c r="H858" s="15"/>
+      <c r="I858" s="15"/>
     </row>
     <row r="859" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A859" s="15"/>
@@ -9770,6 +10647,7 @@
       <c r="F859" s="18"/>
       <c r="G859" s="17"/>
       <c r="H859" s="15"/>
+      <c r="I859" s="15"/>
     </row>
     <row r="860" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A860" s="15"/>
@@ -9780,6 +10658,7 @@
       <c r="F860" s="18"/>
       <c r="G860" s="17"/>
       <c r="H860" s="15"/>
+      <c r="I860" s="15"/>
     </row>
     <row r="861" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A861" s="15"/>
@@ -9790,6 +10669,7 @@
       <c r="F861" s="18"/>
       <c r="G861" s="17"/>
       <c r="H861" s="15"/>
+      <c r="I861" s="15"/>
     </row>
     <row r="862" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A862" s="15"/>
@@ -9800,6 +10680,7 @@
       <c r="F862" s="18"/>
       <c r="G862" s="17"/>
       <c r="H862" s="15"/>
+      <c r="I862" s="15"/>
     </row>
     <row r="863" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A863" s="15"/>
@@ -9810,6 +10691,7 @@
       <c r="F863" s="18"/>
       <c r="G863" s="17"/>
       <c r="H863" s="15"/>
+      <c r="I863" s="15"/>
     </row>
     <row r="864" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A864" s="15"/>
@@ -9820,6 +10702,7 @@
       <c r="F864" s="18"/>
       <c r="G864" s="17"/>
       <c r="H864" s="15"/>
+      <c r="I864" s="15"/>
     </row>
     <row r="865" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A865" s="15"/>
@@ -9830,6 +10713,7 @@
       <c r="F865" s="18"/>
       <c r="G865" s="17"/>
       <c r="H865" s="15"/>
+      <c r="I865" s="15"/>
     </row>
     <row r="866" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A866" s="15"/>
@@ -9840,6 +10724,7 @@
       <c r="F866" s="18"/>
       <c r="G866" s="17"/>
       <c r="H866" s="15"/>
+      <c r="I866" s="15"/>
     </row>
     <row r="867" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A867" s="15"/>
@@ -9850,6 +10735,7 @@
       <c r="F867" s="18"/>
       <c r="G867" s="17"/>
       <c r="H867" s="15"/>
+      <c r="I867" s="15"/>
     </row>
     <row r="868" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A868" s="15"/>
@@ -9860,6 +10746,7 @@
       <c r="F868" s="18"/>
       <c r="G868" s="17"/>
       <c r="H868" s="15"/>
+      <c r="I868" s="15"/>
     </row>
     <row r="869" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A869" s="15"/>
@@ -9870,6 +10757,7 @@
       <c r="F869" s="18"/>
       <c r="G869" s="17"/>
       <c r="H869" s="15"/>
+      <c r="I869" s="15"/>
     </row>
     <row r="870" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A870" s="15"/>
@@ -9880,6 +10768,7 @@
       <c r="F870" s="18"/>
       <c r="G870" s="17"/>
       <c r="H870" s="15"/>
+      <c r="I870" s="15"/>
     </row>
     <row r="871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A871" s="15"/>
@@ -9890,6 +10779,7 @@
       <c r="F871" s="18"/>
       <c r="G871" s="17"/>
       <c r="H871" s="15"/>
+      <c r="I871" s="15"/>
     </row>
     <row r="872" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A872" s="15"/>
@@ -9900,6 +10790,7 @@
       <c r="F872" s="18"/>
       <c r="G872" s="17"/>
       <c r="H872" s="15"/>
+      <c r="I872" s="15"/>
     </row>
     <row r="873" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A873" s="15"/>
@@ -9910,6 +10801,7 @@
       <c r="F873" s="18"/>
       <c r="G873" s="17"/>
       <c r="H873" s="15"/>
+      <c r="I873" s="15"/>
     </row>
     <row r="874" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A874" s="15"/>
@@ -9920,6 +10812,7 @@
       <c r="F874" s="18"/>
       <c r="G874" s="17"/>
       <c r="H874" s="15"/>
+      <c r="I874" s="15"/>
     </row>
     <row r="875" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A875" s="15"/>
@@ -9930,6 +10823,7 @@
       <c r="F875" s="18"/>
       <c r="G875" s="17"/>
       <c r="H875" s="15"/>
+      <c r="I875" s="15"/>
     </row>
     <row r="876" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A876" s="15"/>
@@ -9940,6 +10834,7 @@
       <c r="F876" s="18"/>
       <c r="G876" s="17"/>
       <c r="H876" s="15"/>
+      <c r="I876" s="15"/>
     </row>
     <row r="877" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A877" s="15"/>
@@ -9950,6 +10845,7 @@
       <c r="F877" s="18"/>
       <c r="G877" s="17"/>
       <c r="H877" s="15"/>
+      <c r="I877" s="15"/>
     </row>
     <row r="878" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A878" s="15"/>
@@ -9960,6 +10856,7 @@
       <c r="F878" s="18"/>
       <c r="G878" s="17"/>
       <c r="H878" s="15"/>
+      <c r="I878" s="15"/>
     </row>
     <row r="879" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A879" s="15"/>
@@ -9970,6 +10867,7 @@
       <c r="F879" s="18"/>
       <c r="G879" s="17"/>
       <c r="H879" s="15"/>
+      <c r="I879" s="15"/>
     </row>
     <row r="880" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A880" s="15"/>
@@ -9980,6 +10878,7 @@
       <c r="F880" s="18"/>
       <c r="G880" s="17"/>
       <c r="H880" s="15"/>
+      <c r="I880" s="15"/>
     </row>
     <row r="881" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A881" s="15"/>
@@ -9990,6 +10889,7 @@
       <c r="F881" s="18"/>
       <c r="G881" s="17"/>
       <c r="H881" s="15"/>
+      <c r="I881" s="15"/>
     </row>
     <row r="882" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A882" s="15"/>
@@ -10000,6 +10900,7 @@
       <c r="F882" s="18"/>
       <c r="G882" s="17"/>
       <c r="H882" s="15"/>
+      <c r="I882" s="15"/>
     </row>
     <row r="883" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A883" s="15"/>
@@ -10010,6 +10911,7 @@
       <c r="F883" s="18"/>
       <c r="G883" s="17"/>
       <c r="H883" s="15"/>
+      <c r="I883" s="15"/>
     </row>
     <row r="884" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A884" s="15"/>
@@ -10020,6 +10922,7 @@
       <c r="F884" s="18"/>
       <c r="G884" s="17"/>
       <c r="H884" s="15"/>
+      <c r="I884" s="15"/>
     </row>
     <row r="885" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A885" s="15"/>
@@ -10030,6 +10933,7 @@
       <c r="F885" s="18"/>
       <c r="G885" s="17"/>
       <c r="H885" s="15"/>
+      <c r="I885" s="15"/>
     </row>
     <row r="886" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A886" s="15"/>
@@ -10040,6 +10944,7 @@
       <c r="F886" s="18"/>
       <c r="G886" s="17"/>
       <c r="H886" s="15"/>
+      <c r="I886" s="15"/>
     </row>
     <row r="887" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A887" s="15"/>
@@ -10050,6 +10955,7 @@
       <c r="F887" s="18"/>
       <c r="G887" s="17"/>
       <c r="H887" s="15"/>
+      <c r="I887" s="15"/>
     </row>
     <row r="888" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A888" s="15"/>
@@ -10060,6 +10966,7 @@
       <c r="F888" s="18"/>
       <c r="G888" s="17"/>
       <c r="H888" s="15"/>
+      <c r="I888" s="15"/>
     </row>
     <row r="889" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A889" s="15"/>
@@ -10070,6 +10977,7 @@
       <c r="F889" s="18"/>
       <c r="G889" s="17"/>
       <c r="H889" s="15"/>
+      <c r="I889" s="15"/>
     </row>
     <row r="890" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A890" s="15"/>
@@ -10080,6 +10988,7 @@
       <c r="F890" s="18"/>
       <c r="G890" s="17"/>
       <c r="H890" s="15"/>
+      <c r="I890" s="15"/>
     </row>
     <row r="891" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A891" s="15"/>
@@ -10090,6 +10999,7 @@
       <c r="F891" s="18"/>
       <c r="G891" s="17"/>
       <c r="H891" s="15"/>
+      <c r="I891" s="15"/>
     </row>
     <row r="892" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A892" s="15"/>
@@ -10100,6 +11010,7 @@
       <c r="F892" s="18"/>
       <c r="G892" s="17"/>
       <c r="H892" s="15"/>
+      <c r="I892" s="15"/>
     </row>
     <row r="893" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A893" s="15"/>
@@ -10110,6 +11021,7 @@
       <c r="F893" s="18"/>
       <c r="G893" s="17"/>
       <c r="H893" s="15"/>
+      <c r="I893" s="15"/>
     </row>
     <row r="894" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A894" s="15"/>
@@ -10120,6 +11032,7 @@
       <c r="F894" s="18"/>
       <c r="G894" s="17"/>
       <c r="H894" s="15"/>
+      <c r="I894" s="15"/>
     </row>
     <row r="895" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A895" s="15"/>
@@ -10130,6 +11043,7 @@
       <c r="F895" s="18"/>
       <c r="G895" s="17"/>
       <c r="H895" s="15"/>
+      <c r="I895" s="15"/>
     </row>
     <row r="896" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A896" s="15"/>
@@ -10140,6 +11054,7 @@
       <c r="F896" s="18"/>
       <c r="G896" s="17"/>
       <c r="H896" s="15"/>
+      <c r="I896" s="15"/>
     </row>
     <row r="897" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A897" s="15"/>
@@ -10150,6 +11065,7 @@
       <c r="F897" s="18"/>
       <c r="G897" s="17"/>
       <c r="H897" s="15"/>
+      <c r="I897" s="15"/>
     </row>
     <row r="898" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A898" s="15"/>
@@ -10160,6 +11076,7 @@
       <c r="F898" s="18"/>
       <c r="G898" s="17"/>
       <c r="H898" s="15"/>
+      <c r="I898" s="15"/>
     </row>
     <row r="899" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A899" s="15"/>
@@ -10170,6 +11087,7 @@
       <c r="F899" s="18"/>
       <c r="G899" s="17"/>
       <c r="H899" s="15"/>
+      <c r="I899" s="15"/>
     </row>
     <row r="900" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A900" s="15"/>
@@ -10180,6 +11098,7 @@
       <c r="F900" s="18"/>
       <c r="G900" s="17"/>
       <c r="H900" s="15"/>
+      <c r="I900" s="15"/>
     </row>
     <row r="901" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A901" s="15"/>
@@ -10190,6 +11109,7 @@
       <c r="F901" s="18"/>
       <c r="G901" s="17"/>
       <c r="H901" s="15"/>
+      <c r="I901" s="15"/>
     </row>
     <row r="902" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A902" s="15"/>
@@ -10200,6 +11120,7 @@
       <c r="F902" s="18"/>
       <c r="G902" s="17"/>
       <c r="H902" s="15"/>
+      <c r="I902" s="15"/>
     </row>
     <row r="903" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A903" s="15"/>
@@ -10210,6 +11131,7 @@
       <c r="F903" s="18"/>
       <c r="G903" s="17"/>
       <c r="H903" s="15"/>
+      <c r="I903" s="15"/>
     </row>
     <row r="904" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A904" s="15"/>
@@ -10220,6 +11142,7 @@
       <c r="F904" s="18"/>
       <c r="G904" s="17"/>
       <c r="H904" s="15"/>
+      <c r="I904" s="15"/>
     </row>
     <row r="905" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A905" s="15"/>
@@ -10230,6 +11153,7 @@
       <c r="F905" s="18"/>
       <c r="G905" s="17"/>
       <c r="H905" s="15"/>
+      <c r="I905" s="15"/>
     </row>
     <row r="906" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A906" s="15"/>
@@ -10240,6 +11164,7 @@
       <c r="F906" s="18"/>
       <c r="G906" s="17"/>
       <c r="H906" s="15"/>
+      <c r="I906" s="15"/>
     </row>
     <row r="907" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A907" s="15"/>
@@ -10250,6 +11175,7 @@
       <c r="F907" s="18"/>
       <c r="G907" s="17"/>
       <c r="H907" s="15"/>
+      <c r="I907" s="15"/>
     </row>
     <row r="908" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A908" s="15"/>
@@ -10260,6 +11186,7 @@
       <c r="F908" s="18"/>
       <c r="G908" s="17"/>
       <c r="H908" s="15"/>
+      <c r="I908" s="15"/>
     </row>
     <row r="909" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A909" s="15"/>
@@ -10270,6 +11197,7 @@
       <c r="F909" s="18"/>
       <c r="G909" s="17"/>
       <c r="H909" s="15"/>
+      <c r="I909" s="15"/>
     </row>
     <row r="910" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A910" s="15"/>
@@ -10280,6 +11208,7 @@
       <c r="F910" s="18"/>
       <c r="G910" s="17"/>
       <c r="H910" s="15"/>
+      <c r="I910" s="15"/>
     </row>
     <row r="911" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A911" s="15"/>
@@ -10290,6 +11219,7 @@
       <c r="F911" s="18"/>
       <c r="G911" s="17"/>
       <c r="H911" s="15"/>
+      <c r="I911" s="15"/>
     </row>
     <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A912" s="15"/>
@@ -10300,6 +11230,7 @@
       <c r="F912" s="18"/>
       <c r="G912" s="17"/>
       <c r="H912" s="15"/>
+      <c r="I912" s="15"/>
     </row>
     <row r="913" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A913" s="15"/>
@@ -10310,6 +11241,7 @@
       <c r="F913" s="18"/>
       <c r="G913" s="17"/>
       <c r="H913" s="15"/>
+      <c r="I913" s="15"/>
     </row>
     <row r="914" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A914" s="15"/>
@@ -10320,6 +11252,7 @@
       <c r="F914" s="18"/>
       <c r="G914" s="17"/>
       <c r="H914" s="15"/>
+      <c r="I914" s="15"/>
     </row>
     <row r="915" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A915" s="15"/>
@@ -10330,6 +11263,7 @@
       <c r="F915" s="18"/>
       <c r="G915" s="17"/>
       <c r="H915" s="15"/>
+      <c r="I915" s="15"/>
     </row>
     <row r="916" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A916" s="15"/>
@@ -10340,6 +11274,7 @@
       <c r="F916" s="18"/>
       <c r="G916" s="17"/>
       <c r="H916" s="15"/>
+      <c r="I916" s="15"/>
     </row>
     <row r="917" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A917" s="15"/>
@@ -10350,6 +11285,7 @@
       <c r="F917" s="18"/>
       <c r="G917" s="17"/>
       <c r="H917" s="15"/>
+      <c r="I917" s="15"/>
     </row>
     <row r="918" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A918" s="15"/>
@@ -10360,6 +11296,7 @@
       <c r="F918" s="18"/>
       <c r="G918" s="17"/>
       <c r="H918" s="15"/>
+      <c r="I918" s="15"/>
     </row>
     <row r="919" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A919" s="15"/>
@@ -10370,6 +11307,7 @@
       <c r="F919" s="18"/>
       <c r="G919" s="17"/>
       <c r="H919" s="15"/>
+      <c r="I919" s="15"/>
     </row>
     <row r="920" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A920" s="15"/>
@@ -10380,6 +11318,7 @@
       <c r="F920" s="18"/>
       <c r="G920" s="17"/>
       <c r="H920" s="15"/>
+      <c r="I920" s="15"/>
     </row>
     <row r="921" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A921" s="15"/>
@@ -10390,6 +11329,7 @@
       <c r="F921" s="18"/>
       <c r="G921" s="17"/>
       <c r="H921" s="15"/>
+      <c r="I921" s="15"/>
     </row>
     <row r="922" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A922" s="15"/>
@@ -10400,6 +11340,7 @@
       <c r="F922" s="18"/>
       <c r="G922" s="17"/>
       <c r="H922" s="15"/>
+      <c r="I922" s="15"/>
     </row>
     <row r="923" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A923" s="15"/>
@@ -10410,6 +11351,7 @@
       <c r="F923" s="18"/>
       <c r="G923" s="17"/>
       <c r="H923" s="15"/>
+      <c r="I923" s="15"/>
     </row>
     <row r="924" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A924" s="15"/>
@@ -10420,6 +11362,7 @@
       <c r="F924" s="18"/>
       <c r="G924" s="17"/>
       <c r="H924" s="15"/>
+      <c r="I924" s="15"/>
     </row>
     <row r="925" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="15"/>
@@ -10430,6 +11373,7 @@
       <c r="F925" s="18"/>
       <c r="G925" s="17"/>
       <c r="H925" s="15"/>
+      <c r="I925" s="15"/>
     </row>
     <row r="926" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A926" s="15"/>
@@ -10440,6 +11384,7 @@
       <c r="F926" s="18"/>
       <c r="G926" s="17"/>
       <c r="H926" s="15"/>
+      <c r="I926" s="15"/>
     </row>
     <row r="927" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="15"/>
@@ -10450,6 +11395,7 @@
       <c r="F927" s="18"/>
       <c r="G927" s="17"/>
       <c r="H927" s="15"/>
+      <c r="I927" s="15"/>
     </row>
     <row r="928" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A928" s="15"/>
@@ -10460,6 +11406,7 @@
       <c r="F928" s="18"/>
       <c r="G928" s="17"/>
       <c r="H928" s="15"/>
+      <c r="I928" s="15"/>
     </row>
     <row r="929" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A929" s="15"/>
@@ -10470,6 +11417,7 @@
       <c r="F929" s="18"/>
       <c r="G929" s="17"/>
       <c r="H929" s="15"/>
+      <c r="I929" s="15"/>
     </row>
     <row r="930" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A930" s="15"/>
@@ -10480,6 +11428,7 @@
       <c r="F930" s="18"/>
       <c r="G930" s="17"/>
       <c r="H930" s="15"/>
+      <c r="I930" s="15"/>
     </row>
     <row r="931" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A931" s="15"/>
@@ -10490,6 +11439,7 @@
       <c r="F931" s="18"/>
       <c r="G931" s="17"/>
       <c r="H931" s="15"/>
+      <c r="I931" s="15"/>
     </row>
     <row r="932" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A932" s="15"/>
@@ -10500,6 +11450,7 @@
       <c r="F932" s="18"/>
       <c r="G932" s="17"/>
       <c r="H932" s="15"/>
+      <c r="I932" s="15"/>
     </row>
     <row r="933" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="15"/>
@@ -10510,6 +11461,7 @@
       <c r="F933" s="18"/>
       <c r="G933" s="17"/>
       <c r="H933" s="15"/>
+      <c r="I933" s="15"/>
     </row>
     <row r="934" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A934" s="15"/>
@@ -10520,6 +11472,7 @@
       <c r="F934" s="18"/>
       <c r="G934" s="17"/>
       <c r="H934" s="15"/>
+      <c r="I934" s="15"/>
     </row>
     <row r="935" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A935" s="15"/>
@@ -10530,6 +11483,7 @@
       <c r="F935" s="18"/>
       <c r="G935" s="17"/>
       <c r="H935" s="15"/>
+      <c r="I935" s="15"/>
     </row>
     <row r="936" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A936" s="15"/>
@@ -10540,6 +11494,7 @@
       <c r="F936" s="18"/>
       <c r="G936" s="17"/>
       <c r="H936" s="15"/>
+      <c r="I936" s="15"/>
     </row>
     <row r="937" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A937" s="15"/>
@@ -10550,6 +11505,7 @@
       <c r="F937" s="18"/>
       <c r="G937" s="17"/>
       <c r="H937" s="15"/>
+      <c r="I937" s="15"/>
     </row>
     <row r="938" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A938" s="15"/>
@@ -10560,6 +11516,7 @@
       <c r="F938" s="18"/>
       <c r="G938" s="17"/>
       <c r="H938" s="15"/>
+      <c r="I938" s="15"/>
     </row>
     <row r="939" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A939" s="15"/>
@@ -10570,6 +11527,7 @@
       <c r="F939" s="18"/>
       <c r="G939" s="17"/>
       <c r="H939" s="15"/>
+      <c r="I939" s="15"/>
     </row>
     <row r="940" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A940" s="15"/>
@@ -10580,6 +11538,7 @@
       <c r="F940" s="18"/>
       <c r="G940" s="17"/>
       <c r="H940" s="15"/>
+      <c r="I940" s="15"/>
     </row>
     <row r="941" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A941" s="15"/>
@@ -10590,6 +11549,7 @@
       <c r="F941" s="18"/>
       <c r="G941" s="17"/>
       <c r="H941" s="15"/>
+      <c r="I941" s="15"/>
     </row>
     <row r="942" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A942" s="15"/>
@@ -10600,6 +11560,7 @@
       <c r="F942" s="18"/>
       <c r="G942" s="17"/>
       <c r="H942" s="15"/>
+      <c r="I942" s="15"/>
     </row>
     <row r="943" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A943" s="15"/>
@@ -10610,6 +11571,7 @@
       <c r="F943" s="18"/>
       <c r="G943" s="17"/>
       <c r="H943" s="15"/>
+      <c r="I943" s="15"/>
     </row>
     <row r="944" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A944" s="15"/>
@@ -10620,6 +11582,7 @@
       <c r="F944" s="18"/>
       <c r="G944" s="17"/>
       <c r="H944" s="15"/>
+      <c r="I944" s="15"/>
     </row>
     <row r="945" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A945" s="15"/>
@@ -10630,6 +11593,7 @@
       <c r="F945" s="18"/>
       <c r="G945" s="17"/>
       <c r="H945" s="15"/>
+      <c r="I945" s="15"/>
     </row>
     <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A946" s="15"/>
@@ -10640,6 +11604,7 @@
       <c r="F946" s="18"/>
       <c r="G946" s="17"/>
       <c r="H946" s="15"/>
+      <c r="I946" s="15"/>
     </row>
     <row r="947" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A947" s="15"/>
@@ -10650,6 +11615,7 @@
       <c r="F947" s="18"/>
       <c r="G947" s="17"/>
       <c r="H947" s="15"/>
+      <c r="I947" s="15"/>
     </row>
     <row r="948" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="15"/>
@@ -10660,6 +11626,7 @@
       <c r="F948" s="18"/>
       <c r="G948" s="17"/>
       <c r="H948" s="15"/>
+      <c r="I948" s="15"/>
     </row>
     <row r="949" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="15"/>
@@ -10670,6 +11637,7 @@
       <c r="F949" s="18"/>
       <c r="G949" s="17"/>
       <c r="H949" s="15"/>
+      <c r="I949" s="15"/>
     </row>
     <row r="950" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A950" s="15"/>
@@ -10680,6 +11648,7 @@
       <c r="F950" s="18"/>
       <c r="G950" s="17"/>
       <c r="H950" s="15"/>
+      <c r="I950" s="15"/>
     </row>
     <row r="951" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A951" s="15"/>
@@ -10690,6 +11659,7 @@
       <c r="F951" s="18"/>
       <c r="G951" s="17"/>
       <c r="H951" s="15"/>
+      <c r="I951" s="15"/>
     </row>
     <row r="952" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A952" s="15"/>
@@ -10700,6 +11670,7 @@
       <c r="F952" s="18"/>
       <c r="G952" s="17"/>
       <c r="H952" s="15"/>
+      <c r="I952" s="15"/>
     </row>
     <row r="953" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A953" s="15"/>
@@ -10710,6 +11681,7 @@
       <c r="F953" s="18"/>
       <c r="G953" s="17"/>
       <c r="H953" s="15"/>
+      <c r="I953" s="15"/>
     </row>
     <row r="954" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A954" s="15"/>
@@ -10720,6 +11692,7 @@
       <c r="F954" s="18"/>
       <c r="G954" s="17"/>
       <c r="H954" s="15"/>
+      <c r="I954" s="15"/>
     </row>
     <row r="955" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A955" s="15"/>
@@ -10730,6 +11703,7 @@
       <c r="F955" s="18"/>
       <c r="G955" s="17"/>
       <c r="H955" s="15"/>
+      <c r="I955" s="15"/>
     </row>
     <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A956" s="15"/>
@@ -10740,6 +11714,7 @@
       <c r="F956" s="18"/>
       <c r="G956" s="17"/>
       <c r="H956" s="15"/>
+      <c r="I956" s="15"/>
     </row>
     <row r="957" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A957" s="15"/>
@@ -10750,6 +11725,7 @@
       <c r="F957" s="18"/>
       <c r="G957" s="17"/>
       <c r="H957" s="15"/>
+      <c r="I957" s="15"/>
     </row>
     <row r="958" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A958" s="15"/>
@@ -10760,6 +11736,7 @@
       <c r="F958" s="18"/>
       <c r="G958" s="17"/>
       <c r="H958" s="15"/>
+      <c r="I958" s="15"/>
     </row>
     <row r="959" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A959" s="15"/>
@@ -10770,6 +11747,7 @@
       <c r="F959" s="18"/>
       <c r="G959" s="17"/>
       <c r="H959" s="15"/>
+      <c r="I959" s="15"/>
     </row>
     <row r="960" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A960" s="15"/>
@@ -10780,6 +11758,7 @@
       <c r="F960" s="18"/>
       <c r="G960" s="17"/>
       <c r="H960" s="15"/>
+      <c r="I960" s="15"/>
     </row>
     <row r="961" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A961" s="15"/>
@@ -10790,6 +11769,7 @@
       <c r="F961" s="18"/>
       <c r="G961" s="17"/>
       <c r="H961" s="15"/>
+      <c r="I961" s="15"/>
     </row>
     <row r="962" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A962" s="15"/>
@@ -10800,6 +11780,7 @@
       <c r="F962" s="18"/>
       <c r="G962" s="17"/>
       <c r="H962" s="15"/>
+      <c r="I962" s="15"/>
     </row>
     <row r="963" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A963" s="15"/>
@@ -10810,6 +11791,7 @@
       <c r="F963" s="18"/>
       <c r="G963" s="17"/>
       <c r="H963" s="15"/>
+      <c r="I963" s="15"/>
     </row>
     <row r="964" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A964" s="15"/>
@@ -10820,6 +11802,7 @@
       <c r="F964" s="18"/>
       <c r="G964" s="17"/>
       <c r="H964" s="15"/>
+      <c r="I964" s="15"/>
     </row>
     <row r="965" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A965" s="15"/>
@@ -10830,6 +11813,7 @@
       <c r="F965" s="18"/>
       <c r="G965" s="17"/>
       <c r="H965" s="15"/>
+      <c r="I965" s="15"/>
     </row>
     <row r="966" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A966" s="15"/>
@@ -10840,6 +11824,7 @@
       <c r="F966" s="18"/>
       <c r="G966" s="17"/>
       <c r="H966" s="15"/>
+      <c r="I966" s="15"/>
     </row>
     <row r="967" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A967" s="15"/>
@@ -10850,6 +11835,7 @@
       <c r="F967" s="18"/>
       <c r="G967" s="17"/>
       <c r="H967" s="15"/>
+      <c r="I967" s="15"/>
     </row>
     <row r="968" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A968" s="15"/>
@@ -10860,6 +11846,7 @@
       <c r="F968" s="18"/>
       <c r="G968" s="17"/>
       <c r="H968" s="15"/>
+      <c r="I968" s="15"/>
     </row>
     <row r="969" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A969" s="15"/>
@@ -10870,6 +11857,7 @@
       <c r="F969" s="18"/>
       <c r="G969" s="17"/>
       <c r="H969" s="15"/>
+      <c r="I969" s="15"/>
     </row>
     <row r="970" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A970" s="15"/>
@@ -10880,6 +11868,7 @@
       <c r="F970" s="18"/>
       <c r="G970" s="17"/>
       <c r="H970" s="15"/>
+      <c r="I970" s="15"/>
     </row>
     <row r="971" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A971" s="15"/>
@@ -10890,6 +11879,7 @@
       <c r="F971" s="18"/>
       <c r="G971" s="17"/>
       <c r="H971" s="15"/>
+      <c r="I971" s="15"/>
     </row>
     <row r="972" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A972" s="15"/>
@@ -10900,6 +11890,7 @@
       <c r="F972" s="18"/>
       <c r="G972" s="17"/>
       <c r="H972" s="15"/>
+      <c r="I972" s="15"/>
     </row>
     <row r="973" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A973" s="15"/>
@@ -10910,6 +11901,7 @@
       <c r="F973" s="18"/>
       <c r="G973" s="17"/>
       <c r="H973" s="15"/>
+      <c r="I973" s="15"/>
     </row>
     <row r="974" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A974" s="15"/>
@@ -10920,6 +11912,7 @@
       <c r="F974" s="18"/>
       <c r="G974" s="17"/>
       <c r="H974" s="15"/>
+      <c r="I974" s="15"/>
     </row>
     <row r="975" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A975" s="15"/>
@@ -10930,6 +11923,7 @@
       <c r="F975" s="18"/>
       <c r="G975" s="17"/>
       <c r="H975" s="15"/>
+      <c r="I975" s="15"/>
     </row>
     <row r="976" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A976" s="15"/>
@@ -10940,6 +11934,7 @@
       <c r="F976" s="18"/>
       <c r="G976" s="17"/>
       <c r="H976" s="15"/>
+      <c r="I976" s="15"/>
     </row>
     <row r="977" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A977" s="15"/>
@@ -10950,6 +11945,7 @@
       <c r="F977" s="18"/>
       <c r="G977" s="17"/>
       <c r="H977" s="15"/>
+      <c r="I977" s="15"/>
     </row>
     <row r="978" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A978" s="15"/>
@@ -10960,6 +11956,7 @@
       <c r="F978" s="18"/>
       <c r="G978" s="17"/>
       <c r="H978" s="15"/>
+      <c r="I978" s="15"/>
     </row>
     <row r="979" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A979" s="15"/>
@@ -10970,6 +11967,7 @@
       <c r="F979" s="18"/>
       <c r="G979" s="17"/>
       <c r="H979" s="15"/>
+      <c r="I979" s="15"/>
     </row>
     <row r="980" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A980" s="15"/>
@@ -10980,6 +11978,7 @@
       <c r="F980" s="18"/>
       <c r="G980" s="17"/>
       <c r="H980" s="15"/>
+      <c r="I980" s="15"/>
     </row>
     <row r="981" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A981" s="15"/>
@@ -10990,6 +11989,7 @@
       <c r="F981" s="18"/>
       <c r="G981" s="17"/>
       <c r="H981" s="15"/>
+      <c r="I981" s="15"/>
     </row>
     <row r="982" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A982" s="15"/>
@@ -11000,6 +12000,7 @@
       <c r="F982" s="18"/>
       <c r="G982" s="17"/>
       <c r="H982" s="15"/>
+      <c r="I982" s="15"/>
     </row>
     <row r="983" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A983" s="15"/>
@@ -11010,6 +12011,7 @@
       <c r="F983" s="18"/>
       <c r="G983" s="17"/>
       <c r="H983" s="15"/>
+      <c r="I983" s="15"/>
     </row>
     <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A984" s="15"/>
@@ -11020,6 +12022,7 @@
       <c r="F984" s="18"/>
       <c r="G984" s="17"/>
       <c r="H984" s="15"/>
+      <c r="I984" s="15"/>
     </row>
     <row r="985" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A985" s="15"/>
@@ -11030,6 +12033,7 @@
       <c r="F985" s="18"/>
       <c r="G985" s="17"/>
       <c r="H985" s="15"/>
+      <c r="I985" s="15"/>
     </row>
     <row r="986" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A986" s="15"/>
@@ -11040,6 +12044,7 @@
       <c r="F986" s="18"/>
       <c r="G986" s="17"/>
       <c r="H986" s="15"/>
+      <c r="I986" s="15"/>
     </row>
     <row r="987" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A987" s="15"/>
@@ -11050,6 +12055,7 @@
       <c r="F987" s="18"/>
       <c r="G987" s="17"/>
       <c r="H987" s="15"/>
+      <c r="I987" s="15"/>
     </row>
     <row r="988" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A988" s="15"/>
@@ -11060,6 +12066,7 @@
       <c r="F988" s="18"/>
       <c r="G988" s="17"/>
       <c r="H988" s="15"/>
+      <c r="I988" s="15"/>
     </row>
     <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A989" s="15"/>
@@ -11070,6 +12077,7 @@
       <c r="F989" s="18"/>
       <c r="G989" s="17"/>
       <c r="H989" s="15"/>
+      <c r="I989" s="15"/>
     </row>
     <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A990" s="15"/>
@@ -11080,6 +12088,7 @@
       <c r="F990" s="18"/>
       <c r="G990" s="17"/>
       <c r="H990" s="15"/>
+      <c r="I990" s="15"/>
     </row>
     <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A991" s="15"/>
@@ -11090,6 +12099,7 @@
       <c r="F991" s="18"/>
       <c r="G991" s="17"/>
       <c r="H991" s="15"/>
+      <c r="I991" s="15"/>
     </row>
     <row r="992" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A992" s="15"/>
@@ -11100,6 +12110,7 @@
       <c r="F992" s="18"/>
       <c r="G992" s="17"/>
       <c r="H992" s="15"/>
+      <c r="I992" s="15"/>
     </row>
     <row r="993" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A993" s="15"/>
@@ -11110,6 +12121,7 @@
       <c r="F993" s="18"/>
       <c r="G993" s="17"/>
       <c r="H993" s="15"/>
+      <c r="I993" s="15"/>
     </row>
     <row r="994" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A994" s="15"/>
@@ -11120,6 +12132,7 @@
       <c r="F994" s="18"/>
       <c r="G994" s="17"/>
       <c r="H994" s="15"/>
+      <c r="I994" s="15"/>
     </row>
     <row r="995" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A995" s="15"/>
@@ -11130,6 +12143,7 @@
       <c r="F995" s="18"/>
       <c r="G995" s="17"/>
       <c r="H995" s="15"/>
+      <c r="I995" s="15"/>
     </row>
     <row r="996" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A996" s="15"/>
@@ -11140,6 +12154,7 @@
       <c r="F996" s="18"/>
       <c r="G996" s="17"/>
       <c r="H996" s="15"/>
+      <c r="I996" s="15"/>
     </row>
     <row r="997" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A997" s="15"/>
@@ -11150,6 +12165,7 @@
       <c r="F997" s="18"/>
       <c r="G997" s="17"/>
       <c r="H997" s="15"/>
+      <c r="I997" s="15"/>
     </row>
     <row r="998" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A998" s="15"/>
@@ -11160,6 +12176,7 @@
       <c r="F998" s="18"/>
       <c r="G998" s="17"/>
       <c r="H998" s="15"/>
+      <c r="I998" s="15"/>
     </row>
     <row r="999" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A999" s="15"/>
@@ -11170,6 +12187,7 @@
       <c r="F999" s="18"/>
       <c r="G999" s="17"/>
       <c r="H999" s="15"/>
+      <c r="I999" s="15"/>
     </row>
     <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1000" s="15"/>
@@ -11180,6 +12198,7 @@
       <c r="F1000" s="18"/>
       <c r="G1000" s="17"/>
       <c r="H1000" s="15"/>
+      <c r="I1000" s="15"/>
     </row>
     <row r="1001" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1001" s="15"/>
@@ -11190,6 +12209,7 @@
       <c r="F1001" s="18"/>
       <c r="G1001" s="17"/>
       <c r="H1001" s="15"/>
+      <c r="I1001" s="15"/>
     </row>
     <row r="1002" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1002" s="15"/>
@@ -11200,6 +12220,7 @@
       <c r="F1002" s="18"/>
       <c r="G1002" s="17"/>
       <c r="H1002" s="15"/>
+      <c r="I1002" s="15"/>
     </row>
     <row r="1003" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1003" s="15"/>
@@ -11210,6 +12231,7 @@
       <c r="F1003" s="18"/>
       <c r="G1003" s="17"/>
       <c r="H1003" s="15"/>
+      <c r="I1003" s="15"/>
     </row>
     <row r="1004" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1004" s="15"/>
@@ -11220,6 +12242,7 @@
       <c r="F1004" s="18"/>
       <c r="G1004" s="17"/>
       <c r="H1004" s="15"/>
+      <c r="I1004" s="15"/>
     </row>
     <row r="1005" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1005" s="15"/>
@@ -11230,21 +12253,31 @@
       <c r="F1005" s="18"/>
       <c r="G1005" s="17"/>
       <c r="H1005" s="15"/>
+      <c r="I1005" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H2004"/>
-  <conditionalFormatting sqref="A5:H2004">
+  <autoFilter ref="A4:I2004"/>
+  <conditionalFormatting sqref="H5:H2004">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND($D5="Visitante",$H5="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:I2004">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND($C5&lt;&gt;"",$F5="NO")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A2004">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>AND($A5&lt;&gt;"",COUNTIF($A$5:$A$2004,$A5)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation allowBlank="true" error="Elige un área de la lista (hoja Áreas)" errorStyle="stop" errorTitle="Área" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D1005" type="list">
+      <formula1>Áreas!$A$2:$A$31</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige el área que visita (hoja Áreas)" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H1005" type="list">
       <formula1>Áreas!$A$2:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11278,46 +12311,45 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:K45"/>
+  <dimension ref="B1:L45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="20" t="n">
         <f aca="true">TODAY()</f>
-        <v>46311</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H4" s="21" t="s">
-        <v>44</v>
+      <c r="I4" s="21" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="23" t="n">
         <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3)</f>
-        <v>1</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>47</v>
@@ -11325,142 +12357,152 @@
       <c r="J5" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="K5" s="10" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="23" t="n">
         <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI")</f>
-        <v>1</v>
-      </c>
-      <c r="H6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="24" t="n">
         <v>0.479166666666667</v>
       </c>
-      <c r="I6" s="25" t="n">
-        <f aca="false">H6+TIME(0,30,0)</f>
+      <c r="J6" s="25" t="n">
+        <f aca="false">I6+TIME(0,30,0)</f>
         <v>0.5</v>
       </c>
-      <c r="J6" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H6,Registro!$G$5:$G$2004,"&lt;"&amp;I6)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>50</v>
+      <c r="K6" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I6,Registro!$G$5:$G$2004,"&lt;"&amp;J6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="23" t="n">
         <f aca="false">C5-C6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="n">
-        <f aca="false">I6</f>
+      <c r="I7" s="25" t="n">
+        <f aca="false">J6</f>
         <v>0.5</v>
       </c>
-      <c r="I7" s="25" t="n">
-        <f aca="false">H7+TIME(0,30,0)</f>
+      <c r="J7" s="25" t="n">
+        <f aca="false">I7+TIME(0,30,0)</f>
         <v>0.520833333333333</v>
       </c>
-      <c r="J7" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H7,Registro!$G$5:$G$2004,"&lt;"&amp;I7)</f>
+      <c r="K7" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I7,Registro!$G$5:$G$2004,"&lt;"&amp;J7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="27" t="n">
         <f aca="false">IF(C5=0,0,C6/C5)</f>
-        <v>1</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <f aca="false">I7</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <f aca="false">J7</f>
         <v>0.520833333333333</v>
       </c>
-      <c r="I8" s="25" t="n">
-        <f aca="false">H8+TIME(0,30,0)</f>
+      <c r="J8" s="25" t="n">
+        <f aca="false">I8+TIME(0,30,0)</f>
         <v>0.541666666666667</v>
       </c>
-      <c r="J8" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H8,Registro!$G$5:$G$2004,"&lt;"&amp;I8)</f>
+      <c r="K8" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I8,Registro!$G$5:$G$2004,"&lt;"&amp;J8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="28" t="n">
-        <f aca="false">IF(C6=0,"-",_xlfn.MINIFS(Registro!$G$5:$G$2004,Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI"))</f>
-        <v>0.545138888888889</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <f aca="false">I8</f>
+        <v>54</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,"Visitante")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <f aca="false">J8</f>
         <v>0.541666666666667</v>
       </c>
-      <c r="I9" s="25" t="n">
-        <f aca="false">H9+TIME(0,30,0)</f>
+      <c r="J9" s="25" t="n">
+        <f aca="false">I9+TIME(0,30,0)</f>
         <v>0.5625</v>
       </c>
-      <c r="J9" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H9,Registro!$G$5:$G$2004,"&lt;"&amp;I9)</f>
-        <v>1</v>
+      <c r="K9" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I9,Registro!$G$5:$G$2004,"&lt;"&amp;J9)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" s="28" t="str">
+        <f aca="false">IF(C6=0,"-",_xlfn.MINIFS(Registro!$G$5:$G$2004,Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI"))</f>
+        <v>-</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <f aca="false">J9</f>
+        <v>0.5625</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <f aca="false">I10+TIME(0,30,0)</f>
+        <v>0.583333333333333</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I10,Registro!$G$5:$G$2004,"&lt;"&amp;J10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="28" t="str">
         <f aca="false">IF(C6=0,"-",_xlfn.MAXIFS(Registro!$G$5:$G$2004,Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI"))</f>
-        <v>0.545138888888889</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <f aca="false">I9</f>
-        <v>0.5625</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <f aca="false">H10+TIME(0,30,0)</f>
+        <v>-</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <f aca="false">J10</f>
         <v>0.583333333333333</v>
       </c>
-      <c r="J10" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H10,Registro!$G$5:$G$2004,"&lt;"&amp;I10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="25" t="n">
-        <f aca="false">I10</f>
-        <v>0.583333333333333</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <f aca="false">H11+TIME(0,30,0)</f>
+      <c r="J11" s="25" t="n">
+        <f aca="false">I11+TIME(0,30,0)</f>
         <v>0.604166666666667</v>
       </c>
-      <c r="J11" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H11,Registro!$G$5:$G$2004,"&lt;"&amp;I11)</f>
+      <c r="K11" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I11,Registro!$G$5:$G$2004,"&lt;"&amp;J11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <f aca="false">I11</f>
+        <v>57</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <f aca="false">J11</f>
         <v>0.604166666666667</v>
       </c>
-      <c r="I12" s="25" t="n">
-        <f aca="false">H12+TIME(0,30,0)</f>
+      <c r="J12" s="25" t="n">
+        <f aca="false">I12+TIME(0,30,0)</f>
         <v>0.625</v>
       </c>
-      <c r="J12" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H12,Registro!$G$5:$G$2004,"&lt;"&amp;I12)</f>
+      <c r="K12" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I12,Registro!$G$5:$G$2004,"&lt;"&amp;J12)</f>
         <v>0</v>
       </c>
     </row>
@@ -11469,27 +12511,30 @@
         <v>33</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <f aca="false">I12</f>
+        <v>60</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <f aca="false">J12</f>
         <v>0.625</v>
       </c>
-      <c r="I13" s="25" t="n">
-        <f aca="false">H13+TIME(0,30,0)</f>
+      <c r="J13" s="25" t="n">
+        <f aca="false">I13+TIME(0,30,0)</f>
         <v>0.645833333333333</v>
       </c>
-      <c r="J13" s="26" t="n">
-        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;H13,Registro!$G$5:$G$2004,"&lt;"&amp;I13)</f>
+      <c r="K13" s="26" t="n">
+        <f aca="false">COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$F$5:$F$2004,"SI",Registro!$G$5:$G$2004,"&gt;="&amp;I13,Registro!$G$5:$G$2004,"&lt;"&amp;J13)</f>
         <v>0</v>
       </c>
     </row>
@@ -11514,27 +12559,31 @@
         <f aca="false">IF(B14="","",IF(C14=0,0,D14/C14))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32" t="n">
-        <f aca="false">SUM(J6:J13)</f>
-        <v>1</v>
+      <c r="G14" s="26" t="n">
+        <f aca="false">IF(OR(B14="",B14="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B14))</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="31"/>
+      <c r="K14" s="32" t="n">
+        <f aca="false">SUM(K6:K13)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="22" t="str">
         <f aca="false">IF(Áreas!A3="","",Áreas!A3)</f>
-        <v>Mantención</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C15" s="26" t="n">
         <f aca="false">IF(B15="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B15))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="26" t="n">
         <f aca="false">IF(B15="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B15,Registro!$F$5:$F$2004,"SI"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="26" t="n">
         <f aca="false">IF(B15="","",C15-D15)</f>
@@ -11542,13 +12591,17 @@
       </c>
       <c r="F15" s="29" t="n">
         <f aca="false">IF(B15="","",IF(C15=0,0,D15/C15))</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <f aca="false">IF(OR(B15="",B15="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B15))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="22" t="str">
         <f aca="false">IF(Áreas!A4="","",Áreas!A4)</f>
-        <v>Bodega</v>
+        <v>Control calidad</v>
       </c>
       <c r="C16" s="26" t="n">
         <f aca="false">IF(B16="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B16))</f>
@@ -11564,13 +12617,17 @@
       </c>
       <c r="F16" s="29" t="n">
         <f aca="false">IF(B16="","",IF(C16=0,0,D16/C16))</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <f aca="false">IF(OR(B16="",B16="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B16))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="22" t="str">
         <f aca="false">IF(Áreas!A5="","",Áreas!A5)</f>
-        <v>Calidad</v>
+        <v>Logística</v>
       </c>
       <c r="C17" s="26" t="n">
         <f aca="false">IF(B17="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B17))</f>
@@ -11586,13 +12643,17 @@
       </c>
       <c r="F17" s="29" t="n">
         <f aca="false">IF(B17="","",IF(C17=0,0,D17/C17))</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <f aca="false">IF(OR(B17="",B17="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B17))</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="22" t="str">
         <f aca="false">IF(Áreas!A6="","",Áreas!A6)</f>
-        <v>Administración</v>
+        <v>Seguridad</v>
       </c>
       <c r="C18" s="26" t="n">
         <f aca="false">IF(B18="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B18))</f>
@@ -11608,13 +12669,17 @@
       </c>
       <c r="F18" s="29" t="n">
         <f aca="false">IF(B18="","",IF(C18=0,0,D18/C18))</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <f aca="false">IF(OR(B18="",B18="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B18))</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="str">
         <f aca="false">IF(Áreas!A7="","",Áreas!A7)</f>
-        <v>Prevención de Riesgos</v>
+        <v>HSE</v>
       </c>
       <c r="C19" s="26" t="n">
         <f aca="false">IF(B19="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B19))</f>
@@ -11630,13 +12695,17 @@
       </c>
       <c r="F19" s="29" t="n">
         <f aca="false">IF(B19="","",IF(C19=0,0,D19/C19))</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <f aca="false">IF(OR(B19="",B19="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B19))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="22" t="str">
         <f aca="false">IF(Áreas!A8="","",Áreas!A8)</f>
-        <v>Contratista</v>
+        <v>Gestión Humana</v>
       </c>
       <c r="C20" s="26" t="n">
         <f aca="false">IF(B20="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B20))</f>
@@ -11652,13 +12721,17 @@
       </c>
       <c r="F20" s="29" t="n">
         <f aca="false">IF(B20="","",IF(C20=0,0,D20/C20))</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <f aca="false">IF(OR(B20="",B20="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B20))</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="str">
         <f aca="false">IF(Áreas!A9="","",Áreas!A9)</f>
-        <v>Visita</v>
+        <v>Contabilidad</v>
       </c>
       <c r="C21" s="26" t="n">
         <f aca="false">IF(B21="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B21))</f>
@@ -11674,28 +12747,36 @@
       </c>
       <c r="F21" s="29" t="n">
         <f aca="false">IF(B21="","",IF(C21=0,0,D21/C21))</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="26" t="n">
+        <f aca="false">IF(OR(B21="",B21="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B21))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="22" t="str">
         <f aca="false">IF(Áreas!A10="","",Áreas!A10)</f>
-        <v/>
-      </c>
-      <c r="C22" s="26" t="str">
+        <v>Visitante</v>
+      </c>
+      <c r="C22" s="26" t="n">
         <f aca="false">IF(B22="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B22))</f>
-        <v/>
-      </c>
-      <c r="D22" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="D22" s="26" t="n">
         <f aca="false">IF(B22="","",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$D$5:$D$2004,B22,Registro!$F$5:$F$2004,"SI"))</f>
-        <v/>
-      </c>
-      <c r="E22" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="E22" s="26" t="n">
         <f aca="false">IF(B22="","",C22-D22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="29" t="str">
+        <v>0</v>
+      </c>
+      <c r="F22" s="29" t="n">
         <f aca="false">IF(B22="","",IF(C22=0,0,D22/C22))</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="26" t="str">
+        <f aca="false">IF(OR(B22="",B22="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B22))</f>
         <v/>
       </c>
     </row>
@@ -11720,6 +12801,10 @@
         <f aca="false">IF(B23="","",IF(C23=0,0,D23/C23))</f>
         <v/>
       </c>
+      <c r="G23" s="26" t="str">
+        <f aca="false">IF(OR(B23="",B23="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="str">
@@ -11742,6 +12827,10 @@
         <f aca="false">IF(B24="","",IF(C24=0,0,D24/C24))</f>
         <v/>
       </c>
+      <c r="G24" s="26" t="str">
+        <f aca="false">IF(OR(B24="",B24="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="str">
@@ -11764,6 +12853,10 @@
         <f aca="false">IF(B25="","",IF(C25=0,0,D25/C25))</f>
         <v/>
       </c>
+      <c r="G25" s="26" t="str">
+        <f aca="false">IF(OR(B25="",B25="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="22" t="str">
@@ -11786,6 +12879,10 @@
         <f aca="false">IF(B26="","",IF(C26=0,0,D26/C26))</f>
         <v/>
       </c>
+      <c r="G26" s="26" t="str">
+        <f aca="false">IF(OR(B26="",B26="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="str">
@@ -11808,6 +12905,10 @@
         <f aca="false">IF(B27="","",IF(C27=0,0,D27/C27))</f>
         <v/>
       </c>
+      <c r="G27" s="26" t="str">
+        <f aca="false">IF(OR(B27="",B27="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="str">
@@ -11830,6 +12931,10 @@
         <f aca="false">IF(B28="","",IF(C28=0,0,D28/C28))</f>
         <v/>
       </c>
+      <c r="G28" s="26" t="str">
+        <f aca="false">IF(OR(B28="",B28="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="str">
@@ -11852,6 +12957,10 @@
         <f aca="false">IF(B29="","",IF(C29=0,0,D29/C29))</f>
         <v/>
       </c>
+      <c r="G29" s="26" t="str">
+        <f aca="false">IF(OR(B29="",B29="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="22" t="str">
@@ -11874,6 +12983,10 @@
         <f aca="false">IF(B30="","",IF(C30=0,0,D30/C30))</f>
         <v/>
       </c>
+      <c r="G30" s="26" t="str">
+        <f aca="false">IF(OR(B30="",B30="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="22" t="str">
@@ -11896,6 +13009,10 @@
         <f aca="false">IF(B31="","",IF(C31=0,0,D31/C31))</f>
         <v/>
       </c>
+      <c r="G31" s="26" t="str">
+        <f aca="false">IF(OR(B31="",B31="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B31))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="str">
@@ -11918,6 +13035,10 @@
         <f aca="false">IF(B32="","",IF(C32=0,0,D32/C32))</f>
         <v/>
       </c>
+      <c r="G32" s="26" t="str">
+        <f aca="false">IF(OR(B32="",B32="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B32))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="22" t="str">
@@ -11940,6 +13061,10 @@
         <f aca="false">IF(B33="","",IF(C33=0,0,D33/C33))</f>
         <v/>
       </c>
+      <c r="G33" s="26" t="str">
+        <f aca="false">IF(OR(B33="",B33="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="22" t="str">
@@ -11962,6 +13087,10 @@
         <f aca="false">IF(B34="","",IF(C34=0,0,D34/C34))</f>
         <v/>
       </c>
+      <c r="G34" s="26" t="str">
+        <f aca="false">IF(OR(B34="",B34="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="str">
@@ -11984,6 +13113,10 @@
         <f aca="false">IF(B35="","",IF(C35=0,0,D35/C35))</f>
         <v/>
       </c>
+      <c r="G35" s="26" t="str">
+        <f aca="false">IF(OR(B35="",B35="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B35))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="22" t="str">
@@ -12006,6 +13139,10 @@
         <f aca="false">IF(B36="","",IF(C36=0,0,D36/C36))</f>
         <v/>
       </c>
+      <c r="G36" s="26" t="str">
+        <f aca="false">IF(OR(B36="",B36="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B36))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="22" t="str">
@@ -12028,6 +13165,10 @@
         <f aca="false">IF(B37="","",IF(C37=0,0,D37/C37))</f>
         <v/>
       </c>
+      <c r="G37" s="26" t="str">
+        <f aca="false">IF(OR(B37="",B37="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B37))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="22" t="str">
@@ -12050,6 +13191,10 @@
         <f aca="false">IF(B38="","",IF(C38=0,0,D38/C38))</f>
         <v/>
       </c>
+      <c r="G38" s="26" t="str">
+        <f aca="false">IF(OR(B38="",B38="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B38))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="22" t="str">
@@ -12072,6 +13217,10 @@
         <f aca="false">IF(B39="","",IF(C39=0,0,D39/C39))</f>
         <v/>
       </c>
+      <c r="G39" s="26" t="str">
+        <f aca="false">IF(OR(B39="",B39="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B39))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="22" t="str">
@@ -12094,6 +13243,10 @@
         <f aca="false">IF(B40="","",IF(C40=0,0,D40/C40))</f>
         <v/>
       </c>
+      <c r="G40" s="26" t="str">
+        <f aca="false">IF(OR(B40="",B40="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B40))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="22" t="str">
@@ -12116,6 +13269,10 @@
         <f aca="false">IF(B41="","",IF(C41=0,0,D41/C41))</f>
         <v/>
       </c>
+      <c r="G41" s="26" t="str">
+        <f aca="false">IF(OR(B41="",B41="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B41))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="str">
@@ -12138,6 +13295,10 @@
         <f aca="false">IF(B42="","",IF(C42=0,0,D42/C42))</f>
         <v/>
       </c>
+      <c r="G42" s="26" t="str">
+        <f aca="false">IF(OR(B42="",B42="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B42))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="22" t="str">
@@ -12160,18 +13321,22 @@
         <f aca="false">IF(B43="","",IF(C43=0,0,D43/C43))</f>
         <v/>
       </c>
+      <c r="G43" s="26" t="str">
+        <f aca="false">IF(OR(B43="",B43="Visitante"),"",COUNTIFS(Registro!$B$5:$B$2004,$C$3,Registro!$H$5:$H$2004,B43))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C44" s="32" t="n">
         <f aca="false">SUM(C14:C43)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="32" t="n">
         <f aca="false">SUM(D14:D43)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="32" t="n">
         <f aca="false">SUM(E14:E43)</f>
@@ -12179,12 +13344,16 @@
       </c>
       <c r="F44" s="33" t="n">
         <f aca="false">IF(C44=0,0,D44/C44)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G44" s="32" t="n">
+        <f aca="false">SUM(G14:G43)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -12222,27 +13391,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="34" t="n">
         <f aca="true">YEAR(TODAY())</f>
         <v>2026</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" s="34" t="n">
         <f aca="true">MONTH(TODAY())</f>
@@ -12262,19 +13431,19 @@
         <v>31</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13085,7 +14254,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C38" s="31"/>
       <c r="D38" s="32" t="n">
@@ -13107,7 +14276,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B7:G37">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>AND($B7&lt;&gt;"",WEEKDAY($B7,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13133,7 +14302,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -13144,47 +14313,52 @@
         <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="40" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
